--- a/Results/Group Analysis/GroupCrossing_YoungAdults_SPSS.xlsx
+++ b/Results/Group Analysis/GroupCrossing_YoungAdults_SPSS.xlsx
@@ -18,1165 +18,1165 @@
     <t>Test</t>
   </si>
   <si>
-    <t>T1_clr_min_W1_H1_Leading</t>
-  </si>
-  <si>
-    <t>T1_clr_min_W1_H1_Trailing</t>
-  </si>
-  <si>
-    <t>T1_clr_min_W1_H2_Leading</t>
-  </si>
-  <si>
-    <t>T1_clr_min_W1_H2_Trailing</t>
-  </si>
-  <si>
-    <t>T1_clr_min_W1_H3_Leading</t>
-  </si>
-  <si>
-    <t>T1_clr_min_W1_H3_Trailing</t>
-  </si>
-  <si>
-    <t>T1_clr_min_W2_H1_Leading</t>
-  </si>
-  <si>
-    <t>T1_clr_min_W2_H1_Trailing</t>
-  </si>
-  <si>
-    <t>T1_clr_min_W2_H2_Leading</t>
-  </si>
-  <si>
-    <t>T1_clr_min_W2_H2_Trailing</t>
-  </si>
-  <si>
-    <t>T1_clr_min_W2_H3_Leading</t>
-  </si>
-  <si>
-    <t>T1_clr_min_W2_H3_Trailing</t>
-  </si>
-  <si>
-    <t>T1_lift_dist_W1_H1_Leading</t>
-  </si>
-  <si>
-    <t>T1_lift_dist_W1_H1_Trailing</t>
-  </si>
-  <si>
-    <t>T1_lift_dist_W1_H2_Leading</t>
-  </si>
-  <si>
-    <t>T1_lift_dist_W1_H2_Trailing</t>
-  </si>
-  <si>
-    <t>T1_lift_dist_W1_H3_Leading</t>
-  </si>
-  <si>
-    <t>T1_lift_dist_W1_H3_Trailing</t>
-  </si>
-  <si>
-    <t>T1_lift_dist_W2_H1_Leading</t>
-  </si>
-  <si>
-    <t>T1_lift_dist_W2_H1_Trailing</t>
-  </si>
-  <si>
-    <t>T1_lift_dist_W2_H2_Leading</t>
-  </si>
-  <si>
-    <t>T1_lift_dist_W2_H2_Trailing</t>
-  </si>
-  <si>
-    <t>T1_lift_dist_W2_H3_Leading</t>
-  </si>
-  <si>
-    <t>T1_lift_dist_W2_H3_Trailing</t>
-  </si>
-  <si>
-    <t>T1_land_dist_W1_H1_Leading</t>
-  </si>
-  <si>
-    <t>T1_land_dist_W1_H1_Trailing</t>
-  </si>
-  <si>
-    <t>T1_land_dist_W1_H2_Leading</t>
-  </si>
-  <si>
-    <t>T1_land_dist_W1_H2_Trailing</t>
-  </si>
-  <si>
-    <t>T1_land_dist_W1_H3_Leading</t>
-  </si>
-  <si>
-    <t>T1_land_dist_W1_H3_Trailing</t>
-  </si>
-  <si>
-    <t>T1_land_dist_W2_H1_Leading</t>
-  </si>
-  <si>
-    <t>T1_land_dist_W2_H1_Trailing</t>
-  </si>
-  <si>
-    <t>T1_land_dist_W2_H2_Leading</t>
-  </si>
-  <si>
-    <t>T1_land_dist_W2_H2_Trailing</t>
-  </si>
-  <si>
-    <t>T1_land_dist_W2_H3_Leading</t>
-  </si>
-  <si>
-    <t>T1_land_dist_W2_H3_Trailing</t>
-  </si>
-  <si>
-    <t>SPT_stride_W1_H1_Leading</t>
-  </si>
-  <si>
-    <t>SPT_stride_W1_H1_Trailing</t>
-  </si>
-  <si>
-    <t>SPT_stride_W1_H2_Leading</t>
-  </si>
-  <si>
-    <t>SPT_stride_W1_H2_Trailing</t>
-  </si>
-  <si>
-    <t>SPT_stride_W1_H3_Leading</t>
-  </si>
-  <si>
-    <t>SPT_stride_W1_H3_Trailing</t>
-  </si>
-  <si>
-    <t>SPT_stride_W2_H1_Leading</t>
-  </si>
-  <si>
-    <t>SPT_stride_W2_H1_Trailing</t>
-  </si>
-  <si>
-    <t>SPT_stride_W2_H2_Leading</t>
-  </si>
-  <si>
-    <t>SPT_stride_W2_H2_Trailing</t>
-  </si>
-  <si>
-    <t>SPT_stride_W2_H3_Leading</t>
-  </si>
-  <si>
-    <t>SPT_stride_W2_H3_Trailing</t>
-  </si>
-  <si>
-    <t>SPT_stride_Level_Walk</t>
-  </si>
-  <si>
-    <t>SPT_cadence_W1_H1_Leading</t>
-  </si>
-  <si>
-    <t>SPT_cadence_W1_H1_Trailing</t>
-  </si>
-  <si>
-    <t>SPT_cadence_W1_H2_Leading</t>
-  </si>
-  <si>
-    <t>SPT_cadence_W1_H2_Trailing</t>
-  </si>
-  <si>
-    <t>SPT_cadence_W1_H3_Leading</t>
-  </si>
-  <si>
-    <t>SPT_cadence_W1_H3_Trailing</t>
-  </si>
-  <si>
-    <t>SPT_cadence_W2_H1_Leading</t>
-  </si>
-  <si>
-    <t>SPT_cadence_W2_H1_Trailing</t>
-  </si>
-  <si>
-    <t>SPT_cadence_W2_H2_Leading</t>
-  </si>
-  <si>
-    <t>SPT_cadence_W2_H2_Trailing</t>
-  </si>
-  <si>
-    <t>SPT_cadence_W2_H3_Leading</t>
-  </si>
-  <si>
-    <t>SPT_cadence_W2_H3_Trailing</t>
-  </si>
-  <si>
-    <t>SPT_cadence_Level_Walk</t>
-  </si>
-  <si>
-    <t>SPT_speed_W1_H1_Leading</t>
-  </si>
-  <si>
-    <t>SPT_speed_W1_H1_Trailing</t>
-  </si>
-  <si>
-    <t>SPT_speed_W1_H2_Leading</t>
-  </si>
-  <si>
-    <t>SPT_speed_W1_H2_Trailing</t>
-  </si>
-  <si>
-    <t>SPT_speed_W1_H3_Leading</t>
-  </si>
-  <si>
-    <t>SPT_speed_W1_H3_Trailing</t>
-  </si>
-  <si>
-    <t>SPT_speed_W2_H1_Leading</t>
-  </si>
-  <si>
-    <t>SPT_speed_W2_H1_Trailing</t>
-  </si>
-  <si>
-    <t>SPT_speed_W2_H2_Leading</t>
-  </si>
-  <si>
-    <t>SPT_speed_W2_H2_Trailing</t>
-  </si>
-  <si>
-    <t>SPT_speed_W2_H3_Leading</t>
-  </si>
-  <si>
-    <t>SPT_speed_W2_H3_Trailing</t>
-  </si>
-  <si>
-    <t>SPT_speed_Level_Walk</t>
-  </si>
-  <si>
-    <t>ROM_ankle_angle_W1_H1_Leading</t>
-  </si>
-  <si>
-    <t>ROM_ankle_angle_W1_H1_Trailing</t>
-  </si>
-  <si>
-    <t>ROM_ankle_angle_W1_H2_Leading</t>
-  </si>
-  <si>
-    <t>ROM_ankle_angle_W1_H2_Trailing</t>
-  </si>
-  <si>
-    <t>ROM_ankle_angle_W1_H3_Leading</t>
-  </si>
-  <si>
-    <t>ROM_ankle_angle_W1_H3_Trailing</t>
-  </si>
-  <si>
-    <t>ROM_ankle_angle_W2_H1_Leading</t>
-  </si>
-  <si>
-    <t>ROM_ankle_angle_W2_H1_Trailing</t>
-  </si>
-  <si>
-    <t>ROM_ankle_angle_W2_H2_Leading</t>
-  </si>
-  <si>
-    <t>ROM_ankle_angle_W2_H2_Trailing</t>
-  </si>
-  <si>
-    <t>ROM_ankle_angle_W2_H3_Leading</t>
-  </si>
-  <si>
-    <t>ROM_ankle_angle_W2_H3_Trailing</t>
-  </si>
-  <si>
-    <t>ROM_ankle_angle_Level_Walk</t>
-  </si>
-  <si>
-    <t>JMAX_hip_flexion_W1_H1_Leading</t>
-  </si>
-  <si>
-    <t>JMAX_hip_flexion_W1_H1_Trailing</t>
-  </si>
-  <si>
-    <t>JMAX_hip_flexion_W1_H2_Leading</t>
-  </si>
-  <si>
-    <t>JMAX_hip_flexion_W1_H2_Trailing</t>
-  </si>
-  <si>
-    <t>JMAX_hip_flexion_W1_H3_Leading</t>
-  </si>
-  <si>
-    <t>JMAX_hip_flexion_W1_H3_Trailing</t>
-  </si>
-  <si>
-    <t>JMAX_hip_flexion_W2_H1_Leading</t>
-  </si>
-  <si>
-    <t>JMAX_hip_flexion_W2_H1_Trailing</t>
-  </si>
-  <si>
-    <t>JMAX_hip_flexion_W2_H2_Leading</t>
-  </si>
-  <si>
-    <t>JMAX_hip_flexion_W2_H2_Trailing</t>
-  </si>
-  <si>
-    <t>JMAX_hip_flexion_W2_H3_Leading</t>
-  </si>
-  <si>
-    <t>JMAX_hip_flexion_W2_H3_Trailing</t>
-  </si>
-  <si>
-    <t>JMAX_hip_flexion_Level_Walk</t>
-  </si>
-  <si>
-    <t>JMAX_knee_angle_W1_H1_Leading</t>
-  </si>
-  <si>
-    <t>JMAX_knee_angle_W1_H1_Trailing</t>
-  </si>
-  <si>
-    <t>JMAX_knee_angle_W1_H2_Leading</t>
-  </si>
-  <si>
-    <t>JMAX_knee_angle_W1_H2_Trailing</t>
-  </si>
-  <si>
-    <t>JMAX_knee_angle_W1_H3_Leading</t>
-  </si>
-  <si>
-    <t>JMAX_knee_angle_W1_H3_Trailing</t>
-  </si>
-  <si>
-    <t>JMAX_knee_angle_W2_H1_Leading</t>
-  </si>
-  <si>
-    <t>JMAX_knee_angle_W2_H1_Trailing</t>
-  </si>
-  <si>
-    <t>JMAX_knee_angle_W2_H2_Leading</t>
-  </si>
-  <si>
-    <t>JMAX_knee_angle_W2_H2_Trailing</t>
-  </si>
-  <si>
-    <t>JMAX_knee_angle_W2_H3_Leading</t>
-  </si>
-  <si>
-    <t>JMAX_knee_angle_W2_H3_Trailing</t>
-  </si>
-  <si>
-    <t>JMAX_knee_angle_Level_Walk</t>
-  </si>
-  <si>
-    <t>JMAX_ankle_angle_W1_H1_Leading</t>
-  </si>
-  <si>
-    <t>JMAX_ankle_angle_W1_H1_Trailing</t>
-  </si>
-  <si>
-    <t>JMAX_ankle_angle_W1_H2_Leading</t>
-  </si>
-  <si>
-    <t>JMAX_ankle_angle_W1_H2_Trailing</t>
-  </si>
-  <si>
-    <t>JMAX_ankle_angle_W1_H3_Leading</t>
-  </si>
-  <si>
-    <t>JMAX_ankle_angle_W1_H3_Trailing</t>
-  </si>
-  <si>
-    <t>JMAX_ankle_angle_W2_H1_Leading</t>
-  </si>
-  <si>
-    <t>JMAX_ankle_angle_W2_H1_Trailing</t>
-  </si>
-  <si>
-    <t>JMAX_ankle_angle_W2_H2_Leading</t>
-  </si>
-  <si>
-    <t>JMAX_ankle_angle_W2_H2_Trailing</t>
-  </si>
-  <si>
-    <t>JMAX_ankle_angle_W2_H3_Leading</t>
-  </si>
-  <si>
-    <t>JMAX_ankle_angle_W2_H3_Trailing</t>
-  </si>
-  <si>
-    <t>JMAX_ankle_angle_Level_Walk</t>
-  </si>
-  <si>
-    <t>JMIN_hip_flexion_W1_H1_Leading</t>
-  </si>
-  <si>
-    <t>JMIN_hip_flexion_W1_H1_Trailing</t>
-  </si>
-  <si>
-    <t>JMIN_hip_flexion_W1_H2_Leading</t>
-  </si>
-  <si>
-    <t>JMIN_hip_flexion_W1_H2_Trailing</t>
-  </si>
-  <si>
-    <t>JMIN_hip_flexion_W1_H3_Leading</t>
-  </si>
-  <si>
-    <t>JMIN_hip_flexion_W1_H3_Trailing</t>
-  </si>
-  <si>
-    <t>JMIN_hip_flexion_W2_H1_Leading</t>
-  </si>
-  <si>
-    <t>JMIN_hip_flexion_W2_H1_Trailing</t>
-  </si>
-  <si>
-    <t>JMIN_hip_flexion_W2_H2_Leading</t>
-  </si>
-  <si>
-    <t>JMIN_hip_flexion_W2_H2_Trailing</t>
-  </si>
-  <si>
-    <t>JMIN_hip_flexion_W2_H3_Leading</t>
-  </si>
-  <si>
-    <t>JMIN_hip_flexion_W2_H3_Trailing</t>
-  </si>
-  <si>
-    <t>JMIN_hip_flexion_Level_Walk</t>
-  </si>
-  <si>
-    <t>JMIN_knee_angle_W1_H1_Leading</t>
-  </si>
-  <si>
-    <t>JMIN_knee_angle_W1_H1_Trailing</t>
-  </si>
-  <si>
-    <t>JMIN_knee_angle_W1_H2_Leading</t>
-  </si>
-  <si>
-    <t>JMIN_knee_angle_W1_H2_Trailing</t>
-  </si>
-  <si>
-    <t>JMIN_knee_angle_W1_H3_Leading</t>
-  </si>
-  <si>
-    <t>JMIN_knee_angle_W1_H3_Trailing</t>
-  </si>
-  <si>
-    <t>JMIN_knee_angle_W2_H1_Leading</t>
-  </si>
-  <si>
-    <t>JMIN_knee_angle_W2_H1_Trailing</t>
-  </si>
-  <si>
-    <t>JMIN_knee_angle_W2_H2_Leading</t>
-  </si>
-  <si>
-    <t>JMIN_knee_angle_W2_H2_Trailing</t>
-  </si>
-  <si>
-    <t>JMIN_knee_angle_W2_H3_Leading</t>
-  </si>
-  <si>
-    <t>JMIN_knee_angle_W2_H3_Trailing</t>
-  </si>
-  <si>
-    <t>JMIN_knee_angle_Level_Walk</t>
-  </si>
-  <si>
-    <t>JMIN_ankle_angle_W1_H1_Leading</t>
-  </si>
-  <si>
-    <t>JMIN_ankle_angle_W1_H1_Trailing</t>
-  </si>
-  <si>
-    <t>JMIN_ankle_angle_W1_H2_Leading</t>
-  </si>
-  <si>
-    <t>JMIN_ankle_angle_W1_H2_Trailing</t>
-  </si>
-  <si>
-    <t>JMIN_ankle_angle_W1_H3_Leading</t>
-  </si>
-  <si>
-    <t>JMIN_ankle_angle_W1_H3_Trailing</t>
-  </si>
-  <si>
-    <t>JMIN_ankle_angle_W2_H1_Leading</t>
-  </si>
-  <si>
-    <t>JMIN_ankle_angle_W2_H1_Trailing</t>
-  </si>
-  <si>
-    <t>JMIN_ankle_angle_W2_H2_Leading</t>
-  </si>
-  <si>
-    <t>JMIN_ankle_angle_W2_H2_Trailing</t>
-  </si>
-  <si>
-    <t>JMIN_ankle_angle_W2_H3_Leading</t>
-  </si>
-  <si>
-    <t>JMIN_ankle_angle_W2_H3_Trailing</t>
-  </si>
-  <si>
-    <t>JMIN_ankle_angle_Level_Walk</t>
-  </si>
-  <si>
-    <t>SROM_Foot_W1_H1_Leading</t>
-  </si>
-  <si>
-    <t>SROM_Foot_W1_H1_Trailing</t>
-  </si>
-  <si>
-    <t>SROM_Foot_W1_H2_Leading</t>
-  </si>
-  <si>
-    <t>SROM_Foot_W1_H2_Trailing</t>
-  </si>
-  <si>
-    <t>SROM_Foot_W1_H3_Leading</t>
-  </si>
-  <si>
-    <t>SROM_Foot_W1_H3_Trailing</t>
-  </si>
-  <si>
-    <t>SROM_Foot_W2_H1_Leading</t>
-  </si>
-  <si>
-    <t>SROM_Foot_W2_H1_Trailing</t>
-  </si>
-  <si>
-    <t>SROM_Foot_W2_H2_Leading</t>
-  </si>
-  <si>
-    <t>SROM_Foot_W2_H2_Trailing</t>
-  </si>
-  <si>
-    <t>SROM_Foot_W2_H3_Leading</t>
-  </si>
-  <si>
-    <t>SROM_Foot_W2_H3_Trailing</t>
-  </si>
-  <si>
-    <t>SROM_Foot_Level_Walk</t>
-  </si>
-  <si>
-    <t>PEX_hip_pk_flex_W1_H1_Leading</t>
-  </si>
-  <si>
-    <t>PEX_hip_pk_flex_W1_H1_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_hip_pk_flex_W1_H2_Leading</t>
-  </si>
-  <si>
-    <t>PEX_hip_pk_flex_W1_H2_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_hip_pk_flex_W1_H3_Leading</t>
-  </si>
-  <si>
-    <t>PEX_hip_pk_flex_W1_H3_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_hip_pk_flex_W2_H1_Leading</t>
-  </si>
-  <si>
-    <t>PEX_hip_pk_flex_W2_H1_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_hip_pk_flex_W2_H2_Leading</t>
-  </si>
-  <si>
-    <t>PEX_hip_pk_flex_W2_H2_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_hip_pk_flex_W2_H3_Leading</t>
-  </si>
-  <si>
-    <t>PEX_hip_pk_flex_W2_H3_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_hip_pk_flex_Level_Walk</t>
-  </si>
-  <si>
-    <t>PEX_knee_pk_flex_W1_H1_Leading</t>
-  </si>
-  <si>
-    <t>PEX_knee_pk_flex_W1_H1_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_knee_pk_flex_W1_H2_Leading</t>
-  </si>
-  <si>
-    <t>PEX_knee_pk_flex_W1_H2_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_knee_pk_flex_W1_H3_Leading</t>
-  </si>
-  <si>
-    <t>PEX_knee_pk_flex_W1_H3_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_knee_pk_flex_W2_H1_Leading</t>
-  </si>
-  <si>
-    <t>PEX_knee_pk_flex_W2_H1_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_knee_pk_flex_W2_H2_Leading</t>
-  </si>
-  <si>
-    <t>PEX_knee_pk_flex_W2_H2_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_knee_pk_flex_W2_H3_Leading</t>
-  </si>
-  <si>
-    <t>PEX_knee_pk_flex_W2_H3_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_knee_pk_flex_Level_Walk</t>
-  </si>
-  <si>
-    <t>PEX_ank_plant_W1_H1_Leading</t>
-  </si>
-  <si>
-    <t>PEX_ank_plant_W1_H1_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_ank_plant_W1_H2_Leading</t>
-  </si>
-  <si>
-    <t>PEX_ank_plant_W1_H2_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_ank_plant_W1_H3_Leading</t>
-  </si>
-  <si>
-    <t>PEX_ank_plant_W1_H3_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_ank_plant_W2_H1_Leading</t>
-  </si>
-  <si>
-    <t>PEX_ank_plant_W2_H1_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_ank_plant_W2_H2_Leading</t>
-  </si>
-  <si>
-    <t>PEX_ank_plant_W2_H2_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_ank_plant_W2_H3_Leading</t>
-  </si>
-  <si>
-    <t>PEX_ank_plant_W2_H3_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_ank_plant_Level_Walk</t>
-  </si>
-  <si>
-    <t>PEX_ank_dorsi_W1_H1_Leading</t>
-  </si>
-  <si>
-    <t>PEX_ank_dorsi_W1_H1_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_ank_dorsi_W1_H2_Leading</t>
-  </si>
-  <si>
-    <t>PEX_ank_dorsi_W1_H2_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_ank_dorsi_W1_H3_Leading</t>
-  </si>
-  <si>
-    <t>PEX_ank_dorsi_W1_H3_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_ank_dorsi_W2_H1_Leading</t>
-  </si>
-  <si>
-    <t>PEX_ank_dorsi_W2_H1_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_ank_dorsi_W2_H2_Leading</t>
-  </si>
-  <si>
-    <t>PEX_ank_dorsi_W2_H2_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_ank_dorsi_W2_H3_Leading</t>
-  </si>
-  <si>
-    <t>PEX_ank_dorsi_W2_H3_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_ank_dorsi_Level_Walk</t>
-  </si>
-  <si>
-    <t>PEX_thigh_fwd_W1_H1_Leading</t>
-  </si>
-  <si>
-    <t>PEX_thigh_fwd_W1_H1_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_thigh_fwd_W1_H2_Leading</t>
-  </si>
-  <si>
-    <t>PEX_thigh_fwd_W1_H2_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_thigh_fwd_W1_H3_Leading</t>
-  </si>
-  <si>
-    <t>PEX_thigh_fwd_W1_H3_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_thigh_fwd_W2_H1_Leading</t>
-  </si>
-  <si>
-    <t>PEX_thigh_fwd_W2_H1_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_thigh_fwd_W2_H2_Leading</t>
-  </si>
-  <si>
-    <t>PEX_thigh_fwd_W2_H2_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_thigh_fwd_W2_H3_Leading</t>
-  </si>
-  <si>
-    <t>PEX_thigh_fwd_W2_H3_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_thigh_fwd_Level_Walk</t>
-  </si>
-  <si>
-    <t>PEX_shank_back_W1_H1_Leading</t>
-  </si>
-  <si>
-    <t>PEX_shank_back_W1_H1_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_shank_back_W1_H2_Leading</t>
-  </si>
-  <si>
-    <t>PEX_shank_back_W1_H2_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_shank_back_W1_H3_Leading</t>
-  </si>
-  <si>
-    <t>PEX_shank_back_W1_H3_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_shank_back_W2_H1_Leading</t>
-  </si>
-  <si>
-    <t>PEX_shank_back_W2_H1_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_shank_back_W2_H2_Leading</t>
-  </si>
-  <si>
-    <t>PEX_shank_back_W2_H2_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_shank_back_W2_H3_Leading</t>
-  </si>
-  <si>
-    <t>PEX_shank_back_W2_H3_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_shank_back_Level_Walk</t>
-  </si>
-  <si>
-    <t>PEX_foot_toedown_W1_H1_Leading</t>
-  </si>
-  <si>
-    <t>PEX_foot_toedown_W1_H1_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_foot_toedown_W1_H2_Leading</t>
-  </si>
-  <si>
-    <t>PEX_foot_toedown_W1_H2_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_foot_toedown_W1_H3_Leading</t>
-  </si>
-  <si>
-    <t>PEX_foot_toedown_W1_H3_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_foot_toedown_W2_H1_Leading</t>
-  </si>
-  <si>
-    <t>PEX_foot_toedown_W2_H1_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_foot_toedown_W2_H2_Leading</t>
-  </si>
-  <si>
-    <t>PEX_foot_toedown_W2_H2_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_foot_toedown_W2_H3_Leading</t>
-  </si>
-  <si>
-    <t>PEX_foot_toedown_W2_H3_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_foot_toedown_Level_Walk</t>
-  </si>
-  <si>
-    <t>PEX_shank_fwd_W1_H1_Leading</t>
-  </si>
-  <si>
-    <t>PEX_shank_fwd_W1_H1_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_shank_fwd_W1_H2_Leading</t>
-  </si>
-  <si>
-    <t>PEX_shank_fwd_W1_H2_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_shank_fwd_W1_H3_Leading</t>
-  </si>
-  <si>
-    <t>PEX_shank_fwd_W1_H3_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_shank_fwd_W2_H1_Leading</t>
-  </si>
-  <si>
-    <t>PEX_shank_fwd_W2_H1_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_shank_fwd_W2_H2_Leading</t>
-  </si>
-  <si>
-    <t>PEX_shank_fwd_W2_H2_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_shank_fwd_W2_H3_Leading</t>
-  </si>
-  <si>
-    <t>PEX_shank_fwd_W2_H3_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_shank_fwd_Level_Walk</t>
-  </si>
-  <si>
-    <t>PEX_foot_toeup_W1_H1_Leading</t>
-  </si>
-  <si>
-    <t>PEX_foot_toeup_W1_H1_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_foot_toeup_W1_H2_Leading</t>
-  </si>
-  <si>
-    <t>PEX_foot_toeup_W1_H2_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_foot_toeup_W1_H3_Leading</t>
-  </si>
-  <si>
-    <t>PEX_foot_toeup_W1_H3_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_foot_toeup_W2_H1_Leading</t>
-  </si>
-  <si>
-    <t>PEX_foot_toeup_W2_H1_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_foot_toeup_W2_H2_Leading</t>
-  </si>
-  <si>
-    <t>PEX_foot_toeup_W2_H2_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_foot_toeup_W2_H3_Leading</t>
-  </si>
-  <si>
-    <t>PEX_foot_toeup_W2_H3_Trailing</t>
-  </si>
-  <si>
-    <t>PEX_foot_toeup_Level_Walk</t>
-  </si>
-  <si>
-    <t>PKT_hip_flexion_W1_H1_Leading</t>
-  </si>
-  <si>
-    <t>PKT_hip_flexion_W1_H1_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_hip_flexion_W1_H2_Leading</t>
-  </si>
-  <si>
-    <t>PKT_hip_flexion_W1_H2_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_hip_flexion_W1_H3_Leading</t>
-  </si>
-  <si>
-    <t>PKT_hip_flexion_W1_H3_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_hip_flexion_W2_H1_Leading</t>
-  </si>
-  <si>
-    <t>PKT_hip_flexion_W2_H1_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_hip_flexion_W2_H2_Leading</t>
-  </si>
-  <si>
-    <t>PKT_hip_flexion_W2_H2_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_hip_flexion_W2_H3_Leading</t>
-  </si>
-  <si>
-    <t>PKT_hip_flexion_W2_H3_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_hip_flexion_Level_Walk</t>
-  </si>
-  <si>
-    <t>PKT_knee_angle_W1_H1_Leading</t>
-  </si>
-  <si>
-    <t>PKT_knee_angle_W1_H1_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_knee_angle_W1_H2_Leading</t>
-  </si>
-  <si>
-    <t>PKT_knee_angle_W1_H2_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_knee_angle_W1_H3_Leading</t>
-  </si>
-  <si>
-    <t>PKT_knee_angle_W1_H3_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_knee_angle_W2_H1_Leading</t>
-  </si>
-  <si>
-    <t>PKT_knee_angle_W2_H1_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_knee_angle_W2_H2_Leading</t>
-  </si>
-  <si>
-    <t>PKT_knee_angle_W2_H2_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_knee_angle_W2_H3_Leading</t>
-  </si>
-  <si>
-    <t>PKT_knee_angle_W2_H3_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_knee_angle_Level_Walk</t>
-  </si>
-  <si>
-    <t>PKT_ankle_angle_W1_H1_Leading</t>
-  </si>
-  <si>
-    <t>PKT_ankle_angle_W1_H1_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_ankle_angle_W1_H2_Leading</t>
-  </si>
-  <si>
-    <t>PKT_ankle_angle_W1_H2_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_ankle_angle_W1_H3_Leading</t>
-  </si>
-  <si>
-    <t>PKT_ankle_angle_W1_H3_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_ankle_angle_W2_H1_Leading</t>
-  </si>
-  <si>
-    <t>PKT_ankle_angle_W2_H1_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_ankle_angle_W2_H2_Leading</t>
-  </si>
-  <si>
-    <t>PKT_ankle_angle_W2_H2_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_ankle_angle_W2_H3_Leading</t>
-  </si>
-  <si>
-    <t>PKT_ankle_angle_W2_H3_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_ankle_angle_Level_Walk</t>
-  </si>
-  <si>
-    <t>PKT_FootHeight_W1_H1_Leading</t>
-  </si>
-  <si>
-    <t>PKT_FootHeight_W1_H1_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_FootHeight_W1_H2_Leading</t>
-  </si>
-  <si>
-    <t>PKT_FootHeight_W1_H2_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_FootHeight_W1_H3_Leading</t>
-  </si>
-  <si>
-    <t>PKT_FootHeight_W1_H3_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_FootHeight_W2_H1_Leading</t>
-  </si>
-  <si>
-    <t>PKT_FootHeight_W2_H1_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_FootHeight_W2_H2_Leading</t>
-  </si>
-  <si>
-    <t>PKT_FootHeight_W2_H2_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_FootHeight_W2_H3_Leading</t>
-  </si>
-  <si>
-    <t>PKT_FootHeight_W2_H3_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_FootHeight_Level_Walk</t>
-  </si>
-  <si>
-    <t>PKT_Foot_W1_H1_Leading</t>
-  </si>
-  <si>
-    <t>PKT_Foot_W1_H1_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_Foot_W1_H2_Leading</t>
-  </si>
-  <si>
-    <t>PKT_Foot_W1_H2_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_Foot_W1_H3_Leading</t>
-  </si>
-  <si>
-    <t>PKT_Foot_W1_H3_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_Foot_W2_H1_Leading</t>
-  </si>
-  <si>
-    <t>PKT_Foot_W2_H1_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_Foot_W2_H2_Leading</t>
-  </si>
-  <si>
-    <t>PKT_Foot_W2_H2_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_Foot_W2_H3_Leading</t>
-  </si>
-  <si>
-    <t>PKT_Foot_W2_H3_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_Foot_Level_Walk</t>
-  </si>
-  <si>
-    <t>PKT_Shank_W1_H1_Leading</t>
-  </si>
-  <si>
-    <t>PKT_Shank_W1_H1_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_Shank_W1_H2_Leading</t>
-  </si>
-  <si>
-    <t>PKT_Shank_W1_H2_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_Shank_W1_H3_Leading</t>
-  </si>
-  <si>
-    <t>PKT_Shank_W1_H3_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_Shank_W2_H1_Leading</t>
-  </si>
-  <si>
-    <t>PKT_Shank_W2_H1_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_Shank_W2_H2_Leading</t>
-  </si>
-  <si>
-    <t>PKT_Shank_W2_H2_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_Shank_W2_H3_Leading</t>
-  </si>
-  <si>
-    <t>PKT_Shank_W2_H3_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_Shank_Level_Walk</t>
-  </si>
-  <si>
-    <t>PKT_Thigh_W1_H1_Leading</t>
-  </si>
-  <si>
-    <t>PKT_Thigh_W1_H1_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_Thigh_W1_H2_Leading</t>
-  </si>
-  <si>
-    <t>PKT_Thigh_W1_H2_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_Thigh_W1_H3_Leading</t>
-  </si>
-  <si>
-    <t>PKT_Thigh_W1_H3_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_Thigh_W2_H1_Leading</t>
-  </si>
-  <si>
-    <t>PKT_Thigh_W2_H1_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_Thigh_W2_H2_Leading</t>
-  </si>
-  <si>
-    <t>PKT_Thigh_W2_H2_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_Thigh_W2_H3_Leading</t>
-  </si>
-  <si>
-    <t>PKT_Thigh_W2_H3_Trailing</t>
-  </si>
-  <si>
-    <t>PKT_Thigh_Level_Walk</t>
+    <t>clearance_min_W1_H1_Leading</t>
+  </si>
+  <si>
+    <t>clearance_min_W1_H1_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_min_W1_H2_Leading</t>
+  </si>
+  <si>
+    <t>clearance_min_W1_H2_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_min_W1_H3_Leading</t>
+  </si>
+  <si>
+    <t>clearance_min_W1_H3_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_min_W2_H1_Leading</t>
+  </si>
+  <si>
+    <t>clearance_min_W2_H1_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_min_W2_H2_Leading</t>
+  </si>
+  <si>
+    <t>clearance_min_W2_H2_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_min_W2_H3_Leading</t>
+  </si>
+  <si>
+    <t>clearance_min_W2_H3_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_takeoff_W1_H1_Leading</t>
+  </si>
+  <si>
+    <t>clearance_takeoff_W1_H1_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_takeoff_W1_H2_Leading</t>
+  </si>
+  <si>
+    <t>clearance_takeoff_W1_H2_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_takeoff_W1_H3_Leading</t>
+  </si>
+  <si>
+    <t>clearance_takeoff_W1_H3_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_takeoff_W2_H1_Leading</t>
+  </si>
+  <si>
+    <t>clearance_takeoff_W2_H1_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_takeoff_W2_H2_Leading</t>
+  </si>
+  <si>
+    <t>clearance_takeoff_W2_H2_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_takeoff_W2_H3_Leading</t>
+  </si>
+  <si>
+    <t>clearance_takeoff_W2_H3_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_landing_W1_H1_Leading</t>
+  </si>
+  <si>
+    <t>clearance_landing_W1_H1_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_landing_W1_H2_Leading</t>
+  </si>
+  <si>
+    <t>clearance_landing_W1_H2_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_landing_W1_H3_Leading</t>
+  </si>
+  <si>
+    <t>clearance_landing_W1_H3_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_landing_W2_H1_Leading</t>
+  </si>
+  <si>
+    <t>clearance_landing_W2_H1_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_landing_W2_H2_Leading</t>
+  </si>
+  <si>
+    <t>clearance_landing_W2_H2_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_landing_W2_H3_Leading</t>
+  </si>
+  <si>
+    <t>clearance_landing_W2_H3_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_stride_W1_H1_Leading</t>
+  </si>
+  <si>
+    <t>clearance_stride_W1_H1_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_stride_W1_H2_Leading</t>
+  </si>
+  <si>
+    <t>clearance_stride_W1_H2_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_stride_W1_H3_Leading</t>
+  </si>
+  <si>
+    <t>clearance_stride_W1_H3_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_stride_W2_H1_Leading</t>
+  </si>
+  <si>
+    <t>clearance_stride_W2_H1_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_stride_W2_H2_Leading</t>
+  </si>
+  <si>
+    <t>clearance_stride_W2_H2_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_stride_W2_H3_Leading</t>
+  </si>
+  <si>
+    <t>clearance_stride_W2_H3_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_stride_Level_Walk</t>
+  </si>
+  <si>
+    <t>clearance_cadence_W1_H1_Leading</t>
+  </si>
+  <si>
+    <t>clearance_cadence_W1_H1_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_cadence_W1_H2_Leading</t>
+  </si>
+  <si>
+    <t>clearance_cadence_W1_H2_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_cadence_W1_H3_Leading</t>
+  </si>
+  <si>
+    <t>clearance_cadence_W1_H3_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_cadence_W2_H1_Leading</t>
+  </si>
+  <si>
+    <t>clearance_cadence_W2_H1_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_cadence_W2_H2_Leading</t>
+  </si>
+  <si>
+    <t>clearance_cadence_W2_H2_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_cadence_W2_H3_Leading</t>
+  </si>
+  <si>
+    <t>clearance_cadence_W2_H3_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_cadence_Level_Walk</t>
+  </si>
+  <si>
+    <t>clearance_speed_W1_H1_Leading</t>
+  </si>
+  <si>
+    <t>clearance_speed_W1_H1_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_speed_W1_H2_Leading</t>
+  </si>
+  <si>
+    <t>clearance_speed_W1_H2_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_speed_W1_H3_Leading</t>
+  </si>
+  <si>
+    <t>clearance_speed_W1_H3_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_speed_W2_H1_Leading</t>
+  </si>
+  <si>
+    <t>clearance_speed_W2_H1_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_speed_W2_H2_Leading</t>
+  </si>
+  <si>
+    <t>clearance_speed_W2_H2_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_speed_W2_H3_Leading</t>
+  </si>
+  <si>
+    <t>clearance_speed_W2_H3_Trailing</t>
+  </si>
+  <si>
+    <t>clearance_speed_Level_Walk</t>
+  </si>
+  <si>
+    <t>joints_ankle_rom_W1_H1_Leading</t>
+  </si>
+  <si>
+    <t>joints_ankle_rom_W1_H1_Trailing</t>
+  </si>
+  <si>
+    <t>joints_ankle_rom_W1_H2_Leading</t>
+  </si>
+  <si>
+    <t>joints_ankle_rom_W1_H2_Trailing</t>
+  </si>
+  <si>
+    <t>joints_ankle_rom_W1_H3_Leading</t>
+  </si>
+  <si>
+    <t>joints_ankle_rom_W1_H3_Trailing</t>
+  </si>
+  <si>
+    <t>joints_ankle_rom_W2_H1_Leading</t>
+  </si>
+  <si>
+    <t>joints_ankle_rom_W2_H1_Trailing</t>
+  </si>
+  <si>
+    <t>joints_ankle_rom_W2_H2_Leading</t>
+  </si>
+  <si>
+    <t>joints_ankle_rom_W2_H2_Trailing</t>
+  </si>
+  <si>
+    <t>joints_ankle_rom_W2_H3_Leading</t>
+  </si>
+  <si>
+    <t>joints_ankle_rom_W2_H3_Trailing</t>
+  </si>
+  <si>
+    <t>joints_ankle_rom_Level_Walk</t>
+  </si>
+  <si>
+    <t>joints_hip_max_W1_H1_Leading</t>
+  </si>
+  <si>
+    <t>joints_hip_max_W1_H1_Trailing</t>
+  </si>
+  <si>
+    <t>joints_hip_max_W1_H2_Leading</t>
+  </si>
+  <si>
+    <t>joints_hip_max_W1_H2_Trailing</t>
+  </si>
+  <si>
+    <t>joints_hip_max_W1_H3_Leading</t>
+  </si>
+  <si>
+    <t>joints_hip_max_W1_H3_Trailing</t>
+  </si>
+  <si>
+    <t>joints_hip_max_W2_H1_Leading</t>
+  </si>
+  <si>
+    <t>joints_hip_max_W2_H1_Trailing</t>
+  </si>
+  <si>
+    <t>joints_hip_max_W2_H2_Leading</t>
+  </si>
+  <si>
+    <t>joints_hip_max_W2_H2_Trailing</t>
+  </si>
+  <si>
+    <t>joints_hip_max_W2_H3_Leading</t>
+  </si>
+  <si>
+    <t>joints_hip_max_W2_H3_Trailing</t>
+  </si>
+  <si>
+    <t>joints_hip_max_Level_Walk</t>
+  </si>
+  <si>
+    <t>joints_knee_max_W1_H1_Leading</t>
+  </si>
+  <si>
+    <t>joints_knee_max_W1_H1_Trailing</t>
+  </si>
+  <si>
+    <t>joints_knee_max_W1_H2_Leading</t>
+  </si>
+  <si>
+    <t>joints_knee_max_W1_H2_Trailing</t>
+  </si>
+  <si>
+    <t>joints_knee_max_W1_H3_Leading</t>
+  </si>
+  <si>
+    <t>joints_knee_max_W1_H3_Trailing</t>
+  </si>
+  <si>
+    <t>joints_knee_max_W2_H1_Leading</t>
+  </si>
+  <si>
+    <t>joints_knee_max_W2_H1_Trailing</t>
+  </si>
+  <si>
+    <t>joints_knee_max_W2_H2_Leading</t>
+  </si>
+  <si>
+    <t>joints_knee_max_W2_H2_Trailing</t>
+  </si>
+  <si>
+    <t>joints_knee_max_W2_H3_Leading</t>
+  </si>
+  <si>
+    <t>joints_knee_max_W2_H3_Trailing</t>
+  </si>
+  <si>
+    <t>joints_knee_max_Level_Walk</t>
+  </si>
+  <si>
+    <t>joints_ankle_max_W1_H1_Leading</t>
+  </si>
+  <si>
+    <t>joints_ankle_max_W1_H1_Trailing</t>
+  </si>
+  <si>
+    <t>joints_ankle_max_W1_H2_Leading</t>
+  </si>
+  <si>
+    <t>joints_ankle_max_W1_H2_Trailing</t>
+  </si>
+  <si>
+    <t>joints_ankle_max_W1_H3_Leading</t>
+  </si>
+  <si>
+    <t>joints_ankle_max_W1_H3_Trailing</t>
+  </si>
+  <si>
+    <t>joints_ankle_max_W2_H1_Leading</t>
+  </si>
+  <si>
+    <t>joints_ankle_max_W2_H1_Trailing</t>
+  </si>
+  <si>
+    <t>joints_ankle_max_W2_H2_Leading</t>
+  </si>
+  <si>
+    <t>joints_ankle_max_W2_H2_Trailing</t>
+  </si>
+  <si>
+    <t>joints_ankle_max_W2_H3_Leading</t>
+  </si>
+  <si>
+    <t>joints_ankle_max_W2_H3_Trailing</t>
+  </si>
+  <si>
+    <t>joints_ankle_max_Level_Walk</t>
+  </si>
+  <si>
+    <t>joints_hip_min_W1_H1_Leading</t>
+  </si>
+  <si>
+    <t>joints_hip_min_W1_H1_Trailing</t>
+  </si>
+  <si>
+    <t>joints_hip_min_W1_H2_Leading</t>
+  </si>
+  <si>
+    <t>joints_hip_min_W1_H2_Trailing</t>
+  </si>
+  <si>
+    <t>joints_hip_min_W1_H3_Leading</t>
+  </si>
+  <si>
+    <t>joints_hip_min_W1_H3_Trailing</t>
+  </si>
+  <si>
+    <t>joints_hip_min_W2_H1_Leading</t>
+  </si>
+  <si>
+    <t>joints_hip_min_W2_H1_Trailing</t>
+  </si>
+  <si>
+    <t>joints_hip_min_W2_H2_Leading</t>
+  </si>
+  <si>
+    <t>joints_hip_min_W2_H2_Trailing</t>
+  </si>
+  <si>
+    <t>joints_hip_min_W2_H3_Leading</t>
+  </si>
+  <si>
+    <t>joints_hip_min_W2_H3_Trailing</t>
+  </si>
+  <si>
+    <t>joints_hip_min_Level_Walk</t>
+  </si>
+  <si>
+    <t>joints_knee_min_W1_H1_Leading</t>
+  </si>
+  <si>
+    <t>joints_knee_min_W1_H1_Trailing</t>
+  </si>
+  <si>
+    <t>joints_knee_min_W1_H2_Leading</t>
+  </si>
+  <si>
+    <t>joints_knee_min_W1_H2_Trailing</t>
+  </si>
+  <si>
+    <t>joints_knee_min_W1_H3_Leading</t>
+  </si>
+  <si>
+    <t>joints_knee_min_W1_H3_Trailing</t>
+  </si>
+  <si>
+    <t>joints_knee_min_W2_H1_Leading</t>
+  </si>
+  <si>
+    <t>joints_knee_min_W2_H1_Trailing</t>
+  </si>
+  <si>
+    <t>joints_knee_min_W2_H2_Leading</t>
+  </si>
+  <si>
+    <t>joints_knee_min_W2_H2_Trailing</t>
+  </si>
+  <si>
+    <t>joints_knee_min_W2_H3_Leading</t>
+  </si>
+  <si>
+    <t>joints_knee_min_W2_H3_Trailing</t>
+  </si>
+  <si>
+    <t>joints_knee_min_Level_Walk</t>
+  </si>
+  <si>
+    <t>joints_ankle_min_W1_H1_Leading</t>
+  </si>
+  <si>
+    <t>joints_ankle_min_W1_H1_Trailing</t>
+  </si>
+  <si>
+    <t>joints_ankle_min_W1_H2_Leading</t>
+  </si>
+  <si>
+    <t>joints_ankle_min_W1_H2_Trailing</t>
+  </si>
+  <si>
+    <t>joints_ankle_min_W1_H3_Leading</t>
+  </si>
+  <si>
+    <t>joints_ankle_min_W1_H3_Trailing</t>
+  </si>
+  <si>
+    <t>joints_ankle_min_W2_H1_Leading</t>
+  </si>
+  <si>
+    <t>joints_ankle_min_W2_H1_Trailing</t>
+  </si>
+  <si>
+    <t>joints_ankle_min_W2_H2_Leading</t>
+  </si>
+  <si>
+    <t>joints_ankle_min_W2_H2_Trailing</t>
+  </si>
+  <si>
+    <t>joints_ankle_min_W2_H3_Leading</t>
+  </si>
+  <si>
+    <t>joints_ankle_min_W2_H3_Trailing</t>
+  </si>
+  <si>
+    <t>joints_ankle_min_Level_Walk</t>
+  </si>
+  <si>
+    <t>joints_hip_flexion_W1_H1_Leading</t>
+  </si>
+  <si>
+    <t>joints_hip_flexion_W1_H1_Trailing</t>
+  </si>
+  <si>
+    <t>joints_hip_flexion_W1_H2_Leading</t>
+  </si>
+  <si>
+    <t>joints_hip_flexion_W1_H2_Trailing</t>
+  </si>
+  <si>
+    <t>joints_hip_flexion_W1_H3_Leading</t>
+  </si>
+  <si>
+    <t>joints_hip_flexion_W1_H3_Trailing</t>
+  </si>
+  <si>
+    <t>joints_hip_flexion_W2_H1_Leading</t>
+  </si>
+  <si>
+    <t>joints_hip_flexion_W2_H1_Trailing</t>
+  </si>
+  <si>
+    <t>joints_hip_flexion_W2_H2_Leading</t>
+  </si>
+  <si>
+    <t>joints_hip_flexion_W2_H2_Trailing</t>
+  </si>
+  <si>
+    <t>joints_hip_flexion_W2_H3_Leading</t>
+  </si>
+  <si>
+    <t>joints_hip_flexion_W2_H3_Trailing</t>
+  </si>
+  <si>
+    <t>joints_hip_flexion_Level_Walk</t>
+  </si>
+  <si>
+    <t>joints_knee_flexion_W1_H1_Leading</t>
+  </si>
+  <si>
+    <t>joints_knee_flexion_W1_H1_Trailing</t>
+  </si>
+  <si>
+    <t>joints_knee_flexion_W1_H2_Leading</t>
+  </si>
+  <si>
+    <t>joints_knee_flexion_W1_H2_Trailing</t>
+  </si>
+  <si>
+    <t>joints_knee_flexion_W1_H3_Leading</t>
+  </si>
+  <si>
+    <t>joints_knee_flexion_W1_H3_Trailing</t>
+  </si>
+  <si>
+    <t>joints_knee_flexion_W2_H1_Leading</t>
+  </si>
+  <si>
+    <t>joints_knee_flexion_W2_H1_Trailing</t>
+  </si>
+  <si>
+    <t>joints_knee_flexion_W2_H2_Leading</t>
+  </si>
+  <si>
+    <t>joints_knee_flexion_W2_H2_Trailing</t>
+  </si>
+  <si>
+    <t>joints_knee_flexion_W2_H3_Leading</t>
+  </si>
+  <si>
+    <t>joints_knee_flexion_W2_H3_Trailing</t>
+  </si>
+  <si>
+    <t>joints_knee_flexion_Level_Walk</t>
+  </si>
+  <si>
+    <t>joints_ankle_plantar_W1_H1_Leading</t>
+  </si>
+  <si>
+    <t>joints_ankle_plantar_W1_H1_Trailing</t>
+  </si>
+  <si>
+    <t>joints_ankle_plantar_W1_H2_Leading</t>
+  </si>
+  <si>
+    <t>joints_ankle_plantar_W1_H2_Trailing</t>
+  </si>
+  <si>
+    <t>joints_ankle_plantar_W1_H3_Leading</t>
+  </si>
+  <si>
+    <t>joints_ankle_plantar_W1_H3_Trailing</t>
+  </si>
+  <si>
+    <t>joints_ankle_plantar_W2_H1_Leading</t>
+  </si>
+  <si>
+    <t>joints_ankle_plantar_W2_H1_Trailing</t>
+  </si>
+  <si>
+    <t>joints_ankle_plantar_W2_H2_Leading</t>
+  </si>
+  <si>
+    <t>joints_ankle_plantar_W2_H2_Trailing</t>
+  </si>
+  <si>
+    <t>joints_ankle_plantar_W2_H3_Leading</t>
+  </si>
+  <si>
+    <t>joints_ankle_plantar_W2_H3_Trailing</t>
+  </si>
+  <si>
+    <t>joints_ankle_plantar_Level_Walk</t>
+  </si>
+  <si>
+    <t>joints_ankle_dorsi_W1_H1_Leading</t>
+  </si>
+  <si>
+    <t>joints_ankle_dorsi_W1_H1_Trailing</t>
+  </si>
+  <si>
+    <t>joints_ankle_dorsi_W1_H2_Leading</t>
+  </si>
+  <si>
+    <t>joints_ankle_dorsi_W1_H2_Trailing</t>
+  </si>
+  <si>
+    <t>joints_ankle_dorsi_W1_H3_Leading</t>
+  </si>
+  <si>
+    <t>joints_ankle_dorsi_W1_H3_Trailing</t>
+  </si>
+  <si>
+    <t>joints_ankle_dorsi_W2_H1_Leading</t>
+  </si>
+  <si>
+    <t>joints_ankle_dorsi_W2_H1_Trailing</t>
+  </si>
+  <si>
+    <t>joints_ankle_dorsi_W2_H2_Leading</t>
+  </si>
+  <si>
+    <t>joints_ankle_dorsi_W2_H2_Trailing</t>
+  </si>
+  <si>
+    <t>joints_ankle_dorsi_W2_H3_Leading</t>
+  </si>
+  <si>
+    <t>joints_ankle_dorsi_W2_H3_Trailing</t>
+  </si>
+  <si>
+    <t>joints_ankle_dorsi_Level_Walk</t>
+  </si>
+  <si>
+    <t>segments_foot_rom_W1_H1_Leading</t>
+  </si>
+  <si>
+    <t>segments_foot_rom_W1_H1_Trailing</t>
+  </si>
+  <si>
+    <t>segments_foot_rom_W1_H2_Leading</t>
+  </si>
+  <si>
+    <t>segments_foot_rom_W1_H2_Trailing</t>
+  </si>
+  <si>
+    <t>segments_foot_rom_W1_H3_Leading</t>
+  </si>
+  <si>
+    <t>segments_foot_rom_W1_H3_Trailing</t>
+  </si>
+  <si>
+    <t>segments_foot_rom_W2_H1_Leading</t>
+  </si>
+  <si>
+    <t>segments_foot_rom_W2_H1_Trailing</t>
+  </si>
+  <si>
+    <t>segments_foot_rom_W2_H2_Leading</t>
+  </si>
+  <si>
+    <t>segments_foot_rom_W2_H2_Trailing</t>
+  </si>
+  <si>
+    <t>segments_foot_rom_W2_H3_Leading</t>
+  </si>
+  <si>
+    <t>segments_foot_rom_W2_H3_Trailing</t>
+  </si>
+  <si>
+    <t>segments_foot_rom_Level_Walk</t>
+  </si>
+  <si>
+    <t>segments_thigh_forward_W1_H1_Leading</t>
+  </si>
+  <si>
+    <t>segments_thigh_forward_W1_H1_Trailing</t>
+  </si>
+  <si>
+    <t>segments_thigh_forward_W1_H2_Leading</t>
+  </si>
+  <si>
+    <t>segments_thigh_forward_W1_H2_Trailing</t>
+  </si>
+  <si>
+    <t>segments_thigh_forward_W1_H3_Leading</t>
+  </si>
+  <si>
+    <t>segments_thigh_forward_W1_H3_Trailing</t>
+  </si>
+  <si>
+    <t>segments_thigh_forward_W2_H1_Leading</t>
+  </si>
+  <si>
+    <t>segments_thigh_forward_W2_H1_Trailing</t>
+  </si>
+  <si>
+    <t>segments_thigh_forward_W2_H2_Leading</t>
+  </si>
+  <si>
+    <t>segments_thigh_forward_W2_H2_Trailing</t>
+  </si>
+  <si>
+    <t>segments_thigh_forward_W2_H3_Leading</t>
+  </si>
+  <si>
+    <t>segments_thigh_forward_W2_H3_Trailing</t>
+  </si>
+  <si>
+    <t>segments_thigh_forward_Level_Walk</t>
+  </si>
+  <si>
+    <t>segments_shank_backward_W1_H1_Leading</t>
+  </si>
+  <si>
+    <t>segments_shank_backward_W1_H1_Trailing</t>
+  </si>
+  <si>
+    <t>segments_shank_backward_W1_H2_Leading</t>
+  </si>
+  <si>
+    <t>segments_shank_backward_W1_H2_Trailing</t>
+  </si>
+  <si>
+    <t>segments_shank_backward_W1_H3_Leading</t>
+  </si>
+  <si>
+    <t>segments_shank_backward_W1_H3_Trailing</t>
+  </si>
+  <si>
+    <t>segments_shank_backward_W2_H1_Leading</t>
+  </si>
+  <si>
+    <t>segments_shank_backward_W2_H1_Trailing</t>
+  </si>
+  <si>
+    <t>segments_shank_backward_W2_H2_Leading</t>
+  </si>
+  <si>
+    <t>segments_shank_backward_W2_H2_Trailing</t>
+  </si>
+  <si>
+    <t>segments_shank_backward_W2_H3_Leading</t>
+  </si>
+  <si>
+    <t>segments_shank_backward_W2_H3_Trailing</t>
+  </si>
+  <si>
+    <t>segments_shank_backward_Level_Walk</t>
+  </si>
+  <si>
+    <t>segments_shank_forward_W1_H1_Leading</t>
+  </si>
+  <si>
+    <t>segments_shank_forward_W1_H1_Trailing</t>
+  </si>
+  <si>
+    <t>segments_shank_forward_W1_H2_Leading</t>
+  </si>
+  <si>
+    <t>segments_shank_forward_W1_H2_Trailing</t>
+  </si>
+  <si>
+    <t>segments_shank_forward_W1_H3_Leading</t>
+  </si>
+  <si>
+    <t>segments_shank_forward_W1_H3_Trailing</t>
+  </si>
+  <si>
+    <t>segments_shank_forward_W2_H1_Leading</t>
+  </si>
+  <si>
+    <t>segments_shank_forward_W2_H1_Trailing</t>
+  </si>
+  <si>
+    <t>segments_shank_forward_W2_H2_Leading</t>
+  </si>
+  <si>
+    <t>segments_shank_forward_W2_H2_Trailing</t>
+  </si>
+  <si>
+    <t>segments_shank_forward_W2_H3_Leading</t>
+  </si>
+  <si>
+    <t>segments_shank_forward_W2_H3_Trailing</t>
+  </si>
+  <si>
+    <t>segments_shank_forward_Level_Walk</t>
+  </si>
+  <si>
+    <t>segments_foot_toedown_W1_H1_Leading</t>
+  </si>
+  <si>
+    <t>segments_foot_toedown_W1_H1_Trailing</t>
+  </si>
+  <si>
+    <t>segments_foot_toedown_W1_H2_Leading</t>
+  </si>
+  <si>
+    <t>segments_foot_toedown_W1_H2_Trailing</t>
+  </si>
+  <si>
+    <t>segments_foot_toedown_W1_H3_Leading</t>
+  </si>
+  <si>
+    <t>segments_foot_toedown_W1_H3_Trailing</t>
+  </si>
+  <si>
+    <t>segments_foot_toedown_W2_H1_Leading</t>
+  </si>
+  <si>
+    <t>segments_foot_toedown_W2_H1_Trailing</t>
+  </si>
+  <si>
+    <t>segments_foot_toedown_W2_H2_Leading</t>
+  </si>
+  <si>
+    <t>segments_foot_toedown_W2_H2_Trailing</t>
+  </si>
+  <si>
+    <t>segments_foot_toedown_W2_H3_Leading</t>
+  </si>
+  <si>
+    <t>segments_foot_toedown_W2_H3_Trailing</t>
+  </si>
+  <si>
+    <t>segments_foot_toedown_Level_Walk</t>
+  </si>
+  <si>
+    <t>segments_foot_toeup_W1_H1_Leading</t>
+  </si>
+  <si>
+    <t>segments_foot_toeup_W1_H1_Trailing</t>
+  </si>
+  <si>
+    <t>segments_foot_toeup_W1_H2_Leading</t>
+  </si>
+  <si>
+    <t>segments_foot_toeup_W1_H2_Trailing</t>
+  </si>
+  <si>
+    <t>segments_foot_toeup_W1_H3_Leading</t>
+  </si>
+  <si>
+    <t>segments_foot_toeup_W1_H3_Trailing</t>
+  </si>
+  <si>
+    <t>segments_foot_toeup_W2_H1_Leading</t>
+  </si>
+  <si>
+    <t>segments_foot_toeup_W2_H1_Trailing</t>
+  </si>
+  <si>
+    <t>segments_foot_toeup_W2_H2_Leading</t>
+  </si>
+  <si>
+    <t>segments_foot_toeup_W2_H2_Trailing</t>
+  </si>
+  <si>
+    <t>segments_foot_toeup_W2_H3_Leading</t>
+  </si>
+  <si>
+    <t>segments_foot_toeup_W2_H3_Trailing</t>
+  </si>
+  <si>
+    <t>segments_foot_toeup_Level_Walk</t>
+  </si>
+  <si>
+    <t>timings_hip_W1_H1_Leading</t>
+  </si>
+  <si>
+    <t>timings_hip_W1_H1_Trailing</t>
+  </si>
+  <si>
+    <t>timings_hip_W1_H2_Leading</t>
+  </si>
+  <si>
+    <t>timings_hip_W1_H2_Trailing</t>
+  </si>
+  <si>
+    <t>timings_hip_W1_H3_Leading</t>
+  </si>
+  <si>
+    <t>timings_hip_W1_H3_Trailing</t>
+  </si>
+  <si>
+    <t>timings_hip_W2_H1_Leading</t>
+  </si>
+  <si>
+    <t>timings_hip_W2_H1_Trailing</t>
+  </si>
+  <si>
+    <t>timings_hip_W2_H2_Leading</t>
+  </si>
+  <si>
+    <t>timings_hip_W2_H2_Trailing</t>
+  </si>
+  <si>
+    <t>timings_hip_W2_H3_Leading</t>
+  </si>
+  <si>
+    <t>timings_hip_W2_H3_Trailing</t>
+  </si>
+  <si>
+    <t>timings_hip_Level_Walk</t>
+  </si>
+  <si>
+    <t>timings_knee_W1_H1_Leading</t>
+  </si>
+  <si>
+    <t>timings_knee_W1_H1_Trailing</t>
+  </si>
+  <si>
+    <t>timings_knee_W1_H2_Leading</t>
+  </si>
+  <si>
+    <t>timings_knee_W1_H2_Trailing</t>
+  </si>
+  <si>
+    <t>timings_knee_W1_H3_Leading</t>
+  </si>
+  <si>
+    <t>timings_knee_W1_H3_Trailing</t>
+  </si>
+  <si>
+    <t>timings_knee_W2_H1_Leading</t>
+  </si>
+  <si>
+    <t>timings_knee_W2_H1_Trailing</t>
+  </si>
+  <si>
+    <t>timings_knee_W2_H2_Leading</t>
+  </si>
+  <si>
+    <t>timings_knee_W2_H2_Trailing</t>
+  </si>
+  <si>
+    <t>timings_knee_W2_H3_Leading</t>
+  </si>
+  <si>
+    <t>timings_knee_W2_H3_Trailing</t>
+  </si>
+  <si>
+    <t>timings_knee_Level_Walk</t>
+  </si>
+  <si>
+    <t>timings_ankle_W1_H1_Leading</t>
+  </si>
+  <si>
+    <t>timings_ankle_W1_H1_Trailing</t>
+  </si>
+  <si>
+    <t>timings_ankle_W1_H2_Leading</t>
+  </si>
+  <si>
+    <t>timings_ankle_W1_H2_Trailing</t>
+  </si>
+  <si>
+    <t>timings_ankle_W1_H3_Leading</t>
+  </si>
+  <si>
+    <t>timings_ankle_W1_H3_Trailing</t>
+  </si>
+  <si>
+    <t>timings_ankle_W2_H1_Leading</t>
+  </si>
+  <si>
+    <t>timings_ankle_W2_H1_Trailing</t>
+  </si>
+  <si>
+    <t>timings_ankle_W2_H2_Leading</t>
+  </si>
+  <si>
+    <t>timings_ankle_W2_H2_Trailing</t>
+  </si>
+  <si>
+    <t>timings_ankle_W2_H3_Leading</t>
+  </si>
+  <si>
+    <t>timings_ankle_W2_H3_Trailing</t>
+  </si>
+  <si>
+    <t>timings_ankle_Level_Walk</t>
+  </si>
+  <si>
+    <t>timings_footheight_W1_H1_Leading</t>
+  </si>
+  <si>
+    <t>timings_footheight_W1_H1_Trailing</t>
+  </si>
+  <si>
+    <t>timings_footheight_W1_H2_Leading</t>
+  </si>
+  <si>
+    <t>timings_footheight_W1_H2_Trailing</t>
+  </si>
+  <si>
+    <t>timings_footheight_W1_H3_Leading</t>
+  </si>
+  <si>
+    <t>timings_footheight_W1_H3_Trailing</t>
+  </si>
+  <si>
+    <t>timings_footheight_W2_H1_Leading</t>
+  </si>
+  <si>
+    <t>timings_footheight_W2_H1_Trailing</t>
+  </si>
+  <si>
+    <t>timings_footheight_W2_H2_Leading</t>
+  </si>
+  <si>
+    <t>timings_footheight_W2_H2_Trailing</t>
+  </si>
+  <si>
+    <t>timings_footheight_W2_H3_Leading</t>
+  </si>
+  <si>
+    <t>timings_footheight_W2_H3_Trailing</t>
+  </si>
+  <si>
+    <t>timings_footheight_Level_Walk</t>
+  </si>
+  <si>
+    <t>timings_foot_W1_H1_Leading</t>
+  </si>
+  <si>
+    <t>timings_foot_W1_H1_Trailing</t>
+  </si>
+  <si>
+    <t>timings_foot_W1_H2_Leading</t>
+  </si>
+  <si>
+    <t>timings_foot_W1_H2_Trailing</t>
+  </si>
+  <si>
+    <t>timings_foot_W1_H3_Leading</t>
+  </si>
+  <si>
+    <t>timings_foot_W1_H3_Trailing</t>
+  </si>
+  <si>
+    <t>timings_foot_W2_H1_Leading</t>
+  </si>
+  <si>
+    <t>timings_foot_W2_H1_Trailing</t>
+  </si>
+  <si>
+    <t>timings_foot_W2_H2_Leading</t>
+  </si>
+  <si>
+    <t>timings_foot_W2_H2_Trailing</t>
+  </si>
+  <si>
+    <t>timings_foot_W2_H3_Leading</t>
+  </si>
+  <si>
+    <t>timings_foot_W2_H3_Trailing</t>
+  </si>
+  <si>
+    <t>timings_foot_Level_Walk</t>
+  </si>
+  <si>
+    <t>timings_shank_W1_H1_Leading</t>
+  </si>
+  <si>
+    <t>timings_shank_W1_H1_Trailing</t>
+  </si>
+  <si>
+    <t>timings_shank_W1_H2_Leading</t>
+  </si>
+  <si>
+    <t>timings_shank_W1_H2_Trailing</t>
+  </si>
+  <si>
+    <t>timings_shank_W1_H3_Leading</t>
+  </si>
+  <si>
+    <t>timings_shank_W1_H3_Trailing</t>
+  </si>
+  <si>
+    <t>timings_shank_W2_H1_Leading</t>
+  </si>
+  <si>
+    <t>timings_shank_W2_H1_Trailing</t>
+  </si>
+  <si>
+    <t>timings_shank_W2_H2_Leading</t>
+  </si>
+  <si>
+    <t>timings_shank_W2_H2_Trailing</t>
+  </si>
+  <si>
+    <t>timings_shank_W2_H3_Leading</t>
+  </si>
+  <si>
+    <t>timings_shank_W2_H3_Trailing</t>
+  </si>
+  <si>
+    <t>timings_shank_Level_Walk</t>
+  </si>
+  <si>
+    <t>timings_thigh_W1_H1_Leading</t>
+  </si>
+  <si>
+    <t>timings_thigh_W1_H1_Trailing</t>
+  </si>
+  <si>
+    <t>timings_thigh_W1_H2_Leading</t>
+  </si>
+  <si>
+    <t>timings_thigh_W1_H2_Trailing</t>
+  </si>
+  <si>
+    <t>timings_thigh_W1_H3_Leading</t>
+  </si>
+  <si>
+    <t>timings_thigh_W1_H3_Trailing</t>
+  </si>
+  <si>
+    <t>timings_thigh_W2_H1_Leading</t>
+  </si>
+  <si>
+    <t>timings_thigh_W2_H1_Trailing</t>
+  </si>
+  <si>
+    <t>timings_thigh_W2_H2_Leading</t>
+  </si>
+  <si>
+    <t>timings_thigh_W2_H2_Trailing</t>
+  </si>
+  <si>
+    <t>timings_thigh_W2_H3_Leading</t>
+  </si>
+  <si>
+    <t>timings_thigh_W2_H3_Trailing</t>
+  </si>
+  <si>
+    <t>timings_thigh_Level_Walk</t>
   </si>
 </sst>
 </file>
@@ -1226,393 +1226,393 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.85546875" customWidth="true"/>
-    <col min="2" max="2" width="25.7109375" customWidth="true"/>
-    <col min="3" max="3" width="25.42578125" customWidth="true"/>
-    <col min="4" max="4" width="25.7109375" customWidth="true"/>
-    <col min="5" max="5" width="25.42578125" customWidth="true"/>
-    <col min="6" max="6" width="25.7109375" customWidth="true"/>
-    <col min="7" max="7" width="25.42578125" customWidth="true"/>
-    <col min="8" max="8" width="25.7109375" customWidth="true"/>
-    <col min="9" max="9" width="25.42578125" customWidth="true"/>
-    <col min="10" max="10" width="25.7109375" customWidth="true"/>
-    <col min="11" max="11" width="25.42578125" customWidth="true"/>
-    <col min="12" max="12" width="25.7109375" customWidth="true"/>
-    <col min="13" max="13" width="25.42578125" customWidth="true"/>
-    <col min="14" max="14" width="26" customWidth="true"/>
-    <col min="15" max="15" width="25.7109375" customWidth="true"/>
-    <col min="16" max="16" width="26" customWidth="true"/>
-    <col min="17" max="17" width="25.7109375" customWidth="true"/>
-    <col min="18" max="18" width="26" customWidth="true"/>
-    <col min="19" max="19" width="25.7109375" customWidth="true"/>
-    <col min="20" max="20" width="26" customWidth="true"/>
-    <col min="21" max="21" width="25.7109375" customWidth="true"/>
-    <col min="22" max="22" width="26" customWidth="true"/>
-    <col min="23" max="23" width="25.7109375" customWidth="true"/>
-    <col min="24" max="24" width="26" customWidth="true"/>
-    <col min="25" max="25" width="25.7109375" customWidth="true"/>
-    <col min="26" max="26" width="27.28515625" customWidth="true"/>
-    <col min="27" max="27" width="27" customWidth="true"/>
-    <col min="28" max="28" width="27.28515625" customWidth="true"/>
-    <col min="29" max="29" width="27" customWidth="true"/>
-    <col min="30" max="30" width="27.28515625" customWidth="true"/>
-    <col min="31" max="31" width="27" customWidth="true"/>
-    <col min="32" max="32" width="27.28515625" customWidth="true"/>
-    <col min="33" max="33" width="27" customWidth="true"/>
-    <col min="34" max="34" width="27.28515625" customWidth="true"/>
-    <col min="35" max="35" width="27" customWidth="true"/>
-    <col min="36" max="36" width="27.28515625" customWidth="true"/>
-    <col min="37" max="37" width="27" customWidth="true"/>
-    <col min="38" max="38" width="25.42578125" customWidth="true"/>
-    <col min="39" max="39" width="25.140625" customWidth="true"/>
-    <col min="40" max="40" width="25.42578125" customWidth="true"/>
-    <col min="41" max="41" width="25.140625" customWidth="true"/>
-    <col min="42" max="42" width="25.42578125" customWidth="true"/>
-    <col min="43" max="43" width="25.140625" customWidth="true"/>
-    <col min="44" max="44" width="25.42578125" customWidth="true"/>
-    <col min="45" max="45" width="25.140625" customWidth="true"/>
-    <col min="46" max="46" width="25.42578125" customWidth="true"/>
-    <col min="47" max="47" width="25.140625" customWidth="true"/>
-    <col min="48" max="48" width="25.42578125" customWidth="true"/>
-    <col min="49" max="49" width="25.140625" customWidth="true"/>
-    <col min="50" max="50" width="21.5703125" customWidth="true"/>
-    <col min="51" max="51" width="27.5703125" customWidth="true"/>
-    <col min="52" max="52" width="27.28515625" customWidth="true"/>
-    <col min="53" max="53" width="27.5703125" customWidth="true"/>
-    <col min="54" max="54" width="27.28515625" customWidth="true"/>
-    <col min="55" max="55" width="27.5703125" customWidth="true"/>
-    <col min="56" max="56" width="27.28515625" customWidth="true"/>
-    <col min="57" max="57" width="27.5703125" customWidth="true"/>
-    <col min="58" max="58" width="27.28515625" customWidth="true"/>
-    <col min="59" max="59" width="27.5703125" customWidth="true"/>
-    <col min="60" max="60" width="27.28515625" customWidth="true"/>
-    <col min="61" max="61" width="27.5703125" customWidth="true"/>
-    <col min="62" max="62" width="27.28515625" customWidth="true"/>
-    <col min="63" max="63" width="23.7109375" customWidth="true"/>
-    <col min="64" max="64" width="25.7109375" customWidth="true"/>
-    <col min="65" max="65" width="25.42578125" customWidth="true"/>
-    <col min="66" max="66" width="25.7109375" customWidth="true"/>
-    <col min="67" max="67" width="25.42578125" customWidth="true"/>
-    <col min="68" max="68" width="25.7109375" customWidth="true"/>
-    <col min="69" max="69" width="25.42578125" customWidth="true"/>
-    <col min="70" max="70" width="25.7109375" customWidth="true"/>
-    <col min="71" max="71" width="25.42578125" customWidth="true"/>
-    <col min="72" max="72" width="25.7109375" customWidth="true"/>
-    <col min="73" max="73" width="25.42578125" customWidth="true"/>
-    <col min="74" max="74" width="25.7109375" customWidth="true"/>
-    <col min="75" max="75" width="25.42578125" customWidth="true"/>
-    <col min="76" max="76" width="21.85546875" customWidth="true"/>
-    <col min="77" max="77" width="32.140625" customWidth="true"/>
-    <col min="78" max="78" width="31.85546875" customWidth="true"/>
-    <col min="79" max="79" width="32.140625" customWidth="true"/>
-    <col min="80" max="80" width="31.85546875" customWidth="true"/>
-    <col min="81" max="81" width="32.140625" customWidth="true"/>
-    <col min="82" max="82" width="31.85546875" customWidth="true"/>
-    <col min="83" max="83" width="32.140625" customWidth="true"/>
-    <col min="84" max="84" width="31.85546875" customWidth="true"/>
-    <col min="85" max="85" width="32.140625" customWidth="true"/>
-    <col min="86" max="86" width="31.85546875" customWidth="true"/>
-    <col min="87" max="87" width="32.140625" customWidth="true"/>
-    <col min="88" max="88" width="31.85546875" customWidth="true"/>
-    <col min="89" max="89" width="28.28515625" customWidth="true"/>
-    <col min="90" max="90" width="32.140625" customWidth="true"/>
-    <col min="91" max="91" width="31.85546875" customWidth="true"/>
-    <col min="92" max="92" width="32.140625" customWidth="true"/>
-    <col min="93" max="93" width="31.85546875" customWidth="true"/>
-    <col min="94" max="94" width="32.140625" customWidth="true"/>
-    <col min="95" max="95" width="31.85546875" customWidth="true"/>
-    <col min="96" max="96" width="32.140625" customWidth="true"/>
-    <col min="97" max="97" width="31.85546875" customWidth="true"/>
-    <col min="98" max="98" width="32.140625" customWidth="true"/>
-    <col min="99" max="99" width="31.85546875" customWidth="true"/>
-    <col min="100" max="100" width="32.140625" customWidth="true"/>
-    <col min="101" max="101" width="31.85546875" customWidth="true"/>
-    <col min="102" max="102" width="28.28515625" customWidth="true"/>
-    <col min="103" max="103" width="32.28515625" customWidth="true"/>
-    <col min="104" max="104" width="32" customWidth="true"/>
-    <col min="105" max="105" width="32.28515625" customWidth="true"/>
-    <col min="106" max="106" width="32" customWidth="true"/>
-    <col min="107" max="107" width="32.28515625" customWidth="true"/>
-    <col min="108" max="108" width="32" customWidth="true"/>
-    <col min="109" max="109" width="32.28515625" customWidth="true"/>
-    <col min="110" max="110" width="32" customWidth="true"/>
-    <col min="111" max="111" width="32.28515625" customWidth="true"/>
-    <col min="112" max="112" width="32" customWidth="true"/>
-    <col min="113" max="113" width="32.28515625" customWidth="true"/>
-    <col min="114" max="114" width="32" customWidth="true"/>
-    <col min="115" max="115" width="28.42578125" customWidth="true"/>
-    <col min="116" max="116" width="32.7109375" customWidth="true"/>
-    <col min="117" max="117" width="32.42578125" customWidth="true"/>
-    <col min="118" max="118" width="32.7109375" customWidth="true"/>
-    <col min="119" max="119" width="32.42578125" customWidth="true"/>
-    <col min="120" max="120" width="32.7109375" customWidth="true"/>
-    <col min="121" max="121" width="32.42578125" customWidth="true"/>
-    <col min="122" max="122" width="32.7109375" customWidth="true"/>
-    <col min="123" max="123" width="32.42578125" customWidth="true"/>
-    <col min="124" max="124" width="32.7109375" customWidth="true"/>
-    <col min="125" max="125" width="32.42578125" customWidth="true"/>
-    <col min="126" max="126" width="32.7109375" customWidth="true"/>
-    <col min="127" max="127" width="32.42578125" customWidth="true"/>
-    <col min="128" max="128" width="28.85546875" customWidth="true"/>
-    <col min="129" max="129" width="31.7109375" customWidth="true"/>
-    <col min="130" max="130" width="31.42578125" customWidth="true"/>
-    <col min="131" max="131" width="31.7109375" customWidth="true"/>
-    <col min="132" max="132" width="31.42578125" customWidth="true"/>
-    <col min="133" max="133" width="31.7109375" customWidth="true"/>
-    <col min="134" max="134" width="31.42578125" customWidth="true"/>
-    <col min="135" max="135" width="31.7109375" customWidth="true"/>
-    <col min="136" max="136" width="31.42578125" customWidth="true"/>
-    <col min="137" max="137" width="31.7109375" customWidth="true"/>
-    <col min="138" max="138" width="31.42578125" customWidth="true"/>
-    <col min="139" max="139" width="31.7109375" customWidth="true"/>
-    <col min="140" max="140" width="31.42578125" customWidth="true"/>
-    <col min="141" max="141" width="27.85546875" customWidth="true"/>
-    <col min="142" max="142" width="31.85546875" customWidth="true"/>
-    <col min="143" max="143" width="31.5703125" customWidth="true"/>
-    <col min="144" max="144" width="31.85546875" customWidth="true"/>
-    <col min="145" max="145" width="31.5703125" customWidth="true"/>
-    <col min="146" max="146" width="31.85546875" customWidth="true"/>
-    <col min="147" max="147" width="31.5703125" customWidth="true"/>
-    <col min="148" max="148" width="31.85546875" customWidth="true"/>
-    <col min="149" max="149" width="31.5703125" customWidth="true"/>
-    <col min="150" max="150" width="31.85546875" customWidth="true"/>
-    <col min="151" max="151" width="31.5703125" customWidth="true"/>
-    <col min="152" max="152" width="31.85546875" customWidth="true"/>
-    <col min="153" max="153" width="31.5703125" customWidth="true"/>
-    <col min="154" max="154" width="28" customWidth="true"/>
-    <col min="155" max="155" width="32.28515625" customWidth="true"/>
-    <col min="156" max="156" width="32" customWidth="true"/>
-    <col min="157" max="157" width="32.28515625" customWidth="true"/>
-    <col min="158" max="158" width="32" customWidth="true"/>
-    <col min="159" max="159" width="32.28515625" customWidth="true"/>
-    <col min="160" max="160" width="32" customWidth="true"/>
-    <col min="161" max="161" width="32.28515625" customWidth="true"/>
-    <col min="162" max="162" width="32" customWidth="true"/>
-    <col min="163" max="163" width="32.28515625" customWidth="true"/>
-    <col min="164" max="164" width="32" customWidth="true"/>
-    <col min="165" max="165" width="32.28515625" customWidth="true"/>
-    <col min="166" max="166" width="32" customWidth="true"/>
-    <col min="167" max="167" width="28.42578125" customWidth="true"/>
-    <col min="168" max="168" width="26.42578125" customWidth="true"/>
-    <col min="169" max="169" width="26.140625" customWidth="true"/>
-    <col min="170" max="170" width="26.42578125" customWidth="true"/>
-    <col min="171" max="171" width="26.140625" customWidth="true"/>
-    <col min="172" max="172" width="26.42578125" customWidth="true"/>
-    <col min="173" max="173" width="26.140625" customWidth="true"/>
-    <col min="174" max="174" width="26.42578125" customWidth="true"/>
-    <col min="175" max="175" width="26.140625" customWidth="true"/>
-    <col min="176" max="176" width="26.42578125" customWidth="true"/>
-    <col min="177" max="177" width="26.140625" customWidth="true"/>
-    <col min="178" max="178" width="26.42578125" customWidth="true"/>
-    <col min="179" max="179" width="26.140625" customWidth="true"/>
-    <col min="180" max="180" width="22.5703125" customWidth="true"/>
-    <col min="181" max="181" width="30.85546875" customWidth="true"/>
-    <col min="182" max="182" width="30.5703125" customWidth="true"/>
-    <col min="183" max="183" width="30.85546875" customWidth="true"/>
-    <col min="184" max="184" width="30.5703125" customWidth="true"/>
-    <col min="185" max="185" width="30.85546875" customWidth="true"/>
-    <col min="186" max="186" width="30.5703125" customWidth="true"/>
-    <col min="187" max="187" width="30.85546875" customWidth="true"/>
-    <col min="188" max="188" width="30.5703125" customWidth="true"/>
-    <col min="189" max="189" width="30.85546875" customWidth="true"/>
-    <col min="190" max="190" width="30.5703125" customWidth="true"/>
-    <col min="191" max="191" width="30.85546875" customWidth="true"/>
-    <col min="192" max="192" width="30.5703125" customWidth="true"/>
-    <col min="193" max="193" width="27" customWidth="true"/>
-    <col min="194" max="194" width="32.42578125" customWidth="true"/>
-    <col min="195" max="195" width="32.140625" customWidth="true"/>
-    <col min="196" max="196" width="32.42578125" customWidth="true"/>
-    <col min="197" max="197" width="32.140625" customWidth="true"/>
-    <col min="198" max="198" width="32.42578125" customWidth="true"/>
-    <col min="199" max="199" width="32.140625" customWidth="true"/>
-    <col min="200" max="200" width="32.42578125" customWidth="true"/>
-    <col min="201" max="201" width="32.140625" customWidth="true"/>
-    <col min="202" max="202" width="32.42578125" customWidth="true"/>
-    <col min="203" max="203" width="32.140625" customWidth="true"/>
-    <col min="204" max="204" width="32.42578125" customWidth="true"/>
-    <col min="205" max="205" width="32.140625" customWidth="true"/>
-    <col min="206" max="206" width="28.5703125" customWidth="true"/>
-    <col min="207" max="207" width="29.140625" customWidth="true"/>
-    <col min="208" max="208" width="28.85546875" customWidth="true"/>
-    <col min="209" max="209" width="29.140625" customWidth="true"/>
-    <col min="210" max="210" width="28.85546875" customWidth="true"/>
-    <col min="211" max="211" width="29.140625" customWidth="true"/>
-    <col min="212" max="212" width="28.85546875" customWidth="true"/>
-    <col min="213" max="213" width="29.140625" customWidth="true"/>
-    <col min="214" max="214" width="28.85546875" customWidth="true"/>
-    <col min="215" max="215" width="29.140625" customWidth="true"/>
-    <col min="216" max="216" width="28.85546875" customWidth="true"/>
-    <col min="217" max="217" width="29.140625" customWidth="true"/>
-    <col min="218" max="218" width="28.85546875" customWidth="true"/>
-    <col min="219" max="219" width="25.28515625" customWidth="true"/>
-    <col min="220" max="220" width="29" customWidth="true"/>
-    <col min="221" max="221" width="28.7109375" customWidth="true"/>
-    <col min="222" max="222" width="29" customWidth="true"/>
-    <col min="223" max="223" width="28.7109375" customWidth="true"/>
-    <col min="224" max="224" width="29" customWidth="true"/>
-    <col min="225" max="225" width="28.7109375" customWidth="true"/>
-    <col min="226" max="226" width="29" customWidth="true"/>
-    <col min="227" max="227" width="28.7109375" customWidth="true"/>
-    <col min="228" max="228" width="29" customWidth="true"/>
-    <col min="229" max="229" width="28.7109375" customWidth="true"/>
-    <col min="230" max="230" width="29" customWidth="true"/>
-    <col min="231" max="231" width="28.7109375" customWidth="true"/>
-    <col min="232" max="232" width="25.140625" customWidth="true"/>
-    <col min="233" max="233" width="29.42578125" customWidth="true"/>
-    <col min="234" max="234" width="29.140625" customWidth="true"/>
-    <col min="235" max="235" width="29.42578125" customWidth="true"/>
-    <col min="236" max="236" width="29.140625" customWidth="true"/>
-    <col min="237" max="237" width="29.42578125" customWidth="true"/>
-    <col min="238" max="238" width="29.140625" customWidth="true"/>
-    <col min="239" max="239" width="29.42578125" customWidth="true"/>
-    <col min="240" max="240" width="29.140625" customWidth="true"/>
-    <col min="241" max="241" width="29.42578125" customWidth="true"/>
-    <col min="242" max="242" width="29.140625" customWidth="true"/>
-    <col min="243" max="243" width="29.42578125" customWidth="true"/>
-    <col min="244" max="244" width="29.140625" customWidth="true"/>
-    <col min="245" max="245" width="25.5703125" customWidth="true"/>
-    <col min="246" max="246" width="30.5703125" customWidth="true"/>
-    <col min="247" max="247" width="30.28515625" customWidth="true"/>
-    <col min="248" max="248" width="30.5703125" customWidth="true"/>
-    <col min="249" max="249" width="30.28515625" customWidth="true"/>
-    <col min="250" max="250" width="30.5703125" customWidth="true"/>
-    <col min="251" max="251" width="30.28515625" customWidth="true"/>
-    <col min="252" max="252" width="30.5703125" customWidth="true"/>
-    <col min="253" max="253" width="30.28515625" customWidth="true"/>
-    <col min="254" max="254" width="30.5703125" customWidth="true"/>
-    <col min="255" max="255" width="30.28515625" customWidth="true"/>
-    <col min="256" max="256" width="30.5703125" customWidth="true"/>
-    <col min="257" max="257" width="30.28515625" customWidth="true"/>
-    <col min="258" max="258" width="26.7109375" customWidth="true"/>
-    <col min="259" max="259" width="33.140625" customWidth="true"/>
-    <col min="260" max="260" width="32.85546875" customWidth="true"/>
-    <col min="261" max="261" width="33.140625" customWidth="true"/>
-    <col min="262" max="262" width="32.85546875" customWidth="true"/>
-    <col min="263" max="263" width="33.140625" customWidth="true"/>
-    <col min="264" max="264" width="32.85546875" customWidth="true"/>
-    <col min="265" max="265" width="33.140625" customWidth="true"/>
-    <col min="266" max="266" width="32.85546875" customWidth="true"/>
-    <col min="267" max="267" width="33.140625" customWidth="true"/>
-    <col min="268" max="268" width="32.85546875" customWidth="true"/>
-    <col min="269" max="269" width="33.140625" customWidth="true"/>
-    <col min="270" max="270" width="32.85546875" customWidth="true"/>
-    <col min="271" max="271" width="29.28515625" customWidth="true"/>
-    <col min="272" max="272" width="30" customWidth="true"/>
-    <col min="273" max="273" width="29.7109375" customWidth="true"/>
-    <col min="274" max="274" width="30" customWidth="true"/>
-    <col min="275" max="275" width="29.7109375" customWidth="true"/>
-    <col min="276" max="276" width="30" customWidth="true"/>
-    <col min="277" max="277" width="29.7109375" customWidth="true"/>
-    <col min="278" max="278" width="30" customWidth="true"/>
-    <col min="279" max="279" width="29.7109375" customWidth="true"/>
-    <col min="280" max="280" width="30" customWidth="true"/>
-    <col min="281" max="281" width="29.7109375" customWidth="true"/>
-    <col min="282" max="282" width="30" customWidth="true"/>
-    <col min="283" max="283" width="29.7109375" customWidth="true"/>
-    <col min="284" max="284" width="26.140625" customWidth="true"/>
-    <col min="285" max="285" width="30.42578125" customWidth="true"/>
-    <col min="286" max="286" width="30.140625" customWidth="true"/>
-    <col min="287" max="287" width="30.42578125" customWidth="true"/>
-    <col min="288" max="288" width="30.140625" customWidth="true"/>
-    <col min="289" max="289" width="30.42578125" customWidth="true"/>
-    <col min="290" max="290" width="30.140625" customWidth="true"/>
-    <col min="291" max="291" width="30.42578125" customWidth="true"/>
-    <col min="292" max="292" width="30.140625" customWidth="true"/>
-    <col min="293" max="293" width="30.42578125" customWidth="true"/>
-    <col min="294" max="294" width="30.140625" customWidth="true"/>
-    <col min="295" max="295" width="30.42578125" customWidth="true"/>
-    <col min="296" max="296" width="30.140625" customWidth="true"/>
-    <col min="297" max="297" width="26.5703125" customWidth="true"/>
-    <col min="298" max="298" width="30.5703125" customWidth="true"/>
-    <col min="299" max="299" width="30.28515625" customWidth="true"/>
-    <col min="300" max="300" width="30.5703125" customWidth="true"/>
-    <col min="301" max="301" width="30.28515625" customWidth="true"/>
-    <col min="302" max="302" width="30.5703125" customWidth="true"/>
-    <col min="303" max="303" width="30.28515625" customWidth="true"/>
-    <col min="304" max="304" width="30.5703125" customWidth="true"/>
-    <col min="305" max="305" width="30.28515625" customWidth="true"/>
-    <col min="306" max="306" width="30.5703125" customWidth="true"/>
-    <col min="307" max="307" width="30.28515625" customWidth="true"/>
-    <col min="308" max="308" width="30.5703125" customWidth="true"/>
-    <col min="309" max="309" width="30.28515625" customWidth="true"/>
-    <col min="310" max="310" width="26.7109375" customWidth="true"/>
-    <col min="311" max="311" width="30.7109375" customWidth="true"/>
-    <col min="312" max="312" width="30.42578125" customWidth="true"/>
-    <col min="313" max="313" width="30.7109375" customWidth="true"/>
-    <col min="314" max="314" width="30.42578125" customWidth="true"/>
-    <col min="315" max="315" width="30.7109375" customWidth="true"/>
-    <col min="316" max="316" width="30.42578125" customWidth="true"/>
-    <col min="317" max="317" width="30.7109375" customWidth="true"/>
-    <col min="318" max="318" width="30.42578125" customWidth="true"/>
-    <col min="319" max="319" width="30.7109375" customWidth="true"/>
-    <col min="320" max="320" width="30.42578125" customWidth="true"/>
-    <col min="321" max="321" width="30.7109375" customWidth="true"/>
-    <col min="322" max="322" width="30.42578125" customWidth="true"/>
-    <col min="323" max="323" width="26.85546875" customWidth="true"/>
-    <col min="324" max="324" width="31.140625" customWidth="true"/>
-    <col min="325" max="325" width="30.85546875" customWidth="true"/>
-    <col min="326" max="326" width="31.140625" customWidth="true"/>
-    <col min="327" max="327" width="30.85546875" customWidth="true"/>
-    <col min="328" max="328" width="31.140625" customWidth="true"/>
-    <col min="329" max="329" width="30.85546875" customWidth="true"/>
-    <col min="330" max="330" width="31.140625" customWidth="true"/>
-    <col min="331" max="331" width="30.85546875" customWidth="true"/>
-    <col min="332" max="332" width="31.140625" customWidth="true"/>
-    <col min="333" max="333" width="30.85546875" customWidth="true"/>
-    <col min="334" max="334" width="31.140625" customWidth="true"/>
-    <col min="335" max="335" width="30.85546875" customWidth="true"/>
-    <col min="336" max="336" width="27.28515625" customWidth="true"/>
-    <col min="337" max="337" width="30.28515625" customWidth="true"/>
-    <col min="338" max="338" width="30" customWidth="true"/>
-    <col min="339" max="339" width="30.28515625" customWidth="true"/>
-    <col min="340" max="340" width="30" customWidth="true"/>
-    <col min="341" max="341" width="30.28515625" customWidth="true"/>
-    <col min="342" max="342" width="30" customWidth="true"/>
-    <col min="343" max="343" width="30.28515625" customWidth="true"/>
-    <col min="344" max="344" width="30" customWidth="true"/>
-    <col min="345" max="345" width="30.28515625" customWidth="true"/>
-    <col min="346" max="346" width="30" customWidth="true"/>
-    <col min="347" max="347" width="30.28515625" customWidth="true"/>
-    <col min="348" max="348" width="30" customWidth="true"/>
-    <col min="349" max="349" width="26.42578125" customWidth="true"/>
-    <col min="350" max="350" width="24.42578125" customWidth="true"/>
-    <col min="351" max="351" width="24.140625" customWidth="true"/>
-    <col min="352" max="352" width="24.42578125" customWidth="true"/>
-    <col min="353" max="353" width="24.140625" customWidth="true"/>
-    <col min="354" max="354" width="24.42578125" customWidth="true"/>
-    <col min="355" max="355" width="24.140625" customWidth="true"/>
-    <col min="356" max="356" width="24.42578125" customWidth="true"/>
-    <col min="357" max="357" width="24.140625" customWidth="true"/>
-    <col min="358" max="358" width="24.42578125" customWidth="true"/>
-    <col min="359" max="359" width="24.140625" customWidth="true"/>
-    <col min="360" max="360" width="24.42578125" customWidth="true"/>
-    <col min="361" max="361" width="24.140625" customWidth="true"/>
-    <col min="362" max="362" width="20.5703125" customWidth="true"/>
-    <col min="363" max="363" width="25.7109375" customWidth="true"/>
-    <col min="364" max="364" width="25.42578125" customWidth="true"/>
-    <col min="365" max="365" width="25.7109375" customWidth="true"/>
-    <col min="366" max="366" width="25.42578125" customWidth="true"/>
-    <col min="367" max="367" width="25.7109375" customWidth="true"/>
-    <col min="368" max="368" width="25.42578125" customWidth="true"/>
-    <col min="369" max="369" width="25.7109375" customWidth="true"/>
-    <col min="370" max="370" width="25.42578125" customWidth="true"/>
-    <col min="371" max="371" width="25.7109375" customWidth="true"/>
-    <col min="372" max="372" width="25.42578125" customWidth="true"/>
-    <col min="373" max="373" width="25.7109375" customWidth="true"/>
-    <col min="374" max="374" width="25.42578125" customWidth="true"/>
-    <col min="375" max="375" width="21.85546875" customWidth="true"/>
-    <col min="376" max="376" width="25.28515625" customWidth="true"/>
-    <col min="377" max="377" width="25" customWidth="true"/>
-    <col min="378" max="378" width="25.28515625" customWidth="true"/>
-    <col min="379" max="379" width="25" customWidth="true"/>
-    <col min="380" max="380" width="25.28515625" customWidth="true"/>
-    <col min="381" max="381" width="25" customWidth="true"/>
-    <col min="382" max="382" width="25.28515625" customWidth="true"/>
-    <col min="383" max="383" width="25" customWidth="true"/>
-    <col min="384" max="384" width="25.28515625" customWidth="true"/>
-    <col min="385" max="385" width="25" customWidth="true"/>
-    <col min="386" max="386" width="25.28515625" customWidth="true"/>
-    <col min="387" max="387" width="25" customWidth="true"/>
-    <col min="388" max="388" width="21.42578125" customWidth="true"/>
+    <col min="2" max="2" width="29" customWidth="true"/>
+    <col min="3" max="3" width="28.7109375" customWidth="true"/>
+    <col min="4" max="4" width="29" customWidth="true"/>
+    <col min="5" max="5" width="28.7109375" customWidth="true"/>
+    <col min="6" max="6" width="29" customWidth="true"/>
+    <col min="7" max="7" width="28.7109375" customWidth="true"/>
+    <col min="8" max="8" width="29" customWidth="true"/>
+    <col min="9" max="9" width="28.7109375" customWidth="true"/>
+    <col min="10" max="10" width="29" customWidth="true"/>
+    <col min="11" max="11" width="28.7109375" customWidth="true"/>
+    <col min="12" max="12" width="29" customWidth="true"/>
+    <col min="13" max="13" width="28.7109375" customWidth="true"/>
+    <col min="14" max="14" width="32" customWidth="true"/>
+    <col min="15" max="15" width="31.7109375" customWidth="true"/>
+    <col min="16" max="16" width="32" customWidth="true"/>
+    <col min="17" max="17" width="31.7109375" customWidth="true"/>
+    <col min="18" max="18" width="32" customWidth="true"/>
+    <col min="19" max="19" width="31.7109375" customWidth="true"/>
+    <col min="20" max="20" width="32" customWidth="true"/>
+    <col min="21" max="21" width="31.7109375" customWidth="true"/>
+    <col min="22" max="22" width="32" customWidth="true"/>
+    <col min="23" max="23" width="31.7109375" customWidth="true"/>
+    <col min="24" max="24" width="32" customWidth="true"/>
+    <col min="25" max="25" width="31.7109375" customWidth="true"/>
+    <col min="26" max="26" width="32.140625" customWidth="true"/>
+    <col min="27" max="27" width="31.85546875" customWidth="true"/>
+    <col min="28" max="28" width="32.140625" customWidth="true"/>
+    <col min="29" max="29" width="31.85546875" customWidth="true"/>
+    <col min="30" max="30" width="32.140625" customWidth="true"/>
+    <col min="31" max="31" width="31.85546875" customWidth="true"/>
+    <col min="32" max="32" width="32.140625" customWidth="true"/>
+    <col min="33" max="33" width="31.85546875" customWidth="true"/>
+    <col min="34" max="34" width="32.140625" customWidth="true"/>
+    <col min="35" max="35" width="31.85546875" customWidth="true"/>
+    <col min="36" max="36" width="32.140625" customWidth="true"/>
+    <col min="37" max="37" width="31.85546875" customWidth="true"/>
+    <col min="38" max="38" width="30.7109375" customWidth="true"/>
+    <col min="39" max="39" width="30.42578125" customWidth="true"/>
+    <col min="40" max="40" width="30.7109375" customWidth="true"/>
+    <col min="41" max="41" width="30.42578125" customWidth="true"/>
+    <col min="42" max="42" width="30.7109375" customWidth="true"/>
+    <col min="43" max="43" width="30.42578125" customWidth="true"/>
+    <col min="44" max="44" width="30.7109375" customWidth="true"/>
+    <col min="45" max="45" width="30.42578125" customWidth="true"/>
+    <col min="46" max="46" width="30.7109375" customWidth="true"/>
+    <col min="47" max="47" width="30.42578125" customWidth="true"/>
+    <col min="48" max="48" width="30.7109375" customWidth="true"/>
+    <col min="49" max="49" width="30.42578125" customWidth="true"/>
+    <col min="50" max="50" width="26.85546875" customWidth="true"/>
+    <col min="51" max="51" width="32.85546875" customWidth="true"/>
+    <col min="52" max="52" width="32.5703125" customWidth="true"/>
+    <col min="53" max="53" width="32.85546875" customWidth="true"/>
+    <col min="54" max="54" width="32.5703125" customWidth="true"/>
+    <col min="55" max="55" width="32.85546875" customWidth="true"/>
+    <col min="56" max="56" width="32.5703125" customWidth="true"/>
+    <col min="57" max="57" width="32.85546875" customWidth="true"/>
+    <col min="58" max="58" width="32.5703125" customWidth="true"/>
+    <col min="59" max="59" width="32.85546875" customWidth="true"/>
+    <col min="60" max="60" width="32.5703125" customWidth="true"/>
+    <col min="61" max="61" width="32.85546875" customWidth="true"/>
+    <col min="62" max="62" width="32.5703125" customWidth="true"/>
+    <col min="63" max="63" width="29" customWidth="true"/>
+    <col min="64" max="64" width="31" customWidth="true"/>
+    <col min="65" max="65" width="30.7109375" customWidth="true"/>
+    <col min="66" max="66" width="31" customWidth="true"/>
+    <col min="67" max="67" width="30.7109375" customWidth="true"/>
+    <col min="68" max="68" width="31" customWidth="true"/>
+    <col min="69" max="69" width="30.7109375" customWidth="true"/>
+    <col min="70" max="70" width="31" customWidth="true"/>
+    <col min="71" max="71" width="30.7109375" customWidth="true"/>
+    <col min="72" max="72" width="31" customWidth="true"/>
+    <col min="73" max="73" width="30.7109375" customWidth="true"/>
+    <col min="74" max="74" width="31" customWidth="true"/>
+    <col min="75" max="75" width="30.7109375" customWidth="true"/>
+    <col min="76" max="76" width="27.140625" customWidth="true"/>
+    <col min="77" max="77" width="31.5703125" customWidth="true"/>
+    <col min="78" max="78" width="31.28515625" customWidth="true"/>
+    <col min="79" max="79" width="31.5703125" customWidth="true"/>
+    <col min="80" max="80" width="31.28515625" customWidth="true"/>
+    <col min="81" max="81" width="31.5703125" customWidth="true"/>
+    <col min="82" max="82" width="31.28515625" customWidth="true"/>
+    <col min="83" max="83" width="31.5703125" customWidth="true"/>
+    <col min="84" max="84" width="31.28515625" customWidth="true"/>
+    <col min="85" max="85" width="31.5703125" customWidth="true"/>
+    <col min="86" max="86" width="31.28515625" customWidth="true"/>
+    <col min="87" max="87" width="31.5703125" customWidth="true"/>
+    <col min="88" max="88" width="31.28515625" customWidth="true"/>
+    <col min="89" max="89" width="27.7109375" customWidth="true"/>
+    <col min="90" max="90" width="29.7109375" customWidth="true"/>
+    <col min="91" max="91" width="29.42578125" customWidth="true"/>
+    <col min="92" max="92" width="29.7109375" customWidth="true"/>
+    <col min="93" max="93" width="29.42578125" customWidth="true"/>
+    <col min="94" max="94" width="29.7109375" customWidth="true"/>
+    <col min="95" max="95" width="29.42578125" customWidth="true"/>
+    <col min="96" max="96" width="29.7109375" customWidth="true"/>
+    <col min="97" max="97" width="29.42578125" customWidth="true"/>
+    <col min="98" max="98" width="29.7109375" customWidth="true"/>
+    <col min="99" max="99" width="29.42578125" customWidth="true"/>
+    <col min="100" max="100" width="29.7109375" customWidth="true"/>
+    <col min="101" max="101" width="29.42578125" customWidth="true"/>
+    <col min="102" max="102" width="25.85546875" customWidth="true"/>
+    <col min="103" max="103" width="31.28515625" customWidth="true"/>
+    <col min="104" max="104" width="31" customWidth="true"/>
+    <col min="105" max="105" width="31.28515625" customWidth="true"/>
+    <col min="106" max="106" width="31" customWidth="true"/>
+    <col min="107" max="107" width="31.28515625" customWidth="true"/>
+    <col min="108" max="108" width="31" customWidth="true"/>
+    <col min="109" max="109" width="31.28515625" customWidth="true"/>
+    <col min="110" max="110" width="31" customWidth="true"/>
+    <col min="111" max="111" width="31.28515625" customWidth="true"/>
+    <col min="112" max="112" width="31" customWidth="true"/>
+    <col min="113" max="113" width="31.28515625" customWidth="true"/>
+    <col min="114" max="114" width="31" customWidth="true"/>
+    <col min="115" max="115" width="27.42578125" customWidth="true"/>
+    <col min="116" max="116" width="31.7109375" customWidth="true"/>
+    <col min="117" max="117" width="31.42578125" customWidth="true"/>
+    <col min="118" max="118" width="31.7109375" customWidth="true"/>
+    <col min="119" max="119" width="31.42578125" customWidth="true"/>
+    <col min="120" max="120" width="31.7109375" customWidth="true"/>
+    <col min="121" max="121" width="31.42578125" customWidth="true"/>
+    <col min="122" max="122" width="31.7109375" customWidth="true"/>
+    <col min="123" max="123" width="31.42578125" customWidth="true"/>
+    <col min="124" max="124" width="31.7109375" customWidth="true"/>
+    <col min="125" max="125" width="31.42578125" customWidth="true"/>
+    <col min="126" max="126" width="31.7109375" customWidth="true"/>
+    <col min="127" max="127" width="31.42578125" customWidth="true"/>
+    <col min="128" max="128" width="27.85546875" customWidth="true"/>
+    <col min="129" max="129" width="29.42578125" customWidth="true"/>
+    <col min="130" max="130" width="29.140625" customWidth="true"/>
+    <col min="131" max="131" width="29.42578125" customWidth="true"/>
+    <col min="132" max="132" width="29.140625" customWidth="true"/>
+    <col min="133" max="133" width="29.42578125" customWidth="true"/>
+    <col min="134" max="134" width="29.140625" customWidth="true"/>
+    <col min="135" max="135" width="29.42578125" customWidth="true"/>
+    <col min="136" max="136" width="29.140625" customWidth="true"/>
+    <col min="137" max="137" width="29.42578125" customWidth="true"/>
+    <col min="138" max="138" width="29.140625" customWidth="true"/>
+    <col min="139" max="139" width="29.42578125" customWidth="true"/>
+    <col min="140" max="140" width="29.140625" customWidth="true"/>
+    <col min="141" max="141" width="25.5703125" customWidth="true"/>
+    <col min="142" max="142" width="31" customWidth="true"/>
+    <col min="143" max="143" width="30.7109375" customWidth="true"/>
+    <col min="144" max="144" width="31" customWidth="true"/>
+    <col min="145" max="145" width="30.7109375" customWidth="true"/>
+    <col min="146" max="146" width="31" customWidth="true"/>
+    <col min="147" max="147" width="30.7109375" customWidth="true"/>
+    <col min="148" max="148" width="31" customWidth="true"/>
+    <col min="149" max="149" width="30.7109375" customWidth="true"/>
+    <col min="150" max="150" width="31" customWidth="true"/>
+    <col min="151" max="151" width="30.7109375" customWidth="true"/>
+    <col min="152" max="152" width="31" customWidth="true"/>
+    <col min="153" max="153" width="30.7109375" customWidth="true"/>
+    <col min="154" max="154" width="27.140625" customWidth="true"/>
+    <col min="155" max="155" width="31.42578125" customWidth="true"/>
+    <col min="156" max="156" width="31.140625" customWidth="true"/>
+    <col min="157" max="157" width="31.42578125" customWidth="true"/>
+    <col min="158" max="158" width="31.140625" customWidth="true"/>
+    <col min="159" max="159" width="31.42578125" customWidth="true"/>
+    <col min="160" max="160" width="31.140625" customWidth="true"/>
+    <col min="161" max="161" width="31.42578125" customWidth="true"/>
+    <col min="162" max="162" width="31.140625" customWidth="true"/>
+    <col min="163" max="163" width="31.42578125" customWidth="true"/>
+    <col min="164" max="164" width="31.140625" customWidth="true"/>
+    <col min="165" max="165" width="31.42578125" customWidth="true"/>
+    <col min="166" max="166" width="31.140625" customWidth="true"/>
+    <col min="167" max="167" width="27.5703125" customWidth="true"/>
+    <col min="168" max="168" width="32.28515625" customWidth="true"/>
+    <col min="169" max="169" width="32" customWidth="true"/>
+    <col min="170" max="170" width="32.28515625" customWidth="true"/>
+    <col min="171" max="171" width="32" customWidth="true"/>
+    <col min="172" max="172" width="32.28515625" customWidth="true"/>
+    <col min="173" max="173" width="32" customWidth="true"/>
+    <col min="174" max="174" width="32.28515625" customWidth="true"/>
+    <col min="175" max="175" width="32" customWidth="true"/>
+    <col min="176" max="176" width="32.28515625" customWidth="true"/>
+    <col min="177" max="177" width="32" customWidth="true"/>
+    <col min="178" max="178" width="32.28515625" customWidth="true"/>
+    <col min="179" max="179" width="32" customWidth="true"/>
+    <col min="180" max="180" width="28.42578125" customWidth="true"/>
+    <col min="181" max="181" width="33.85546875" customWidth="true"/>
+    <col min="182" max="182" width="33.5703125" customWidth="true"/>
+    <col min="183" max="183" width="33.85546875" customWidth="true"/>
+    <col min="184" max="184" width="33.5703125" customWidth="true"/>
+    <col min="185" max="185" width="33.85546875" customWidth="true"/>
+    <col min="186" max="186" width="33.5703125" customWidth="true"/>
+    <col min="187" max="187" width="33.85546875" customWidth="true"/>
+    <col min="188" max="188" width="33.5703125" customWidth="true"/>
+    <col min="189" max="189" width="33.85546875" customWidth="true"/>
+    <col min="190" max="190" width="33.5703125" customWidth="true"/>
+    <col min="191" max="191" width="33.85546875" customWidth="true"/>
+    <col min="192" max="192" width="33.5703125" customWidth="true"/>
+    <col min="193" max="193" width="30" customWidth="true"/>
+    <col min="194" max="194" width="34.28515625" customWidth="true"/>
+    <col min="195" max="195" width="34" customWidth="true"/>
+    <col min="196" max="196" width="34.28515625" customWidth="true"/>
+    <col min="197" max="197" width="34" customWidth="true"/>
+    <col min="198" max="198" width="34.28515625" customWidth="true"/>
+    <col min="199" max="199" width="34" customWidth="true"/>
+    <col min="200" max="200" width="34.28515625" customWidth="true"/>
+    <col min="201" max="201" width="34" customWidth="true"/>
+    <col min="202" max="202" width="34.28515625" customWidth="true"/>
+    <col min="203" max="203" width="34" customWidth="true"/>
+    <col min="204" max="204" width="34.28515625" customWidth="true"/>
+    <col min="205" max="205" width="34" customWidth="true"/>
+    <col min="206" max="206" width="30.42578125" customWidth="true"/>
+    <col min="207" max="207" width="32.42578125" customWidth="true"/>
+    <col min="208" max="208" width="32.140625" customWidth="true"/>
+    <col min="209" max="209" width="32.42578125" customWidth="true"/>
+    <col min="210" max="210" width="32.140625" customWidth="true"/>
+    <col min="211" max="211" width="32.42578125" customWidth="true"/>
+    <col min="212" max="212" width="32.140625" customWidth="true"/>
+    <col min="213" max="213" width="32.42578125" customWidth="true"/>
+    <col min="214" max="214" width="32.140625" customWidth="true"/>
+    <col min="215" max="215" width="32.42578125" customWidth="true"/>
+    <col min="216" max="216" width="32.140625" customWidth="true"/>
+    <col min="217" max="217" width="32.42578125" customWidth="true"/>
+    <col min="218" max="218" width="32.140625" customWidth="true"/>
+    <col min="219" max="219" width="28.5703125" customWidth="true"/>
+    <col min="220" max="220" width="34" customWidth="true"/>
+    <col min="221" max="221" width="33.7109375" customWidth="true"/>
+    <col min="222" max="222" width="34" customWidth="true"/>
+    <col min="223" max="223" width="33.7109375" customWidth="true"/>
+    <col min="224" max="224" width="34" customWidth="true"/>
+    <col min="225" max="225" width="33.7109375" customWidth="true"/>
+    <col min="226" max="226" width="34" customWidth="true"/>
+    <col min="227" max="227" width="33.7109375" customWidth="true"/>
+    <col min="228" max="228" width="34" customWidth="true"/>
+    <col min="229" max="229" width="33.7109375" customWidth="true"/>
+    <col min="230" max="230" width="34" customWidth="true"/>
+    <col min="231" max="231" width="33.7109375" customWidth="true"/>
+    <col min="232" max="232" width="30.140625" customWidth="true"/>
+    <col min="233" max="233" width="38.28515625" customWidth="true"/>
+    <col min="234" max="234" width="38" customWidth="true"/>
+    <col min="235" max="235" width="38.28515625" customWidth="true"/>
+    <col min="236" max="236" width="38" customWidth="true"/>
+    <col min="237" max="237" width="38.28515625" customWidth="true"/>
+    <col min="238" max="238" width="38" customWidth="true"/>
+    <col min="239" max="239" width="38.28515625" customWidth="true"/>
+    <col min="240" max="240" width="38" customWidth="true"/>
+    <col min="241" max="241" width="38.28515625" customWidth="true"/>
+    <col min="242" max="242" width="38" customWidth="true"/>
+    <col min="243" max="243" width="38.28515625" customWidth="true"/>
+    <col min="244" max="244" width="38" customWidth="true"/>
+    <col min="245" max="245" width="34.42578125" customWidth="true"/>
+    <col min="246" max="246" width="40.28515625" customWidth="true"/>
+    <col min="247" max="247" width="40" customWidth="true"/>
+    <col min="248" max="248" width="40.28515625" customWidth="true"/>
+    <col min="249" max="249" width="40" customWidth="true"/>
+    <col min="250" max="250" width="40.28515625" customWidth="true"/>
+    <col min="251" max="251" width="40" customWidth="true"/>
+    <col min="252" max="252" width="40.28515625" customWidth="true"/>
+    <col min="253" max="253" width="40" customWidth="true"/>
+    <col min="254" max="254" width="40.28515625" customWidth="true"/>
+    <col min="255" max="255" width="40" customWidth="true"/>
+    <col min="256" max="256" width="40.28515625" customWidth="true"/>
+    <col min="257" max="257" width="40" customWidth="true"/>
+    <col min="258" max="258" width="36.42578125" customWidth="true"/>
+    <col min="259" max="259" width="38.85546875" customWidth="true"/>
+    <col min="260" max="260" width="38.5703125" customWidth="true"/>
+    <col min="261" max="261" width="38.85546875" customWidth="true"/>
+    <col min="262" max="262" width="38.5703125" customWidth="true"/>
+    <col min="263" max="263" width="38.85546875" customWidth="true"/>
+    <col min="264" max="264" width="38.5703125" customWidth="true"/>
+    <col min="265" max="265" width="38.85546875" customWidth="true"/>
+    <col min="266" max="266" width="38.5703125" customWidth="true"/>
+    <col min="267" max="267" width="38.85546875" customWidth="true"/>
+    <col min="268" max="268" width="38.5703125" customWidth="true"/>
+    <col min="269" max="269" width="38.85546875" customWidth="true"/>
+    <col min="270" max="270" width="38.5703125" customWidth="true"/>
+    <col min="271" max="271" width="35" customWidth="true"/>
+    <col min="272" max="272" width="38.42578125" customWidth="true"/>
+    <col min="273" max="273" width="38.140625" customWidth="true"/>
+    <col min="274" max="274" width="38.42578125" customWidth="true"/>
+    <col min="275" max="275" width="38.140625" customWidth="true"/>
+    <col min="276" max="276" width="38.42578125" customWidth="true"/>
+    <col min="277" max="277" width="38.140625" customWidth="true"/>
+    <col min="278" max="278" width="38.42578125" customWidth="true"/>
+    <col min="279" max="279" width="38.140625" customWidth="true"/>
+    <col min="280" max="280" width="38.42578125" customWidth="true"/>
+    <col min="281" max="281" width="38.140625" customWidth="true"/>
+    <col min="282" max="282" width="38.42578125" customWidth="true"/>
+    <col min="283" max="283" width="38.140625" customWidth="true"/>
+    <col min="284" max="284" width="34.5703125" customWidth="true"/>
+    <col min="285" max="285" width="35.7109375" customWidth="true"/>
+    <col min="286" max="286" width="35.42578125" customWidth="true"/>
+    <col min="287" max="287" width="35.7109375" customWidth="true"/>
+    <col min="288" max="288" width="35.42578125" customWidth="true"/>
+    <col min="289" max="289" width="35.7109375" customWidth="true"/>
+    <col min="290" max="290" width="35.42578125" customWidth="true"/>
+    <col min="291" max="291" width="35.7109375" customWidth="true"/>
+    <col min="292" max="292" width="35.42578125" customWidth="true"/>
+    <col min="293" max="293" width="35.7109375" customWidth="true"/>
+    <col min="294" max="294" width="35.42578125" customWidth="true"/>
+    <col min="295" max="295" width="35.7109375" customWidth="true"/>
+    <col min="296" max="296" width="35.42578125" customWidth="true"/>
+    <col min="297" max="297" width="31.85546875" customWidth="true"/>
+    <col min="298" max="298" width="26.5703125" customWidth="true"/>
+    <col min="299" max="299" width="26.28515625" customWidth="true"/>
+    <col min="300" max="300" width="26.5703125" customWidth="true"/>
+    <col min="301" max="301" width="26.28515625" customWidth="true"/>
+    <col min="302" max="302" width="26.5703125" customWidth="true"/>
+    <col min="303" max="303" width="26.28515625" customWidth="true"/>
+    <col min="304" max="304" width="26.5703125" customWidth="true"/>
+    <col min="305" max="305" width="26.28515625" customWidth="true"/>
+    <col min="306" max="306" width="26.5703125" customWidth="true"/>
+    <col min="307" max="307" width="26.28515625" customWidth="true"/>
+    <col min="308" max="308" width="26.5703125" customWidth="true"/>
+    <col min="309" max="309" width="26.28515625" customWidth="true"/>
+    <col min="310" max="310" width="22.7109375" customWidth="true"/>
+    <col min="311" max="311" width="28.140625" customWidth="true"/>
+    <col min="312" max="312" width="27.85546875" customWidth="true"/>
+    <col min="313" max="313" width="28.140625" customWidth="true"/>
+    <col min="314" max="314" width="27.85546875" customWidth="true"/>
+    <col min="315" max="315" width="28.140625" customWidth="true"/>
+    <col min="316" max="316" width="27.85546875" customWidth="true"/>
+    <col min="317" max="317" width="28.140625" customWidth="true"/>
+    <col min="318" max="318" width="27.85546875" customWidth="true"/>
+    <col min="319" max="319" width="28.140625" customWidth="true"/>
+    <col min="320" max="320" width="27.85546875" customWidth="true"/>
+    <col min="321" max="321" width="28.140625" customWidth="true"/>
+    <col min="322" max="322" width="27.85546875" customWidth="true"/>
+    <col min="323" max="323" width="24.28515625" customWidth="true"/>
+    <col min="324" max="324" width="28.5703125" customWidth="true"/>
+    <col min="325" max="325" width="28.28515625" customWidth="true"/>
+    <col min="326" max="326" width="28.5703125" customWidth="true"/>
+    <col min="327" max="327" width="28.28515625" customWidth="true"/>
+    <col min="328" max="328" width="28.5703125" customWidth="true"/>
+    <col min="329" max="329" width="28.28515625" customWidth="true"/>
+    <col min="330" max="330" width="28.5703125" customWidth="true"/>
+    <col min="331" max="331" width="28.28515625" customWidth="true"/>
+    <col min="332" max="332" width="28.5703125" customWidth="true"/>
+    <col min="333" max="333" width="28.28515625" customWidth="true"/>
+    <col min="334" max="334" width="28.5703125" customWidth="true"/>
+    <col min="335" max="335" width="28.28515625" customWidth="true"/>
+    <col min="336" max="336" width="24.7109375" customWidth="true"/>
+    <col min="337" max="337" width="33.140625" customWidth="true"/>
+    <col min="338" max="338" width="32.85546875" customWidth="true"/>
+    <col min="339" max="339" width="33.140625" customWidth="true"/>
+    <col min="340" max="340" width="32.85546875" customWidth="true"/>
+    <col min="341" max="341" width="33.140625" customWidth="true"/>
+    <col min="342" max="342" width="32.85546875" customWidth="true"/>
+    <col min="343" max="343" width="33.140625" customWidth="true"/>
+    <col min="344" max="344" width="32.85546875" customWidth="true"/>
+    <col min="345" max="345" width="33.140625" customWidth="true"/>
+    <col min="346" max="346" width="32.85546875" customWidth="true"/>
+    <col min="347" max="347" width="33.140625" customWidth="true"/>
+    <col min="348" max="348" width="32.85546875" customWidth="true"/>
+    <col min="349" max="349" width="29.28515625" customWidth="true"/>
+    <col min="350" max="350" width="27.42578125" customWidth="true"/>
+    <col min="351" max="351" width="27.140625" customWidth="true"/>
+    <col min="352" max="352" width="27.42578125" customWidth="true"/>
+    <col min="353" max="353" width="27.140625" customWidth="true"/>
+    <col min="354" max="354" width="27.42578125" customWidth="true"/>
+    <col min="355" max="355" width="27.140625" customWidth="true"/>
+    <col min="356" max="356" width="27.42578125" customWidth="true"/>
+    <col min="357" max="357" width="27.140625" customWidth="true"/>
+    <col min="358" max="358" width="27.42578125" customWidth="true"/>
+    <col min="359" max="359" width="27.140625" customWidth="true"/>
+    <col min="360" max="360" width="27.42578125" customWidth="true"/>
+    <col min="361" max="361" width="27.140625" customWidth="true"/>
+    <col min="362" max="362" width="23.5703125" customWidth="true"/>
+    <col min="363" max="363" width="28.85546875" customWidth="true"/>
+    <col min="364" max="364" width="28.5703125" customWidth="true"/>
+    <col min="365" max="365" width="28.85546875" customWidth="true"/>
+    <col min="366" max="366" width="28.5703125" customWidth="true"/>
+    <col min="367" max="367" width="28.85546875" customWidth="true"/>
+    <col min="368" max="368" width="28.5703125" customWidth="true"/>
+    <col min="369" max="369" width="28.85546875" customWidth="true"/>
+    <col min="370" max="370" width="28.5703125" customWidth="true"/>
+    <col min="371" max="371" width="28.85546875" customWidth="true"/>
+    <col min="372" max="372" width="28.5703125" customWidth="true"/>
+    <col min="373" max="373" width="28.85546875" customWidth="true"/>
+    <col min="374" max="374" width="28.5703125" customWidth="true"/>
+    <col min="375" max="375" width="25" customWidth="true"/>
+    <col min="376" max="376" width="28.28515625" customWidth="true"/>
+    <col min="377" max="377" width="28" customWidth="true"/>
+    <col min="378" max="378" width="28.28515625" customWidth="true"/>
+    <col min="379" max="379" width="28" customWidth="true"/>
+    <col min="380" max="380" width="28.28515625" customWidth="true"/>
+    <col min="381" max="381" width="28" customWidth="true"/>
+    <col min="382" max="382" width="28.28515625" customWidth="true"/>
+    <col min="383" max="383" width="28" customWidth="true"/>
+    <col min="384" max="384" width="28.28515625" customWidth="true"/>
+    <col min="385" max="385" width="28" customWidth="true"/>
+    <col min="386" max="386" width="28.28515625" customWidth="true"/>
+    <col min="387" max="387" width="28" customWidth="true"/>
+    <col min="388" max="388" width="24.42578125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3284,199 +3284,199 @@
         <v>-29.905999999999999</v>
       </c>
       <c r="FL2" s="0">
+        <v>32.347000000000001</v>
+      </c>
+      <c r="FM2" s="0">
+        <v>38.136000000000003</v>
+      </c>
+      <c r="FN2" s="0">
+        <v>42.921999999999997</v>
+      </c>
+      <c r="FO2" s="0">
+        <v>42.359999999999999</v>
+      </c>
+      <c r="FP2" s="0">
+        <v>60.189</v>
+      </c>
+      <c r="FQ2" s="0">
+        <v>46.627000000000002</v>
+      </c>
+      <c r="FR2" s="0">
+        <v>37.392000000000003</v>
+      </c>
+      <c r="FS2" s="0">
+        <v>39.841000000000001</v>
+      </c>
+      <c r="FT2" s="0">
+        <v>57.572000000000003</v>
+      </c>
+      <c r="FU2" s="0">
+        <v>37.953000000000003</v>
+      </c>
+      <c r="FV2" s="0">
+        <v>51.972999999999999</v>
+      </c>
+      <c r="FW2" s="0">
+        <v>49.700000000000003</v>
+      </c>
+      <c r="FX2" s="0">
+        <v>15.864000000000001</v>
+      </c>
+      <c r="FY2" s="0">
+        <v>54.323</v>
+      </c>
+      <c r="FZ2" s="0">
+        <v>44.441000000000003</v>
+      </c>
+      <c r="GA2" s="0">
+        <v>63.691000000000003</v>
+      </c>
+      <c r="GB2" s="0">
+        <v>41.356000000000002</v>
+      </c>
+      <c r="GC2" s="0">
+        <v>78.561000000000007</v>
+      </c>
+      <c r="GD2" s="0">
+        <v>66.046000000000006</v>
+      </c>
+      <c r="GE2" s="0">
+        <v>60.637</v>
+      </c>
+      <c r="GF2" s="0">
+        <v>49.387</v>
+      </c>
+      <c r="GG2" s="0">
+        <v>73.284999999999997</v>
+      </c>
+      <c r="GH2" s="0">
+        <v>49.609999999999999</v>
+      </c>
+      <c r="GI2" s="0">
+        <v>86.953000000000003</v>
+      </c>
+      <c r="GJ2" s="0">
+        <v>56.140999999999998</v>
+      </c>
+      <c r="GK2" s="0">
+        <v>32.479999999999997</v>
+      </c>
+      <c r="GL2" s="0">
+        <v>48.191000000000003</v>
+      </c>
+      <c r="GM2" s="0">
+        <v>98.582999999999998</v>
+      </c>
+      <c r="GN2" s="0">
+        <v>48.984000000000002</v>
+      </c>
+      <c r="GO2" s="0">
+        <v>95.766000000000005</v>
+      </c>
+      <c r="GP2" s="0">
+        <v>44.655999999999999</v>
+      </c>
+      <c r="GQ2" s="0">
+        <v>165.52699999999999</v>
+      </c>
+      <c r="GR2" s="0">
+        <v>46.637</v>
+      </c>
+      <c r="GS2" s="0">
+        <v>97.873000000000005</v>
+      </c>
+      <c r="GT2" s="0">
+        <v>43.606000000000002</v>
+      </c>
+      <c r="GU2" s="0">
+        <v>115.17</v>
+      </c>
+      <c r="GV2" s="0">
+        <v>53.997</v>
+      </c>
+      <c r="GW2" s="0">
+        <v>123.084</v>
+      </c>
+      <c r="GX2" s="0">
+        <v>42.484999999999999</v>
+      </c>
+      <c r="GY2" s="0">
+        <v>6.8520000000000003</v>
+      </c>
+      <c r="GZ2" s="0">
+        <v>17.32</v>
+      </c>
+      <c r="HA2" s="0">
+        <v>10.282</v>
+      </c>
+      <c r="HB2" s="0">
+        <v>7.0960000000000001</v>
+      </c>
+      <c r="HC2" s="0">
+        <v>8.1020000000000003</v>
+      </c>
+      <c r="HD2" s="0">
+        <v>16.251999999999999</v>
+      </c>
+      <c r="HE2" s="0">
+        <v>2.1259999999999999</v>
+      </c>
+      <c r="HF2" s="0">
+        <v>11.295999999999999</v>
+      </c>
+      <c r="HG2" s="0">
+        <v>5.46</v>
+      </c>
+      <c r="HH2" s="0">
+        <v>7.0049999999999999</v>
+      </c>
+      <c r="HI2" s="0">
+        <v>5.8390000000000004</v>
+      </c>
+      <c r="HJ2" s="0">
+        <v>13.724</v>
+      </c>
+      <c r="HK2" s="0">
+        <v>5.4580000000000002</v>
+      </c>
+      <c r="HL2" s="0">
         <v>102.667</v>
       </c>
-      <c r="FM2" s="0">
+      <c r="HM2" s="0">
         <v>142.35900000000001</v>
       </c>
-      <c r="FN2" s="0">
+      <c r="HN2" s="0">
         <v>109.495</v>
       </c>
-      <c r="FO2" s="0">
+      <c r="HO2" s="0">
         <v>146.75399999999999</v>
       </c>
-      <c r="FP2" s="0">
+      <c r="HP2" s="0">
         <v>90.275999999999996</v>
       </c>
-      <c r="FQ2" s="0">
+      <c r="HQ2" s="0">
         <v>156.34800000000001</v>
       </c>
-      <c r="FR2" s="0">
+      <c r="HR2" s="0">
         <v>108.151</v>
       </c>
-      <c r="FS2" s="0">
+      <c r="HS2" s="0">
         <v>144.95599999999999</v>
       </c>
-      <c r="FT2" s="0">
+      <c r="HT2" s="0">
         <v>112.43300000000001</v>
       </c>
-      <c r="FU2" s="0">
+      <c r="HU2" s="0">
         <v>141.727</v>
       </c>
-      <c r="FV2" s="0">
+      <c r="HV2" s="0">
         <v>107.03</v>
       </c>
-      <c r="FW2" s="0">
+      <c r="HW2" s="0">
         <v>150.453</v>
       </c>
-      <c r="FX2" s="0">
+      <c r="HX2" s="0">
         <v>97.495999999999995</v>
-      </c>
-      <c r="FY2" s="0">
-        <v>32.347000000000001</v>
-      </c>
-      <c r="FZ2" s="0">
-        <v>38.136000000000003</v>
-      </c>
-      <c r="GA2" s="0">
-        <v>42.921999999999997</v>
-      </c>
-      <c r="GB2" s="0">
-        <v>42.359999999999999</v>
-      </c>
-      <c r="GC2" s="0">
-        <v>60.189</v>
-      </c>
-      <c r="GD2" s="0">
-        <v>46.627000000000002</v>
-      </c>
-      <c r="GE2" s="0">
-        <v>37.392000000000003</v>
-      </c>
-      <c r="GF2" s="0">
-        <v>39.841000000000001</v>
-      </c>
-      <c r="GG2" s="0">
-        <v>57.572000000000003</v>
-      </c>
-      <c r="GH2" s="0">
-        <v>37.953000000000003</v>
-      </c>
-      <c r="GI2" s="0">
-        <v>51.972999999999999</v>
-      </c>
-      <c r="GJ2" s="0">
-        <v>49.700000000000003</v>
-      </c>
-      <c r="GK2" s="0">
-        <v>15.864000000000001</v>
-      </c>
-      <c r="GL2" s="0">
-        <v>54.323</v>
-      </c>
-      <c r="GM2" s="0">
-        <v>44.441000000000003</v>
-      </c>
-      <c r="GN2" s="0">
-        <v>63.691000000000003</v>
-      </c>
-      <c r="GO2" s="0">
-        <v>41.356000000000002</v>
-      </c>
-      <c r="GP2" s="0">
-        <v>78.561000000000007</v>
-      </c>
-      <c r="GQ2" s="0">
-        <v>66.046000000000006</v>
-      </c>
-      <c r="GR2" s="0">
-        <v>60.637</v>
-      </c>
-      <c r="GS2" s="0">
-        <v>49.387</v>
-      </c>
-      <c r="GT2" s="0">
-        <v>73.284999999999997</v>
-      </c>
-      <c r="GU2" s="0">
-        <v>49.609999999999999</v>
-      </c>
-      <c r="GV2" s="0">
-        <v>86.953000000000003</v>
-      </c>
-      <c r="GW2" s="0">
-        <v>56.140999999999998</v>
-      </c>
-      <c r="GX2" s="0">
-        <v>32.479999999999997</v>
-      </c>
-      <c r="GY2" s="0">
-        <v>48.191000000000003</v>
-      </c>
-      <c r="GZ2" s="0">
-        <v>98.582999999999998</v>
-      </c>
-      <c r="HA2" s="0">
-        <v>48.984000000000002</v>
-      </c>
-      <c r="HB2" s="0">
-        <v>95.766000000000005</v>
-      </c>
-      <c r="HC2" s="0">
-        <v>44.655999999999999</v>
-      </c>
-      <c r="HD2" s="0">
-        <v>165.52699999999999</v>
-      </c>
-      <c r="HE2" s="0">
-        <v>46.637</v>
-      </c>
-      <c r="HF2" s="0">
-        <v>97.873000000000005</v>
-      </c>
-      <c r="HG2" s="0">
-        <v>43.606000000000002</v>
-      </c>
-      <c r="HH2" s="0">
-        <v>115.17</v>
-      </c>
-      <c r="HI2" s="0">
-        <v>53.997</v>
-      </c>
-      <c r="HJ2" s="0">
-        <v>123.084</v>
-      </c>
-      <c r="HK2" s="0">
-        <v>42.484999999999999</v>
-      </c>
-      <c r="HL2" s="0">
-        <v>6.8520000000000003</v>
-      </c>
-      <c r="HM2" s="0">
-        <v>17.32</v>
-      </c>
-      <c r="HN2" s="0">
-        <v>10.282</v>
-      </c>
-      <c r="HO2" s="0">
-        <v>7.0960000000000001</v>
-      </c>
-      <c r="HP2" s="0">
-        <v>8.1020000000000003</v>
-      </c>
-      <c r="HQ2" s="0">
-        <v>16.251999999999999</v>
-      </c>
-      <c r="HR2" s="0">
-        <v>2.1259999999999999</v>
-      </c>
-      <c r="HS2" s="0">
-        <v>11.295999999999999</v>
-      </c>
-      <c r="HT2" s="0">
-        <v>5.46</v>
-      </c>
-      <c r="HU2" s="0">
-        <v>7.0049999999999999</v>
-      </c>
-      <c r="HV2" s="0">
-        <v>5.8390000000000004</v>
-      </c>
-      <c r="HW2" s="0">
-        <v>13.724</v>
-      </c>
-      <c r="HX2" s="0">
-        <v>5.4580000000000002</v>
       </c>
       <c r="HY2" s="0">
         <v>49.021999999999998</v>
@@ -3557,82 +3557,82 @@
         <v>41.158999999999999</v>
       </c>
       <c r="IY2" s="0">
+        <v>27.725000000000001</v>
+      </c>
+      <c r="IZ2" s="0">
+        <v>28.734999999999999</v>
+      </c>
+      <c r="JA2" s="0">
+        <v>27.792000000000002</v>
+      </c>
+      <c r="JB2" s="0">
+        <v>30.899000000000001</v>
+      </c>
+      <c r="JC2" s="0">
+        <v>30.699000000000002</v>
+      </c>
+      <c r="JD2" s="0">
+        <v>25.684000000000001</v>
+      </c>
+      <c r="JE2" s="0">
+        <v>30.826000000000001</v>
+      </c>
+      <c r="JF2" s="0">
+        <v>25.149999999999999</v>
+      </c>
+      <c r="JG2" s="0">
+        <v>30.652000000000001</v>
+      </c>
+      <c r="JH2" s="0">
+        <v>17.675000000000001</v>
+      </c>
+      <c r="JI2" s="0">
+        <v>35.906999999999996</v>
+      </c>
+      <c r="JJ2" s="0">
+        <v>26.530000000000001</v>
+      </c>
+      <c r="JK2" s="0">
+        <v>28.713999999999999</v>
+      </c>
+      <c r="JL2" s="0">
         <v>69.439999999999998</v>
       </c>
-      <c r="IZ2" s="0">
+      <c r="JM2" s="0">
         <v>108.133</v>
       </c>
-      <c r="JA2" s="0">
+      <c r="JN2" s="0">
         <v>72.518000000000001</v>
       </c>
-      <c r="JB2" s="0">
+      <c r="JO2" s="0">
         <v>109.313</v>
       </c>
-      <c r="JC2" s="0">
+      <c r="JP2" s="0">
         <v>69.388000000000005</v>
       </c>
-      <c r="JD2" s="0">
+      <c r="JQ2" s="0">
         <v>118.732</v>
       </c>
-      <c r="JE2" s="0">
+      <c r="JR2" s="0">
         <v>74.376000000000005</v>
       </c>
-      <c r="JF2" s="0">
+      <c r="JS2" s="0">
         <v>112.074</v>
       </c>
-      <c r="JG2" s="0">
+      <c r="JT2" s="0">
         <v>73.231999999999999</v>
       </c>
-      <c r="JH2" s="0">
+      <c r="JU2" s="0">
         <v>115.84099999999999</v>
       </c>
-      <c r="JI2" s="0">
+      <c r="JV2" s="0">
         <v>71.795000000000002</v>
       </c>
-      <c r="JJ2" s="0">
+      <c r="JW2" s="0">
         <v>116.414</v>
       </c>
-      <c r="JK2" s="0">
+      <c r="JX2" s="0">
         <v>68.004000000000005</v>
-      </c>
-      <c r="JL2" s="0">
-        <v>27.725000000000001</v>
-      </c>
-      <c r="JM2" s="0">
-        <v>28.734999999999999</v>
-      </c>
-      <c r="JN2" s="0">
-        <v>27.792000000000002</v>
-      </c>
-      <c r="JO2" s="0">
-        <v>30.899000000000001</v>
-      </c>
-      <c r="JP2" s="0">
-        <v>30.699000000000002</v>
-      </c>
-      <c r="JQ2" s="0">
-        <v>25.684000000000001</v>
-      </c>
-      <c r="JR2" s="0">
-        <v>30.826000000000001</v>
-      </c>
-      <c r="JS2" s="0">
-        <v>25.149999999999999</v>
-      </c>
-      <c r="JT2" s="0">
-        <v>30.652000000000001</v>
-      </c>
-      <c r="JU2" s="0">
-        <v>17.675000000000001</v>
-      </c>
-      <c r="JV2" s="0">
-        <v>35.906999999999996</v>
-      </c>
-      <c r="JW2" s="0">
-        <v>26.530000000000001</v>
-      </c>
-      <c r="JX2" s="0">
-        <v>28.713999999999999</v>
       </c>
       <c r="JY2" s="0">
         <v>33.226999999999997</v>
@@ -4450,199 +4450,199 @@
         <v>-15.968</v>
       </c>
       <c r="FL3" s="0">
+        <v>25.460999999999999</v>
+      </c>
+      <c r="FM3" s="0">
+        <v>44.252000000000002</v>
+      </c>
+      <c r="FN3" s="0">
+        <v>18.931999999999999</v>
+      </c>
+      <c r="FO3" s="0">
+        <v>40.155999999999999</v>
+      </c>
+      <c r="FP3" s="0">
+        <v>24.725000000000001</v>
+      </c>
+      <c r="FQ3" s="0">
+        <v>59.134</v>
+      </c>
+      <c r="FR3" s="0">
+        <v>17.367999999999999</v>
+      </c>
+      <c r="FS3" s="0">
+        <v>28.033999999999999</v>
+      </c>
+      <c r="FT3" s="0">
+        <v>25.954999999999998</v>
+      </c>
+      <c r="FU3" s="0">
+        <v>52.228999999999999</v>
+      </c>
+      <c r="FV3" s="0">
+        <v>25.245000000000001</v>
+      </c>
+      <c r="FW3" s="0">
+        <v>56.488</v>
+      </c>
+      <c r="FX3" s="0">
+        <v>9.6989999999999998</v>
+      </c>
+      <c r="FY3" s="0">
+        <v>26.058</v>
+      </c>
+      <c r="FZ3" s="0">
+        <v>49.856000000000002</v>
+      </c>
+      <c r="GA3" s="0">
+        <v>32.216999999999999</v>
+      </c>
+      <c r="GB3" s="0">
+        <v>52.911999999999999</v>
+      </c>
+      <c r="GC3" s="0">
+        <v>27.628</v>
+      </c>
+      <c r="GD3" s="0">
+        <v>50.322000000000003</v>
+      </c>
+      <c r="GE3" s="0">
+        <v>29.138000000000002</v>
+      </c>
+      <c r="GF3" s="0">
+        <v>46.810000000000002</v>
+      </c>
+      <c r="GG3" s="0">
+        <v>25.768000000000001</v>
+      </c>
+      <c r="GH3" s="0">
+        <v>52.484999999999999</v>
+      </c>
+      <c r="GI3" s="0">
+        <v>28.664000000000001</v>
+      </c>
+      <c r="GJ3" s="0">
+        <v>55.826000000000001</v>
+      </c>
+      <c r="GK3" s="0">
+        <v>21.006</v>
+      </c>
+      <c r="GL3" s="0">
+        <v>23.550999999999998</v>
+      </c>
+      <c r="GM3" s="0">
+        <v>24.085000000000001</v>
+      </c>
+      <c r="GN3" s="0">
+        <v>23.974</v>
+      </c>
+      <c r="GO3" s="0">
+        <v>23.202999999999999</v>
+      </c>
+      <c r="GP3" s="0">
+        <v>21.678000000000001</v>
+      </c>
+      <c r="GQ3" s="0">
+        <v>26.998000000000001</v>
+      </c>
+      <c r="GR3" s="0">
+        <v>23.649999999999999</v>
+      </c>
+      <c r="GS3" s="0">
+        <v>21.350000000000001</v>
+      </c>
+      <c r="GT3" s="0">
+        <v>21.873000000000001</v>
+      </c>
+      <c r="GU3" s="0">
+        <v>23.568000000000001</v>
+      </c>
+      <c r="GV3" s="0">
+        <v>22.469000000000001</v>
+      </c>
+      <c r="GW3" s="0">
+        <v>24.797999999999998</v>
+      </c>
+      <c r="GX3" s="0">
+        <v>16.655999999999999</v>
+      </c>
+      <c r="GY3" s="0">
+        <v>10.423999999999999</v>
+      </c>
+      <c r="GZ3" s="0">
+        <v>15.074999999999999</v>
+      </c>
+      <c r="HA3" s="0">
+        <v>6.1829999999999998</v>
+      </c>
+      <c r="HB3" s="0">
+        <v>14.324999999999999</v>
+      </c>
+      <c r="HC3" s="0">
+        <v>10.448</v>
+      </c>
+      <c r="HD3" s="0">
+        <v>19.582000000000001</v>
+      </c>
+      <c r="HE3" s="0">
+        <v>8.9730000000000008</v>
+      </c>
+      <c r="HF3" s="0">
+        <v>18.099</v>
+      </c>
+      <c r="HG3" s="0">
+        <v>12.269</v>
+      </c>
+      <c r="HH3" s="0">
+        <v>20.167999999999999</v>
+      </c>
+      <c r="HI3" s="0">
+        <v>10.932</v>
+      </c>
+      <c r="HJ3" s="0">
+        <v>17.201000000000001</v>
+      </c>
+      <c r="HK3" s="0">
+        <v>7.9630000000000001</v>
+      </c>
+      <c r="HL3" s="0">
         <v>97.090999999999994</v>
       </c>
-      <c r="FM3" s="0">
+      <c r="HM3" s="0">
         <v>100.309</v>
       </c>
-      <c r="FN3" s="0">
+      <c r="HN3" s="0">
         <v>95.725999999999999</v>
       </c>
-      <c r="FO3" s="0">
+      <c r="HO3" s="0">
         <v>112.416</v>
       </c>
-      <c r="FP3" s="0">
+      <c r="HP3" s="0">
         <v>98.454999999999998</v>
       </c>
-      <c r="FQ3" s="0">
+      <c r="HQ3" s="0">
         <v>116.462</v>
       </c>
-      <c r="FR3" s="0">
+      <c r="HR3" s="0">
         <v>93.542000000000002</v>
       </c>
-      <c r="FS3" s="0">
+      <c r="HS3" s="0">
         <v>103.548</v>
       </c>
-      <c r="FT3" s="0">
+      <c r="HT3" s="0">
         <v>89.846999999999994</v>
       </c>
-      <c r="FU3" s="0">
+      <c r="HU3" s="0">
         <v>114.273</v>
       </c>
-      <c r="FV3" s="0">
+      <c r="HV3" s="0">
         <v>95.620999999999995</v>
       </c>
-      <c r="FW3" s="0">
+      <c r="HW3" s="0">
         <v>121.146</v>
       </c>
-      <c r="FX3" s="0">
+      <c r="HX3" s="0">
         <v>88.614999999999995</v>
-      </c>
-      <c r="FY3" s="0">
-        <v>25.460999999999999</v>
-      </c>
-      <c r="FZ3" s="0">
-        <v>44.252000000000002</v>
-      </c>
-      <c r="GA3" s="0">
-        <v>18.931999999999999</v>
-      </c>
-      <c r="GB3" s="0">
-        <v>40.155999999999999</v>
-      </c>
-      <c r="GC3" s="0">
-        <v>24.725000000000001</v>
-      </c>
-      <c r="GD3" s="0">
-        <v>59.134</v>
-      </c>
-      <c r="GE3" s="0">
-        <v>17.367999999999999</v>
-      </c>
-      <c r="GF3" s="0">
-        <v>28.033999999999999</v>
-      </c>
-      <c r="GG3" s="0">
-        <v>25.954999999999998</v>
-      </c>
-      <c r="GH3" s="0">
-        <v>52.228999999999999</v>
-      </c>
-      <c r="GI3" s="0">
-        <v>25.245000000000001</v>
-      </c>
-      <c r="GJ3" s="0">
-        <v>56.488</v>
-      </c>
-      <c r="GK3" s="0">
-        <v>9.6989999999999998</v>
-      </c>
-      <c r="GL3" s="0">
-        <v>26.058</v>
-      </c>
-      <c r="GM3" s="0">
-        <v>49.856000000000002</v>
-      </c>
-      <c r="GN3" s="0">
-        <v>32.216999999999999</v>
-      </c>
-      <c r="GO3" s="0">
-        <v>52.911999999999999</v>
-      </c>
-      <c r="GP3" s="0">
-        <v>27.628</v>
-      </c>
-      <c r="GQ3" s="0">
-        <v>50.322000000000003</v>
-      </c>
-      <c r="GR3" s="0">
-        <v>29.138000000000002</v>
-      </c>
-      <c r="GS3" s="0">
-        <v>46.810000000000002</v>
-      </c>
-      <c r="GT3" s="0">
-        <v>25.768000000000001</v>
-      </c>
-      <c r="GU3" s="0">
-        <v>52.484999999999999</v>
-      </c>
-      <c r="GV3" s="0">
-        <v>28.664000000000001</v>
-      </c>
-      <c r="GW3" s="0">
-        <v>55.826000000000001</v>
-      </c>
-      <c r="GX3" s="0">
-        <v>21.006</v>
-      </c>
-      <c r="GY3" s="0">
-        <v>23.550999999999998</v>
-      </c>
-      <c r="GZ3" s="0">
-        <v>24.085000000000001</v>
-      </c>
-      <c r="HA3" s="0">
-        <v>23.974</v>
-      </c>
-      <c r="HB3" s="0">
-        <v>23.202999999999999</v>
-      </c>
-      <c r="HC3" s="0">
-        <v>21.678000000000001</v>
-      </c>
-      <c r="HD3" s="0">
-        <v>26.998000000000001</v>
-      </c>
-      <c r="HE3" s="0">
-        <v>23.649999999999999</v>
-      </c>
-      <c r="HF3" s="0">
-        <v>21.350000000000001</v>
-      </c>
-      <c r="HG3" s="0">
-        <v>21.873000000000001</v>
-      </c>
-      <c r="HH3" s="0">
-        <v>23.568000000000001</v>
-      </c>
-      <c r="HI3" s="0">
-        <v>22.469000000000001</v>
-      </c>
-      <c r="HJ3" s="0">
-        <v>24.797999999999998</v>
-      </c>
-      <c r="HK3" s="0">
-        <v>16.655999999999999</v>
-      </c>
-      <c r="HL3" s="0">
-        <v>10.423999999999999</v>
-      </c>
-      <c r="HM3" s="0">
-        <v>15.074999999999999</v>
-      </c>
-      <c r="HN3" s="0">
-        <v>6.1829999999999998</v>
-      </c>
-      <c r="HO3" s="0">
-        <v>14.324999999999999</v>
-      </c>
-      <c r="HP3" s="0">
-        <v>10.448</v>
-      </c>
-      <c r="HQ3" s="0">
-        <v>19.582000000000001</v>
-      </c>
-      <c r="HR3" s="0">
-        <v>8.9730000000000008</v>
-      </c>
-      <c r="HS3" s="0">
-        <v>18.099</v>
-      </c>
-      <c r="HT3" s="0">
-        <v>12.269</v>
-      </c>
-      <c r="HU3" s="0">
-        <v>20.167999999999999</v>
-      </c>
-      <c r="HV3" s="0">
-        <v>10.932</v>
-      </c>
-      <c r="HW3" s="0">
-        <v>17.201000000000001</v>
-      </c>
-      <c r="HX3" s="0">
-        <v>7.9630000000000001</v>
       </c>
       <c r="HY3" s="0">
         <v>72.203000000000003</v>
@@ -4723,82 +4723,82 @@
         <v>52.520000000000003</v>
       </c>
       <c r="IY3" s="0">
+        <v>27.553999999999998</v>
+      </c>
+      <c r="IZ3" s="0">
+        <v>20.001999999999999</v>
+      </c>
+      <c r="JA3" s="0">
+        <v>29.805</v>
+      </c>
+      <c r="JB3" s="0">
+        <v>25.297999999999998</v>
+      </c>
+      <c r="JC3" s="0">
+        <v>30.477</v>
+      </c>
+      <c r="JD3" s="0">
+        <v>21.550000000000001</v>
+      </c>
+      <c r="JE3" s="0">
+        <v>26.866</v>
+      </c>
+      <c r="JF3" s="0">
+        <v>24.736000000000001</v>
+      </c>
+      <c r="JG3" s="0">
+        <v>32.902000000000001</v>
+      </c>
+      <c r="JH3" s="0">
+        <v>20.696999999999999</v>
+      </c>
+      <c r="JI3" s="0">
+        <v>32.762</v>
+      </c>
+      <c r="JJ3" s="0">
+        <v>21.335000000000001</v>
+      </c>
+      <c r="JK3" s="0">
+        <v>27.215</v>
+      </c>
+      <c r="JL3" s="0">
         <v>66.453999999999994</v>
       </c>
-      <c r="IZ3" s="0">
+      <c r="JM3" s="0">
         <v>74.707999999999998</v>
       </c>
-      <c r="JA3" s="0">
+      <c r="JN3" s="0">
         <v>66.132000000000005</v>
       </c>
-      <c r="JB3" s="0">
+      <c r="JO3" s="0">
         <v>82.813999999999993</v>
       </c>
-      <c r="JC3" s="0">
+      <c r="JP3" s="0">
         <v>65.024000000000001</v>
       </c>
-      <c r="JD3" s="0">
+      <c r="JQ3" s="0">
         <v>89.424999999999997</v>
       </c>
-      <c r="JE3" s="0">
+      <c r="JR3" s="0">
         <v>64.506</v>
       </c>
-      <c r="JF3" s="0">
+      <c r="JS3" s="0">
         <v>75.372</v>
       </c>
-      <c r="JG3" s="0">
+      <c r="JT3" s="0">
         <v>68.403000000000006</v>
       </c>
-      <c r="JH3" s="0">
+      <c r="JU3" s="0">
         <v>89.028000000000006</v>
       </c>
-      <c r="JI3" s="0">
+      <c r="JV3" s="0">
         <v>65.730999999999995</v>
       </c>
-      <c r="JJ3" s="0">
+      <c r="JW3" s="0">
         <v>93.191000000000003</v>
       </c>
-      <c r="JK3" s="0">
+      <c r="JX3" s="0">
         <v>63.296999999999997</v>
-      </c>
-      <c r="JL3" s="0">
-        <v>27.553999999999998</v>
-      </c>
-      <c r="JM3" s="0">
-        <v>20.001999999999999</v>
-      </c>
-      <c r="JN3" s="0">
-        <v>29.805</v>
-      </c>
-      <c r="JO3" s="0">
-        <v>25.297999999999998</v>
-      </c>
-      <c r="JP3" s="0">
-        <v>30.477</v>
-      </c>
-      <c r="JQ3" s="0">
-        <v>21.550000000000001</v>
-      </c>
-      <c r="JR3" s="0">
-        <v>26.866</v>
-      </c>
-      <c r="JS3" s="0">
-        <v>24.736000000000001</v>
-      </c>
-      <c r="JT3" s="0">
-        <v>32.902000000000001</v>
-      </c>
-      <c r="JU3" s="0">
-        <v>20.696999999999999</v>
-      </c>
-      <c r="JV3" s="0">
-        <v>32.762</v>
-      </c>
-      <c r="JW3" s="0">
-        <v>21.335000000000001</v>
-      </c>
-      <c r="JX3" s="0">
-        <v>27.215</v>
       </c>
       <c r="JY3" s="0">
         <v>30.637</v>
@@ -5616,199 +5616,199 @@
         <v>-31.018000000000001</v>
       </c>
       <c r="FL4" s="0">
+        <v>27.881</v>
+      </c>
+      <c r="FM4" s="0">
+        <v>44.426000000000002</v>
+      </c>
+      <c r="FN4" s="0">
+        <v>37.304000000000002</v>
+      </c>
+      <c r="FO4" s="0">
+        <v>38.709000000000003</v>
+      </c>
+      <c r="FP4" s="0">
+        <v>44.985999999999997</v>
+      </c>
+      <c r="FQ4" s="0">
+        <v>44.515000000000001</v>
+      </c>
+      <c r="FR4" s="0">
+        <v>33.825000000000003</v>
+      </c>
+      <c r="FS4" s="0">
+        <v>30.742000000000001</v>
+      </c>
+      <c r="FT4" s="0">
+        <v>39.530999999999999</v>
+      </c>
+      <c r="FU4" s="0">
+        <v>40.523000000000003</v>
+      </c>
+      <c r="FV4" s="0">
+        <v>29</v>
+      </c>
+      <c r="FW4" s="0">
+        <v>63.540999999999997</v>
+      </c>
+      <c r="FX4" s="0">
+        <v>13.566000000000001</v>
+      </c>
+      <c r="FY4" s="0">
+        <v>61.573</v>
+      </c>
+      <c r="FZ4" s="0">
+        <v>68.668000000000006</v>
+      </c>
+      <c r="GA4" s="0">
+        <v>61.079999999999998</v>
+      </c>
+      <c r="GB4" s="0">
+        <v>72.421999999999997</v>
+      </c>
+      <c r="GC4" s="0">
+        <v>82.951999999999998</v>
+      </c>
+      <c r="GD4" s="0">
+        <v>77.231999999999999</v>
+      </c>
+      <c r="GE4" s="0">
+        <v>57.707000000000001</v>
+      </c>
+      <c r="GF4" s="0">
+        <v>70.596000000000004</v>
+      </c>
+      <c r="GG4" s="0">
+        <v>69.549999999999997</v>
+      </c>
+      <c r="GH4" s="0">
+        <v>74.337999999999994</v>
+      </c>
+      <c r="GI4" s="0">
+        <v>70.998000000000005</v>
+      </c>
+      <c r="GJ4" s="0">
+        <v>94.001999999999995</v>
+      </c>
+      <c r="GK4" s="0">
+        <v>30.533999999999999</v>
+      </c>
+      <c r="GL4" s="0">
+        <v>35.335999999999999</v>
+      </c>
+      <c r="GM4" s="0">
+        <v>50.008000000000003</v>
+      </c>
+      <c r="GN4" s="0">
+        <v>25.047000000000001</v>
+      </c>
+      <c r="GO4" s="0">
+        <v>29.111000000000001</v>
+      </c>
+      <c r="GP4" s="0">
+        <v>38.798999999999999</v>
+      </c>
+      <c r="GQ4" s="0">
+        <v>43.384999999999998</v>
+      </c>
+      <c r="GR4" s="0">
+        <v>42.100999999999999</v>
+      </c>
+      <c r="GS4" s="0">
+        <v>36.343000000000004</v>
+      </c>
+      <c r="GT4" s="0">
+        <v>27.259</v>
+      </c>
+      <c r="GU4" s="0">
+        <v>30.094999999999999</v>
+      </c>
+      <c r="GV4" s="0">
+        <v>32.523000000000003</v>
+      </c>
+      <c r="GW4" s="0">
+        <v>62.475000000000001</v>
+      </c>
+      <c r="GX4" s="0">
+        <v>26.484999999999999</v>
+      </c>
+      <c r="GY4" s="0">
+        <v>23.832999999999998</v>
+      </c>
+      <c r="GZ4" s="0">
+        <v>27.757999999999999</v>
+      </c>
+      <c r="HA4" s="0">
+        <v>11.647</v>
+      </c>
+      <c r="HB4" s="0">
+        <v>8.8309999999999995</v>
+      </c>
+      <c r="HC4" s="0">
+        <v>13.052</v>
+      </c>
+      <c r="HD4" s="0">
+        <v>43.131999999999998</v>
+      </c>
+      <c r="HE4" s="0">
+        <v>7.016</v>
+      </c>
+      <c r="HF4" s="0">
+        <v>35.164000000000001</v>
+      </c>
+      <c r="HG4" s="0">
+        <v>9.8849999999999998</v>
+      </c>
+      <c r="HH4" s="0">
+        <v>17.850999999999999</v>
+      </c>
+      <c r="HI4" s="0">
+        <v>30.353000000000002</v>
+      </c>
+      <c r="HJ4" s="0">
+        <v>17.913</v>
+      </c>
+      <c r="HK4" s="0">
+        <v>12.744999999999999</v>
+      </c>
+      <c r="HL4" s="0">
         <v>105.521</v>
       </c>
-      <c r="FM4" s="0">
+      <c r="HM4" s="0">
         <v>128.78299999999999</v>
       </c>
-      <c r="FN4" s="0">
+      <c r="HN4" s="0">
         <v>113.511</v>
       </c>
-      <c r="FO4" s="0">
+      <c r="HO4" s="0">
         <v>134.71000000000001</v>
       </c>
-      <c r="FP4" s="0">
+      <c r="HP4" s="0">
         <v>103.474</v>
       </c>
-      <c r="FQ4" s="0">
+      <c r="HQ4" s="0">
         <v>143.30000000000001</v>
       </c>
-      <c r="FR4" s="0">
+      <c r="HR4" s="0">
         <v>114.06</v>
       </c>
-      <c r="FS4" s="0">
+      <c r="HS4" s="0">
         <v>131.00800000000001</v>
       </c>
-      <c r="FT4" s="0">
+      <c r="HT4" s="0">
         <v>111.544</v>
       </c>
-      <c r="FU4" s="0">
+      <c r="HU4" s="0">
         <v>141.22999999999999</v>
       </c>
-      <c r="FV4" s="0">
+      <c r="HV4" s="0">
         <v>106.229</v>
       </c>
-      <c r="FW4" s="0">
+      <c r="HW4" s="0">
         <v>147.691</v>
       </c>
-      <c r="FX4" s="0">
+      <c r="HX4" s="0">
         <v>105.023</v>
-      </c>
-      <c r="FY4" s="0">
-        <v>27.881</v>
-      </c>
-      <c r="FZ4" s="0">
-        <v>44.426000000000002</v>
-      </c>
-      <c r="GA4" s="0">
-        <v>37.304000000000002</v>
-      </c>
-      <c r="GB4" s="0">
-        <v>38.709000000000003</v>
-      </c>
-      <c r="GC4" s="0">
-        <v>44.985999999999997</v>
-      </c>
-      <c r="GD4" s="0">
-        <v>44.515000000000001</v>
-      </c>
-      <c r="GE4" s="0">
-        <v>33.825000000000003</v>
-      </c>
-      <c r="GF4" s="0">
-        <v>30.742000000000001</v>
-      </c>
-      <c r="GG4" s="0">
-        <v>39.530999999999999</v>
-      </c>
-      <c r="GH4" s="0">
-        <v>40.523000000000003</v>
-      </c>
-      <c r="GI4" s="0">
-        <v>29</v>
-      </c>
-      <c r="GJ4" s="0">
-        <v>63.540999999999997</v>
-      </c>
-      <c r="GK4" s="0">
-        <v>13.566000000000001</v>
-      </c>
-      <c r="GL4" s="0">
-        <v>61.573</v>
-      </c>
-      <c r="GM4" s="0">
-        <v>68.668000000000006</v>
-      </c>
-      <c r="GN4" s="0">
-        <v>61.079999999999998</v>
-      </c>
-      <c r="GO4" s="0">
-        <v>72.421999999999997</v>
-      </c>
-      <c r="GP4" s="0">
-        <v>82.951999999999998</v>
-      </c>
-      <c r="GQ4" s="0">
-        <v>77.231999999999999</v>
-      </c>
-      <c r="GR4" s="0">
-        <v>57.707000000000001</v>
-      </c>
-      <c r="GS4" s="0">
-        <v>70.596000000000004</v>
-      </c>
-      <c r="GT4" s="0">
-        <v>69.549999999999997</v>
-      </c>
-      <c r="GU4" s="0">
-        <v>74.337999999999994</v>
-      </c>
-      <c r="GV4" s="0">
-        <v>70.998000000000005</v>
-      </c>
-      <c r="GW4" s="0">
-        <v>94.001999999999995</v>
-      </c>
-      <c r="GX4" s="0">
-        <v>30.533999999999999</v>
-      </c>
-      <c r="GY4" s="0">
-        <v>35.335999999999999</v>
-      </c>
-      <c r="GZ4" s="0">
-        <v>50.008000000000003</v>
-      </c>
-      <c r="HA4" s="0">
-        <v>25.047000000000001</v>
-      </c>
-      <c r="HB4" s="0">
-        <v>29.111000000000001</v>
-      </c>
-      <c r="HC4" s="0">
-        <v>38.798999999999999</v>
-      </c>
-      <c r="HD4" s="0">
-        <v>43.384999999999998</v>
-      </c>
-      <c r="HE4" s="0">
-        <v>42.100999999999999</v>
-      </c>
-      <c r="HF4" s="0">
-        <v>36.343000000000004</v>
-      </c>
-      <c r="HG4" s="0">
-        <v>27.259</v>
-      </c>
-      <c r="HH4" s="0">
-        <v>30.094999999999999</v>
-      </c>
-      <c r="HI4" s="0">
-        <v>32.523000000000003</v>
-      </c>
-      <c r="HJ4" s="0">
-        <v>62.475000000000001</v>
-      </c>
-      <c r="HK4" s="0">
-        <v>26.484999999999999</v>
-      </c>
-      <c r="HL4" s="0">
-        <v>23.832999999999998</v>
-      </c>
-      <c r="HM4" s="0">
-        <v>27.757999999999999</v>
-      </c>
-      <c r="HN4" s="0">
-        <v>11.647</v>
-      </c>
-      <c r="HO4" s="0">
-        <v>8.8309999999999995</v>
-      </c>
-      <c r="HP4" s="0">
-        <v>13.052</v>
-      </c>
-      <c r="HQ4" s="0">
-        <v>43.131999999999998</v>
-      </c>
-      <c r="HR4" s="0">
-        <v>7.016</v>
-      </c>
-      <c r="HS4" s="0">
-        <v>35.164000000000001</v>
-      </c>
-      <c r="HT4" s="0">
-        <v>9.8849999999999998</v>
-      </c>
-      <c r="HU4" s="0">
-        <v>17.850999999999999</v>
-      </c>
-      <c r="HV4" s="0">
-        <v>30.353000000000002</v>
-      </c>
-      <c r="HW4" s="0">
-        <v>17.913</v>
-      </c>
-      <c r="HX4" s="0">
-        <v>12.744999999999999</v>
       </c>
       <c r="HY4" s="0">
         <v>71.558999999999997</v>
@@ -5889,82 +5889,82 @@
         <v>57.097999999999999</v>
       </c>
       <c r="IY4" s="0">
+        <v>24.943000000000001</v>
+      </c>
+      <c r="IZ4" s="0">
+        <v>23.486000000000001</v>
+      </c>
+      <c r="JA4" s="0">
+        <v>23.210000000000001</v>
+      </c>
+      <c r="JB4" s="0">
+        <v>24.885000000000002</v>
+      </c>
+      <c r="JC4" s="0">
+        <v>29.359999999999999</v>
+      </c>
+      <c r="JD4" s="0">
+        <v>26.309999999999999</v>
+      </c>
+      <c r="JE4" s="0">
+        <v>34.271999999999998</v>
+      </c>
+      <c r="JF4" s="0">
+        <v>23.588000000000001</v>
+      </c>
+      <c r="JG4" s="0">
+        <v>30.318000000000001</v>
+      </c>
+      <c r="JH4" s="0">
+        <v>25.454000000000001</v>
+      </c>
+      <c r="JI4" s="0">
+        <v>23.452999999999999</v>
+      </c>
+      <c r="JJ4" s="0">
+        <v>29.606000000000002</v>
+      </c>
+      <c r="JK4" s="0">
+        <v>26.036999999999999</v>
+      </c>
+      <c r="JL4" s="0">
         <v>77.298000000000002</v>
       </c>
-      <c r="IZ4" s="0">
+      <c r="JM4" s="0">
         <v>101.09999999999999</v>
       </c>
-      <c r="JA4" s="0">
+      <c r="JN4" s="0">
         <v>79.605000000000004</v>
       </c>
-      <c r="JB4" s="0">
+      <c r="JO4" s="0">
         <v>105.38800000000001</v>
       </c>
-      <c r="JC4" s="0">
+      <c r="JP4" s="0">
         <v>69.968000000000004</v>
       </c>
-      <c r="JD4" s="0">
+      <c r="JQ4" s="0">
         <v>111.85299999999999</v>
       </c>
-      <c r="JE4" s="0">
+      <c r="JR4" s="0">
         <v>79.856999999999999</v>
       </c>
-      <c r="JF4" s="0">
+      <c r="JS4" s="0">
         <v>98.177000000000007</v>
       </c>
-      <c r="JG4" s="0">
+      <c r="JT4" s="0">
         <v>76.477999999999994</v>
       </c>
-      <c r="JH4" s="0">
+      <c r="JU4" s="0">
         <v>110.931</v>
       </c>
-      <c r="JI4" s="0">
+      <c r="JV4" s="0">
         <v>83.385999999999996</v>
       </c>
-      <c r="JJ4" s="0">
+      <c r="JW4" s="0">
         <v>113.777</v>
       </c>
-      <c r="JK4" s="0">
+      <c r="JX4" s="0">
         <v>79.007999999999996</v>
-      </c>
-      <c r="JL4" s="0">
-        <v>24.943000000000001</v>
-      </c>
-      <c r="JM4" s="0">
-        <v>23.486000000000001</v>
-      </c>
-      <c r="JN4" s="0">
-        <v>23.210000000000001</v>
-      </c>
-      <c r="JO4" s="0">
-        <v>24.885000000000002</v>
-      </c>
-      <c r="JP4" s="0">
-        <v>29.359999999999999</v>
-      </c>
-      <c r="JQ4" s="0">
-        <v>26.309999999999999</v>
-      </c>
-      <c r="JR4" s="0">
-        <v>34.271999999999998</v>
-      </c>
-      <c r="JS4" s="0">
-        <v>23.588000000000001</v>
-      </c>
-      <c r="JT4" s="0">
-        <v>30.318000000000001</v>
-      </c>
-      <c r="JU4" s="0">
-        <v>25.454000000000001</v>
-      </c>
-      <c r="JV4" s="0">
-        <v>23.452999999999999</v>
-      </c>
-      <c r="JW4" s="0">
-        <v>29.606000000000002</v>
-      </c>
-      <c r="JX4" s="0">
-        <v>26.036999999999999</v>
       </c>
       <c r="JY4" s="0">
         <v>28.222999999999999</v>
@@ -6782,199 +6782,199 @@
         <v>-47.478000000000002</v>
       </c>
       <c r="FL5" s="0">
+        <v>143.81899999999999</v>
+      </c>
+      <c r="FM5" s="0">
+        <v>44.973999999999997</v>
+      </c>
+      <c r="FN5" s="0">
+        <v>152.327</v>
+      </c>
+      <c r="FO5" s="0">
+        <v>74.994</v>
+      </c>
+      <c r="FP5" s="0">
+        <v>123.009</v>
+      </c>
+      <c r="FQ5" s="0">
+        <v>85.116</v>
+      </c>
+      <c r="FR5" s="0">
+        <v>146.66499999999999</v>
+      </c>
+      <c r="FS5" s="0">
+        <v>45.869</v>
+      </c>
+      <c r="FT5" s="0">
+        <v>151.31700000000001</v>
+      </c>
+      <c r="FU5" s="0">
+        <v>73.150999999999996</v>
+      </c>
+      <c r="FV5" s="0">
+        <v>157.11000000000001</v>
+      </c>
+      <c r="FW5" s="0">
+        <v>96.106999999999999</v>
+      </c>
+      <c r="FX5" s="0">
+        <v>19.183</v>
+      </c>
+      <c r="FY5" s="0">
+        <v>223.321</v>
+      </c>
+      <c r="FZ5" s="0">
+        <v>115.81100000000001</v>
+      </c>
+      <c r="GA5" s="0">
+        <v>233.69900000000001</v>
+      </c>
+      <c r="GB5" s="0">
+        <v>117.122</v>
+      </c>
+      <c r="GC5" s="0">
+        <v>219.208</v>
+      </c>
+      <c r="GD5" s="0">
+        <v>78.635999999999996</v>
+      </c>
+      <c r="GE5" s="0">
+        <v>219.27099999999999</v>
+      </c>
+      <c r="GF5" s="0">
+        <v>108.066</v>
+      </c>
+      <c r="GG5" s="0">
+        <v>205.83000000000001</v>
+      </c>
+      <c r="GH5" s="0">
+        <v>102.258</v>
+      </c>
+      <c r="GI5" s="0">
+        <v>219.96899999999999</v>
+      </c>
+      <c r="GJ5" s="0">
+        <v>116.55500000000001</v>
+      </c>
+      <c r="GK5" s="0">
+        <v>25.559000000000001</v>
+      </c>
+      <c r="GL5" s="0">
+        <v>86.963999999999999</v>
+      </c>
+      <c r="GM5" s="0">
+        <v>191.67500000000001</v>
+      </c>
+      <c r="GN5" s="0">
+        <v>85.646000000000001</v>
+      </c>
+      <c r="GO5" s="0">
+        <v>199.25800000000001</v>
+      </c>
+      <c r="GP5" s="0">
+        <v>72.022000000000006</v>
+      </c>
+      <c r="GQ5" s="0">
+        <v>156.54499999999999</v>
+      </c>
+      <c r="GR5" s="0">
+        <v>93.224999999999994</v>
+      </c>
+      <c r="GS5" s="0">
+        <v>181.77099999999999</v>
+      </c>
+      <c r="GT5" s="0">
+        <v>80.013999999999996</v>
+      </c>
+      <c r="GU5" s="0">
+        <v>179.57499999999999</v>
+      </c>
+      <c r="GV5" s="0">
+        <v>86.100999999999999</v>
+      </c>
+      <c r="GW5" s="0">
+        <v>183.35599999999999</v>
+      </c>
+      <c r="GX5" s="0">
+        <v>91.451999999999998</v>
+      </c>
+      <c r="GY5" s="0">
+        <v>48.191000000000003</v>
+      </c>
+      <c r="GZ5" s="0">
+        <v>18.483000000000001</v>
+      </c>
+      <c r="HA5" s="0">
+        <v>40.604999999999997</v>
+      </c>
+      <c r="HB5" s="0">
+        <v>14.720000000000001</v>
+      </c>
+      <c r="HC5" s="0">
+        <v>38.765000000000001</v>
+      </c>
+      <c r="HD5" s="0">
+        <v>10.353999999999999</v>
+      </c>
+      <c r="HE5" s="0">
+        <v>47.972000000000001</v>
+      </c>
+      <c r="HF5" s="0">
+        <v>16.861999999999998</v>
+      </c>
+      <c r="HG5" s="0">
+        <v>40.171999999999997</v>
+      </c>
+      <c r="HH5" s="0">
+        <v>8.0239999999999991</v>
+      </c>
+      <c r="HI5" s="0">
+        <v>42.055999999999997</v>
+      </c>
+      <c r="HJ5" s="0">
+        <v>20.105</v>
+      </c>
+      <c r="HK5" s="0">
+        <v>9.6379999999999999</v>
+      </c>
+      <c r="HL5" s="0">
         <v>102.495</v>
       </c>
-      <c r="FM5" s="0">
+      <c r="HM5" s="0">
         <v>125.639</v>
       </c>
-      <c r="FN5" s="0">
+      <c r="HN5" s="0">
         <v>66.436999999999998</v>
       </c>
-      <c r="FO5" s="0">
+      <c r="HO5" s="0">
         <v>118.456</v>
       </c>
-      <c r="FP5" s="0">
+      <c r="HP5" s="0">
         <v>57.200000000000003</v>
       </c>
-      <c r="FQ5" s="0">
+      <c r="HQ5" s="0">
         <v>98.864000000000004</v>
       </c>
-      <c r="FR5" s="0">
+      <c r="HR5" s="0">
         <v>116.131</v>
       </c>
-      <c r="FS5" s="0">
+      <c r="HS5" s="0">
         <v>134.792</v>
       </c>
-      <c r="FT5" s="0">
+      <c r="HT5" s="0">
         <v>61.600000000000001</v>
       </c>
-      <c r="FU5" s="0">
+      <c r="HU5" s="0">
         <v>101.09999999999999</v>
       </c>
-      <c r="FV5" s="0">
+      <c r="HV5" s="0">
         <v>68.991</v>
       </c>
-      <c r="FW5" s="0">
+      <c r="HW5" s="0">
         <v>132.67500000000001</v>
       </c>
-      <c r="FX5" s="0">
+      <c r="HX5" s="0">
         <v>95.304000000000002</v>
-      </c>
-      <c r="FY5" s="0">
-        <v>143.81899999999999</v>
-      </c>
-      <c r="FZ5" s="0">
-        <v>44.973999999999997</v>
-      </c>
-      <c r="GA5" s="0">
-        <v>152.327</v>
-      </c>
-      <c r="GB5" s="0">
-        <v>74.994</v>
-      </c>
-      <c r="GC5" s="0">
-        <v>123.009</v>
-      </c>
-      <c r="GD5" s="0">
-        <v>85.116</v>
-      </c>
-      <c r="GE5" s="0">
-        <v>146.66499999999999</v>
-      </c>
-      <c r="GF5" s="0">
-        <v>45.869</v>
-      </c>
-      <c r="GG5" s="0">
-        <v>151.31700000000001</v>
-      </c>
-      <c r="GH5" s="0">
-        <v>73.150999999999996</v>
-      </c>
-      <c r="GI5" s="0">
-        <v>157.11000000000001</v>
-      </c>
-      <c r="GJ5" s="0">
-        <v>96.106999999999999</v>
-      </c>
-      <c r="GK5" s="0">
-        <v>19.183</v>
-      </c>
-      <c r="GL5" s="0">
-        <v>223.321</v>
-      </c>
-      <c r="GM5" s="0">
-        <v>115.81100000000001</v>
-      </c>
-      <c r="GN5" s="0">
-        <v>233.69900000000001</v>
-      </c>
-      <c r="GO5" s="0">
-        <v>117.122</v>
-      </c>
-      <c r="GP5" s="0">
-        <v>219.208</v>
-      </c>
-      <c r="GQ5" s="0">
-        <v>78.635999999999996</v>
-      </c>
-      <c r="GR5" s="0">
-        <v>219.27099999999999</v>
-      </c>
-      <c r="GS5" s="0">
-        <v>108.066</v>
-      </c>
-      <c r="GT5" s="0">
-        <v>205.83000000000001</v>
-      </c>
-      <c r="GU5" s="0">
-        <v>102.258</v>
-      </c>
-      <c r="GV5" s="0">
-        <v>219.96899999999999</v>
-      </c>
-      <c r="GW5" s="0">
-        <v>116.55500000000001</v>
-      </c>
-      <c r="GX5" s="0">
-        <v>25.559000000000001</v>
-      </c>
-      <c r="GY5" s="0">
-        <v>86.963999999999999</v>
-      </c>
-      <c r="GZ5" s="0">
-        <v>191.67500000000001</v>
-      </c>
-      <c r="HA5" s="0">
-        <v>85.646000000000001</v>
-      </c>
-      <c r="HB5" s="0">
-        <v>199.25800000000001</v>
-      </c>
-      <c r="HC5" s="0">
-        <v>72.022000000000006</v>
-      </c>
-      <c r="HD5" s="0">
-        <v>156.54499999999999</v>
-      </c>
-      <c r="HE5" s="0">
-        <v>93.224999999999994</v>
-      </c>
-      <c r="HF5" s="0">
-        <v>181.77099999999999</v>
-      </c>
-      <c r="HG5" s="0">
-        <v>80.013999999999996</v>
-      </c>
-      <c r="HH5" s="0">
-        <v>179.57499999999999</v>
-      </c>
-      <c r="HI5" s="0">
-        <v>86.100999999999999</v>
-      </c>
-      <c r="HJ5" s="0">
-        <v>183.35599999999999</v>
-      </c>
-      <c r="HK5" s="0">
-        <v>91.451999999999998</v>
-      </c>
-      <c r="HL5" s="0">
-        <v>48.191000000000003</v>
-      </c>
-      <c r="HM5" s="0">
-        <v>18.483000000000001</v>
-      </c>
-      <c r="HN5" s="0">
-        <v>40.604999999999997</v>
-      </c>
-      <c r="HO5" s="0">
-        <v>14.720000000000001</v>
-      </c>
-      <c r="HP5" s="0">
-        <v>38.765000000000001</v>
-      </c>
-      <c r="HQ5" s="0">
-        <v>10.353999999999999</v>
-      </c>
-      <c r="HR5" s="0">
-        <v>47.972000000000001</v>
-      </c>
-      <c r="HS5" s="0">
-        <v>16.861999999999998</v>
-      </c>
-      <c r="HT5" s="0">
-        <v>40.171999999999997</v>
-      </c>
-      <c r="HU5" s="0">
-        <v>8.0239999999999991</v>
-      </c>
-      <c r="HV5" s="0">
-        <v>42.055999999999997</v>
-      </c>
-      <c r="HW5" s="0">
-        <v>20.105</v>
-      </c>
-      <c r="HX5" s="0">
-        <v>9.6379999999999999</v>
       </c>
       <c r="HY5" s="0">
         <v>76.887</v>
@@ -7055,82 +7055,82 @@
         <v>46.328000000000003</v>
       </c>
       <c r="IY5" s="0">
+        <v>32.087000000000003</v>
+      </c>
+      <c r="IZ5" s="0">
+        <v>25.215</v>
+      </c>
+      <c r="JA5" s="0">
+        <v>34.680999999999997</v>
+      </c>
+      <c r="JB5" s="0">
+        <v>17.309999999999999</v>
+      </c>
+      <c r="JC5" s="0">
+        <v>37.713000000000001</v>
+      </c>
+      <c r="JD5" s="0">
+        <v>8.048</v>
+      </c>
+      <c r="JE5" s="0">
+        <v>34.615000000000002</v>
+      </c>
+      <c r="JF5" s="0">
+        <v>25.053999999999998</v>
+      </c>
+      <c r="JG5" s="0">
+        <v>34.231999999999999</v>
+      </c>
+      <c r="JH5" s="0">
+        <v>9.9299999999999997</v>
+      </c>
+      <c r="JI5" s="0">
+        <v>26.527999999999999</v>
+      </c>
+      <c r="JJ5" s="0">
+        <v>18.734999999999999</v>
+      </c>
+      <c r="JK5" s="0">
+        <v>26.466000000000001</v>
+      </c>
+      <c r="JL5" s="0">
         <v>71.421000000000006</v>
       </c>
-      <c r="IZ5" s="0">
+      <c r="JM5" s="0">
         <v>98.759</v>
       </c>
-      <c r="JA5" s="0">
+      <c r="JN5" s="0">
         <v>66.176000000000002</v>
       </c>
-      <c r="JB5" s="0">
+      <c r="JO5" s="0">
         <v>96.034999999999997</v>
       </c>
-      <c r="JC5" s="0">
+      <c r="JP5" s="0">
         <v>47.040999999999997</v>
       </c>
-      <c r="JD5" s="0">
+      <c r="JQ5" s="0">
         <v>85.790999999999997</v>
       </c>
-      <c r="JE5" s="0">
+      <c r="JR5" s="0">
         <v>76.016000000000005</v>
       </c>
-      <c r="JF5" s="0">
+      <c r="JS5" s="0">
         <v>107.123</v>
       </c>
-      <c r="JG5" s="0">
+      <c r="JT5" s="0">
         <v>61.228999999999999</v>
       </c>
-      <c r="JH5" s="0">
+      <c r="JU5" s="0">
         <v>89.218999999999994</v>
       </c>
-      <c r="JI5" s="0">
+      <c r="JV5" s="0">
         <v>63.226999999999997</v>
       </c>
-      <c r="JJ5" s="0">
+      <c r="JW5" s="0">
         <v>105.837</v>
       </c>
-      <c r="JK5" s="0">
+      <c r="JX5" s="0">
         <v>72.522000000000006</v>
-      </c>
-      <c r="JL5" s="0">
-        <v>32.087000000000003</v>
-      </c>
-      <c r="JM5" s="0">
-        <v>25.215</v>
-      </c>
-      <c r="JN5" s="0">
-        <v>34.680999999999997</v>
-      </c>
-      <c r="JO5" s="0">
-        <v>17.309999999999999</v>
-      </c>
-      <c r="JP5" s="0">
-        <v>37.713000000000001</v>
-      </c>
-      <c r="JQ5" s="0">
-        <v>8.048</v>
-      </c>
-      <c r="JR5" s="0">
-        <v>34.615000000000002</v>
-      </c>
-      <c r="JS5" s="0">
-        <v>25.053999999999998</v>
-      </c>
-      <c r="JT5" s="0">
-        <v>34.231999999999999</v>
-      </c>
-      <c r="JU5" s="0">
-        <v>9.9299999999999997</v>
-      </c>
-      <c r="JV5" s="0">
-        <v>26.527999999999999</v>
-      </c>
-      <c r="JW5" s="0">
-        <v>18.734999999999999</v>
-      </c>
-      <c r="JX5" s="0">
-        <v>26.466000000000001</v>
       </c>
       <c r="JY5" s="0">
         <v>31.074000000000002</v>
@@ -7948,199 +7948,199 @@
         <v>-10.992000000000001</v>
       </c>
       <c r="FL6" s="0">
+        <v>52.591999999999999</v>
+      </c>
+      <c r="FM6" s="0">
+        <v>15.592000000000001</v>
+      </c>
+      <c r="FN6" s="0">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="FO6" s="0">
+        <v>28.087</v>
+      </c>
+      <c r="FP6" s="0">
+        <v>43.286999999999999</v>
+      </c>
+      <c r="FQ6" s="0">
+        <v>16.184999999999999</v>
+      </c>
+      <c r="FR6" s="0">
+        <v>72.320999999999998</v>
+      </c>
+      <c r="FS6" s="0">
+        <v>29.725999999999999</v>
+      </c>
+      <c r="FT6" s="0">
+        <v>60.673999999999999</v>
+      </c>
+      <c r="FU6" s="0">
+        <v>17.962</v>
+      </c>
+      <c r="FV6" s="0">
+        <v>44.462000000000003</v>
+      </c>
+      <c r="FW6" s="0">
+        <v>17.004999999999999</v>
+      </c>
+      <c r="FX6" s="0">
+        <v>17.030999999999999</v>
+      </c>
+      <c r="FY6" s="0">
+        <v>46.253</v>
+      </c>
+      <c r="FZ6" s="0">
+        <v>45.417999999999999</v>
+      </c>
+      <c r="GA6" s="0">
+        <v>47.582000000000001</v>
+      </c>
+      <c r="GB6" s="0">
+        <v>54.777999999999999</v>
+      </c>
+      <c r="GC6" s="0">
+        <v>59.978000000000002</v>
+      </c>
+      <c r="GD6" s="0">
+        <v>100.916</v>
+      </c>
+      <c r="GE6" s="0">
+        <v>53.863999999999997</v>
+      </c>
+      <c r="GF6" s="0">
+        <v>45.564999999999998</v>
+      </c>
+      <c r="GG6" s="0">
+        <v>83.001999999999995</v>
+      </c>
+      <c r="GH6" s="0">
+        <v>62.915999999999997</v>
+      </c>
+      <c r="GI6" s="0">
+        <v>62.045000000000002</v>
+      </c>
+      <c r="GJ6" s="0">
+        <v>64.334000000000003</v>
+      </c>
+      <c r="GK6" s="0">
+        <v>23.649000000000001</v>
+      </c>
+      <c r="GL6" s="0">
+        <v>43.146000000000001</v>
+      </c>
+      <c r="GM6" s="0">
+        <v>51.798000000000002</v>
+      </c>
+      <c r="GN6" s="0">
+        <v>24.353000000000002</v>
+      </c>
+      <c r="GO6" s="0">
+        <v>82.629000000000005</v>
+      </c>
+      <c r="GP6" s="0">
+        <v>40.104999999999997</v>
+      </c>
+      <c r="GQ6" s="0">
+        <v>125.105</v>
+      </c>
+      <c r="GR6" s="0">
+        <v>43.231000000000002</v>
+      </c>
+      <c r="GS6" s="0">
+        <v>57.558999999999997</v>
+      </c>
+      <c r="GT6" s="0">
+        <v>48.689999999999998</v>
+      </c>
+      <c r="GU6" s="0">
+        <v>70.418000000000006</v>
+      </c>
+      <c r="GV6" s="0">
+        <v>41.518000000000001</v>
+      </c>
+      <c r="GW6" s="0">
+        <v>102.794</v>
+      </c>
+      <c r="GX6" s="0">
+        <v>42.185000000000002</v>
+      </c>
+      <c r="GY6" s="0">
+        <v>8.0809999999999995</v>
+      </c>
+      <c r="GZ6" s="0">
+        <v>5.7279999999999998</v>
+      </c>
+      <c r="HA6" s="0">
+        <v>19.678999999999998</v>
+      </c>
+      <c r="HB6" s="0">
+        <v>4.8419999999999996</v>
+      </c>
+      <c r="HC6" s="0">
+        <v>16.884</v>
+      </c>
+      <c r="HD6" s="0">
+        <v>0.71399999999999997</v>
+      </c>
+      <c r="HE6" s="0">
+        <v>10.787000000000001</v>
+      </c>
+      <c r="HF6" s="0">
+        <v>3.7370000000000001</v>
+      </c>
+      <c r="HG6" s="0">
+        <v>17.177</v>
+      </c>
+      <c r="HH6" s="0">
+        <v>5.593</v>
+      </c>
+      <c r="HI6" s="0">
+        <v>15.755000000000001</v>
+      </c>
+      <c r="HJ6" s="0">
+        <v>2.4260000000000002</v>
+      </c>
+      <c r="HK6" s="0">
+        <v>4.0720000000000001</v>
+      </c>
+      <c r="HL6" s="0">
         <v>73.332999999999998</v>
       </c>
-      <c r="FM6" s="0">
+      <c r="HM6" s="0">
         <v>98.673000000000002</v>
       </c>
-      <c r="FN6" s="0">
+      <c r="HN6" s="0">
         <v>70.409000000000006</v>
       </c>
-      <c r="FO6" s="0">
+      <c r="HO6" s="0">
         <v>105.379</v>
       </c>
-      <c r="FP6" s="0">
+      <c r="HP6" s="0">
         <v>70.269999999999996</v>
       </c>
-      <c r="FQ6" s="0">
+      <c r="HQ6" s="0">
         <v>113.98399999999999</v>
       </c>
-      <c r="FR6" s="0">
+      <c r="HR6" s="0">
         <v>63.613999999999997</v>
       </c>
-      <c r="FS6" s="0">
+      <c r="HS6" s="0">
         <v>102.381</v>
       </c>
-      <c r="FT6" s="0">
+      <c r="HT6" s="0">
         <v>68.230999999999995</v>
       </c>
-      <c r="FU6" s="0">
+      <c r="HU6" s="0">
         <v>112.286</v>
       </c>
-      <c r="FV6" s="0">
+      <c r="HV6" s="0">
         <v>68.429000000000002</v>
       </c>
-      <c r="FW6" s="0">
+      <c r="HW6" s="0">
         <v>105.087</v>
       </c>
-      <c r="FX6" s="0">
+      <c r="HX6" s="0">
         <v>87.650999999999996</v>
-      </c>
-      <c r="FY6" s="0">
-        <v>52.591999999999999</v>
-      </c>
-      <c r="FZ6" s="0">
-        <v>15.592000000000001</v>
-      </c>
-      <c r="GA6" s="0">
-        <v>39.700000000000003</v>
-      </c>
-      <c r="GB6" s="0">
-        <v>28.087</v>
-      </c>
-      <c r="GC6" s="0">
-        <v>43.286999999999999</v>
-      </c>
-      <c r="GD6" s="0">
-        <v>16.184999999999999</v>
-      </c>
-      <c r="GE6" s="0">
-        <v>72.320999999999998</v>
-      </c>
-      <c r="GF6" s="0">
-        <v>29.725999999999999</v>
-      </c>
-      <c r="GG6" s="0">
-        <v>60.673999999999999</v>
-      </c>
-      <c r="GH6" s="0">
-        <v>17.962</v>
-      </c>
-      <c r="GI6" s="0">
-        <v>44.462000000000003</v>
-      </c>
-      <c r="GJ6" s="0">
-        <v>17.004999999999999</v>
-      </c>
-      <c r="GK6" s="0">
-        <v>17.030999999999999</v>
-      </c>
-      <c r="GL6" s="0">
-        <v>46.253</v>
-      </c>
-      <c r="GM6" s="0">
-        <v>45.417999999999999</v>
-      </c>
-      <c r="GN6" s="0">
-        <v>47.582000000000001</v>
-      </c>
-      <c r="GO6" s="0">
-        <v>54.777999999999999</v>
-      </c>
-      <c r="GP6" s="0">
-        <v>59.978000000000002</v>
-      </c>
-      <c r="GQ6" s="0">
-        <v>100.916</v>
-      </c>
-      <c r="GR6" s="0">
-        <v>53.863999999999997</v>
-      </c>
-      <c r="GS6" s="0">
-        <v>45.564999999999998</v>
-      </c>
-      <c r="GT6" s="0">
-        <v>83.001999999999995</v>
-      </c>
-      <c r="GU6" s="0">
-        <v>62.915999999999997</v>
-      </c>
-      <c r="GV6" s="0">
-        <v>62.045000000000002</v>
-      </c>
-      <c r="GW6" s="0">
-        <v>64.334000000000003</v>
-      </c>
-      <c r="GX6" s="0">
-        <v>23.649000000000001</v>
-      </c>
-      <c r="GY6" s="0">
-        <v>43.146000000000001</v>
-      </c>
-      <c r="GZ6" s="0">
-        <v>51.798000000000002</v>
-      </c>
-      <c r="HA6" s="0">
-        <v>24.353000000000002</v>
-      </c>
-      <c r="HB6" s="0">
-        <v>82.629000000000005</v>
-      </c>
-      <c r="HC6" s="0">
-        <v>40.104999999999997</v>
-      </c>
-      <c r="HD6" s="0">
-        <v>125.105</v>
-      </c>
-      <c r="HE6" s="0">
-        <v>43.231000000000002</v>
-      </c>
-      <c r="HF6" s="0">
-        <v>57.558999999999997</v>
-      </c>
-      <c r="HG6" s="0">
-        <v>48.689999999999998</v>
-      </c>
-      <c r="HH6" s="0">
-        <v>70.418000000000006</v>
-      </c>
-      <c r="HI6" s="0">
-        <v>41.518000000000001</v>
-      </c>
-      <c r="HJ6" s="0">
-        <v>102.794</v>
-      </c>
-      <c r="HK6" s="0">
-        <v>42.185000000000002</v>
-      </c>
-      <c r="HL6" s="0">
-        <v>8.0809999999999995</v>
-      </c>
-      <c r="HM6" s="0">
-        <v>5.7279999999999998</v>
-      </c>
-      <c r="HN6" s="0">
-        <v>19.678999999999998</v>
-      </c>
-      <c r="HO6" s="0">
-        <v>4.8419999999999996</v>
-      </c>
-      <c r="HP6" s="0">
-        <v>16.884</v>
-      </c>
-      <c r="HQ6" s="0">
-        <v>0.71399999999999997</v>
-      </c>
-      <c r="HR6" s="0">
-        <v>10.787000000000001</v>
-      </c>
-      <c r="HS6" s="0">
-        <v>3.7370000000000001</v>
-      </c>
-      <c r="HT6" s="0">
-        <v>17.177</v>
-      </c>
-      <c r="HU6" s="0">
-        <v>5.593</v>
-      </c>
-      <c r="HV6" s="0">
-        <v>15.755000000000001</v>
-      </c>
-      <c r="HW6" s="0">
-        <v>2.4260000000000002</v>
-      </c>
-      <c r="HX6" s="0">
-        <v>4.0720000000000001</v>
       </c>
       <c r="HY6" s="0">
         <v>50.329000000000001</v>
@@ -8221,82 +8221,82 @@
         <v>49.222999999999999</v>
       </c>
       <c r="IY6" s="0">
+        <v>23.974</v>
+      </c>
+      <c r="IZ6" s="0">
+        <v>19.75</v>
+      </c>
+      <c r="JA6" s="0">
+        <v>25.155000000000001</v>
+      </c>
+      <c r="JB6" s="0">
+        <v>17.797999999999998</v>
+      </c>
+      <c r="JC6" s="0">
+        <v>21.887</v>
+      </c>
+      <c r="JD6" s="0">
+        <v>20.462</v>
+      </c>
+      <c r="JE6" s="0">
+        <v>25.282</v>
+      </c>
+      <c r="JF6" s="0">
+        <v>18.096</v>
+      </c>
+      <c r="JG6" s="0">
+        <v>23.638999999999999</v>
+      </c>
+      <c r="JH6" s="0">
+        <v>19.84</v>
+      </c>
+      <c r="JI6" s="0">
+        <v>25.524999999999999</v>
+      </c>
+      <c r="JJ6" s="0">
+        <v>23.524999999999999</v>
+      </c>
+      <c r="JK6" s="0">
+        <v>26.821999999999999</v>
+      </c>
+      <c r="JL6" s="0">
         <v>68.471999999999994</v>
       </c>
-      <c r="IZ6" s="0">
+      <c r="JM6" s="0">
         <v>80.201999999999998</v>
       </c>
-      <c r="JA6" s="0">
+      <c r="JN6" s="0">
         <v>70.274000000000001</v>
       </c>
-      <c r="JB6" s="0">
+      <c r="JO6" s="0">
         <v>91.069000000000003</v>
       </c>
-      <c r="JC6" s="0">
+      <c r="JP6" s="0">
         <v>70.125</v>
       </c>
-      <c r="JD6" s="0">
+      <c r="JQ6" s="0">
         <v>102.467</v>
       </c>
-      <c r="JE6" s="0">
+      <c r="JR6" s="0">
         <v>63.377000000000002</v>
       </c>
-      <c r="JF6" s="0">
+      <c r="JS6" s="0">
         <v>90.278999999999996</v>
       </c>
-      <c r="JG6" s="0">
+      <c r="JT6" s="0">
         <v>67.478999999999999</v>
       </c>
-      <c r="JH6" s="0">
+      <c r="JU6" s="0">
         <v>94.938000000000002</v>
       </c>
-      <c r="JI6" s="0">
+      <c r="JV6" s="0">
         <v>68.290000000000006</v>
       </c>
-      <c r="JJ6" s="0">
+      <c r="JW6" s="0">
         <v>96.316000000000003</v>
       </c>
-      <c r="JK6" s="0">
+      <c r="JX6" s="0">
         <v>65.030000000000001</v>
-      </c>
-      <c r="JL6" s="0">
-        <v>23.974</v>
-      </c>
-      <c r="JM6" s="0">
-        <v>19.75</v>
-      </c>
-      <c r="JN6" s="0">
-        <v>25.155000000000001</v>
-      </c>
-      <c r="JO6" s="0">
-        <v>17.797999999999998</v>
-      </c>
-      <c r="JP6" s="0">
-        <v>21.887</v>
-      </c>
-      <c r="JQ6" s="0">
-        <v>20.462</v>
-      </c>
-      <c r="JR6" s="0">
-        <v>25.282</v>
-      </c>
-      <c r="JS6" s="0">
-        <v>18.096</v>
-      </c>
-      <c r="JT6" s="0">
-        <v>23.638999999999999</v>
-      </c>
-      <c r="JU6" s="0">
-        <v>19.84</v>
-      </c>
-      <c r="JV6" s="0">
-        <v>25.524999999999999</v>
-      </c>
-      <c r="JW6" s="0">
-        <v>23.524999999999999</v>
-      </c>
-      <c r="JX6" s="0">
-        <v>26.821999999999999</v>
       </c>
       <c r="JY6" s="0">
         <v>4.8600000000000003</v>
@@ -9065,176 +9065,176 @@
       <c r="FK7" s="0">
         <v>-38.613</v>
       </c>
-      <c r="FL7" s="0">
-        <v>79.177000000000007</v>
-      </c>
-      <c r="FM7" s="0">
-        <v>91.659999999999997</v>
-      </c>
+      <c r="FL7" s="0"/>
+      <c r="FM7" s="0"/>
       <c r="FN7" s="0">
-        <v>89.373999999999995</v>
+        <v>76.933999999999997</v>
       </c>
       <c r="FO7" s="0">
-        <v>104.464</v>
-      </c>
-      <c r="FP7" s="0">
-        <v>87.381</v>
-      </c>
-      <c r="FQ7" s="0">
-        <v>117.218</v>
-      </c>
+        <v>42.774000000000001</v>
+      </c>
+      <c r="FP7" s="0"/>
+      <c r="FQ7" s="0"/>
       <c r="FR7" s="0">
-        <v>96.741</v>
+        <v>38.414999999999999</v>
       </c>
       <c r="FS7" s="0">
-        <v>101.40000000000001</v>
+        <v>30.053999999999998</v>
       </c>
       <c r="FT7" s="0">
-        <v>90.209000000000003</v>
+        <v>40.965000000000003</v>
       </c>
       <c r="FU7" s="0">
-        <v>104.8</v>
-      </c>
-      <c r="FV7" s="0">
-        <v>79.108000000000004</v>
-      </c>
-      <c r="FW7" s="0">
-        <v>120.661</v>
-      </c>
+        <v>29.837</v>
+      </c>
+      <c r="FV7" s="0"/>
+      <c r="FW7" s="0"/>
       <c r="FX7" s="0">
-        <v>80.947999999999993</v>
+        <v>13.313000000000001</v>
       </c>
       <c r="FY7" s="0"/>
       <c r="FZ7" s="0"/>
       <c r="GA7" s="0">
-        <v>76.933999999999997</v>
+        <v>84.745000000000005</v>
       </c>
       <c r="GB7" s="0">
-        <v>42.774000000000001</v>
+        <v>24.518000000000001</v>
       </c>
       <c r="GC7" s="0"/>
       <c r="GD7" s="0"/>
       <c r="GE7" s="0">
-        <v>38.414999999999999</v>
+        <v>40.372999999999998</v>
       </c>
       <c r="GF7" s="0">
-        <v>30.053999999999998</v>
+        <v>92.975999999999999</v>
       </c>
       <c r="GG7" s="0">
-        <v>40.965000000000003</v>
+        <v>81.939999999999998</v>
       </c>
       <c r="GH7" s="0">
-        <v>29.837</v>
+        <v>26.93</v>
       </c>
       <c r="GI7" s="0"/>
       <c r="GJ7" s="0"/>
       <c r="GK7" s="0">
-        <v>13.313000000000001</v>
-      </c>
-      <c r="GL7" s="0"/>
-      <c r="GM7" s="0"/>
+        <v>57.353000000000002</v>
+      </c>
+      <c r="GL7" s="0">
+        <v>23.550000000000001</v>
+      </c>
+      <c r="GM7" s="0">
+        <v>64.960999999999999</v>
+      </c>
       <c r="GN7" s="0">
-        <v>84.745000000000005</v>
+        <v>20.681000000000001</v>
       </c>
       <c r="GO7" s="0">
-        <v>24.518000000000001</v>
-      </c>
-      <c r="GP7" s="0"/>
-      <c r="GQ7" s="0"/>
+        <v>93.664000000000001</v>
+      </c>
+      <c r="GP7" s="0">
+        <v>19.437000000000001</v>
+      </c>
+      <c r="GQ7" s="0">
+        <v>111.271</v>
+      </c>
       <c r="GR7" s="0">
-        <v>40.372999999999998</v>
+        <v>46.180999999999997</v>
       </c>
       <c r="GS7" s="0">
-        <v>92.975999999999999</v>
+        <v>47.381</v>
       </c>
       <c r="GT7" s="0">
-        <v>81.939999999999998</v>
+        <v>20.347999999999999</v>
       </c>
       <c r="GU7" s="0">
-        <v>26.93</v>
-      </c>
-      <c r="GV7" s="0"/>
-      <c r="GW7" s="0"/>
+        <v>94.301000000000002</v>
+      </c>
+      <c r="GV7" s="0">
+        <v>51.011000000000003</v>
+      </c>
+      <c r="GW7" s="0">
+        <v>42.950000000000003</v>
+      </c>
       <c r="GX7" s="0">
-        <v>57.353000000000002</v>
+        <v>42.055</v>
       </c>
       <c r="GY7" s="0">
-        <v>23.550000000000001</v>
+        <v>6.7380000000000004</v>
       </c>
       <c r="GZ7" s="0">
-        <v>64.960999999999999</v>
+        <v>6.2510000000000003</v>
       </c>
       <c r="HA7" s="0">
-        <v>20.681000000000001</v>
+        <v>8.1379999999999999</v>
       </c>
       <c r="HB7" s="0">
-        <v>93.664000000000001</v>
+        <v>7.8150000000000004</v>
       </c>
       <c r="HC7" s="0">
-        <v>19.437000000000001</v>
+        <v>8.4969999999999999</v>
       </c>
       <c r="HD7" s="0">
-        <v>111.271</v>
+        <v>9.4550000000000001</v>
       </c>
       <c r="HE7" s="0">
-        <v>46.180999999999997</v>
+        <v>4.9340000000000002</v>
       </c>
       <c r="HF7" s="0">
-        <v>47.381</v>
+        <v>10.023</v>
       </c>
       <c r="HG7" s="0">
-        <v>20.347999999999999</v>
+        <v>7.0599999999999996</v>
       </c>
       <c r="HH7" s="0">
-        <v>94.301000000000002</v>
+        <v>8.6349999999999998</v>
       </c>
       <c r="HI7" s="0">
-        <v>51.011000000000003</v>
+        <v>2.073</v>
       </c>
       <c r="HJ7" s="0">
-        <v>42.950000000000003</v>
+        <v>8.3109999999999999</v>
       </c>
       <c r="HK7" s="0">
-        <v>42.055</v>
+        <v>4.7889999999999997</v>
       </c>
       <c r="HL7" s="0">
-        <v>6.7380000000000004</v>
+        <v>79.177000000000007</v>
       </c>
       <c r="HM7" s="0">
-        <v>6.2510000000000003</v>
+        <v>91.659999999999997</v>
       </c>
       <c r="HN7" s="0">
-        <v>8.1379999999999999</v>
+        <v>89.373999999999995</v>
       </c>
       <c r="HO7" s="0">
-        <v>7.8150000000000004</v>
+        <v>104.464</v>
       </c>
       <c r="HP7" s="0">
-        <v>8.4969999999999999</v>
+        <v>87.381</v>
       </c>
       <c r="HQ7" s="0">
-        <v>9.4550000000000001</v>
+        <v>117.218</v>
       </c>
       <c r="HR7" s="0">
-        <v>4.9340000000000002</v>
+        <v>96.741</v>
       </c>
       <c r="HS7" s="0">
-        <v>10.023</v>
+        <v>101.40000000000001</v>
       </c>
       <c r="HT7" s="0">
-        <v>7.0599999999999996</v>
+        <v>90.209000000000003</v>
       </c>
       <c r="HU7" s="0">
-        <v>8.6349999999999998</v>
+        <v>104.8</v>
       </c>
       <c r="HV7" s="0">
-        <v>2.073</v>
+        <v>79.108000000000004</v>
       </c>
       <c r="HW7" s="0">
-        <v>8.3109999999999999</v>
+        <v>120.661</v>
       </c>
       <c r="HX7" s="0">
-        <v>4.7889999999999997</v>
+        <v>80.947999999999993</v>
       </c>
       <c r="HY7" s="0"/>
       <c r="HZ7" s="0"/>
@@ -9303,82 +9303,82 @@
         <v>44.832000000000001</v>
       </c>
       <c r="IY7" s="0">
+        <v>28.260999999999999</v>
+      </c>
+      <c r="IZ7" s="0">
+        <v>22.626000000000001</v>
+      </c>
+      <c r="JA7" s="0">
+        <v>32.854999999999997</v>
+      </c>
+      <c r="JB7" s="0">
+        <v>19.338000000000001</v>
+      </c>
+      <c r="JC7" s="0">
+        <v>31.715</v>
+      </c>
+      <c r="JD7" s="0">
+        <v>23.201000000000001</v>
+      </c>
+      <c r="JE7" s="0">
+        <v>34.106000000000002</v>
+      </c>
+      <c r="JF7" s="0">
+        <v>25.530999999999999</v>
+      </c>
+      <c r="JG7" s="0">
+        <v>33.488999999999997</v>
+      </c>
+      <c r="JH7" s="0">
+        <v>20.614999999999998</v>
+      </c>
+      <c r="JI7" s="0">
+        <v>31.161999999999999</v>
+      </c>
+      <c r="JJ7" s="0">
+        <v>20.736999999999998</v>
+      </c>
+      <c r="JK7" s="0">
+        <v>22.780999999999999</v>
+      </c>
+      <c r="JL7" s="0">
         <v>53.695999999999998</v>
       </c>
-      <c r="IZ7" s="0">
+      <c r="JM7" s="0">
         <v>68.731999999999999</v>
       </c>
-      <c r="JA7" s="0">
+      <c r="JN7" s="0">
         <v>59.594000000000001</v>
       </c>
-      <c r="JB7" s="0">
+      <c r="JO7" s="0">
         <v>80.388000000000005</v>
       </c>
-      <c r="JC7" s="0">
+      <c r="JP7" s="0">
         <v>60.316000000000003</v>
       </c>
-      <c r="JD7" s="0">
+      <c r="JQ7" s="0">
         <v>88.989000000000004</v>
       </c>
-      <c r="JE7" s="0">
+      <c r="JR7" s="0">
         <v>64.212999999999994</v>
       </c>
-      <c r="JF7" s="0">
+      <c r="JS7" s="0">
         <v>75.233999999999995</v>
       </c>
-      <c r="JG7" s="0">
+      <c r="JT7" s="0">
         <v>62.500999999999998</v>
       </c>
-      <c r="JH7" s="0">
+      <c r="JU7" s="0">
         <v>80.992000000000004</v>
       </c>
-      <c r="JI7" s="0">
+      <c r="JV7" s="0">
         <v>58.585000000000001</v>
       </c>
-      <c r="JJ7" s="0">
+      <c r="JW7" s="0">
         <v>98.811000000000007</v>
       </c>
-      <c r="JK7" s="0">
+      <c r="JX7" s="0">
         <v>62.368000000000002</v>
-      </c>
-      <c r="JL7" s="0">
-        <v>28.260999999999999</v>
-      </c>
-      <c r="JM7" s="0">
-        <v>22.626000000000001</v>
-      </c>
-      <c r="JN7" s="0">
-        <v>32.854999999999997</v>
-      </c>
-      <c r="JO7" s="0">
-        <v>19.338000000000001</v>
-      </c>
-      <c r="JP7" s="0">
-        <v>31.715</v>
-      </c>
-      <c r="JQ7" s="0">
-        <v>23.201000000000001</v>
-      </c>
-      <c r="JR7" s="0">
-        <v>34.106000000000002</v>
-      </c>
-      <c r="JS7" s="0">
-        <v>25.530999999999999</v>
-      </c>
-      <c r="JT7" s="0">
-        <v>33.488999999999997</v>
-      </c>
-      <c r="JU7" s="0">
-        <v>20.614999999999998</v>
-      </c>
-      <c r="JV7" s="0">
-        <v>31.161999999999999</v>
-      </c>
-      <c r="JW7" s="0">
-        <v>20.736999999999998</v>
-      </c>
-      <c r="JX7" s="0">
-        <v>22.780999999999999</v>
       </c>
       <c r="JY7" s="0">
         <v>25.481000000000002</v>
@@ -10160,199 +10160,199 @@
         <v>-26.876999999999999</v>
       </c>
       <c r="FL8" s="0">
+        <v>27.963000000000001</v>
+      </c>
+      <c r="FM8" s="0">
+        <v>19.809999999999999</v>
+      </c>
+      <c r="FN8" s="0">
+        <v>37.607999999999997</v>
+      </c>
+      <c r="FO8" s="0">
+        <v>24.821000000000002</v>
+      </c>
+      <c r="FP8" s="0">
+        <v>55.807000000000002</v>
+      </c>
+      <c r="FQ8" s="0">
+        <v>14.382</v>
+      </c>
+      <c r="FR8" s="0">
+        <v>34.447000000000003</v>
+      </c>
+      <c r="FS8" s="0">
+        <v>17.748999999999999</v>
+      </c>
+      <c r="FT8" s="0">
+        <v>45.386000000000003</v>
+      </c>
+      <c r="FU8" s="0">
+        <v>15.535</v>
+      </c>
+      <c r="FV8" s="0">
+        <v>52.755000000000003</v>
+      </c>
+      <c r="FW8" s="0">
+        <v>10.398999999999999</v>
+      </c>
+      <c r="FX8" s="0">
+        <v>13.430999999999999</v>
+      </c>
+      <c r="FY8" s="0">
+        <v>25.451000000000001</v>
+      </c>
+      <c r="FZ8" s="0">
+        <v>63.639000000000003</v>
+      </c>
+      <c r="GA8" s="0">
+        <v>30.937999999999999</v>
+      </c>
+      <c r="GB8" s="0">
+        <v>96.144999999999996</v>
+      </c>
+      <c r="GC8" s="0">
+        <v>48.130000000000003</v>
+      </c>
+      <c r="GD8" s="0">
+        <v>86.280000000000001</v>
+      </c>
+      <c r="GE8" s="0">
+        <v>35.020000000000003</v>
+      </c>
+      <c r="GF8" s="0">
+        <v>79.206000000000003</v>
+      </c>
+      <c r="GG8" s="0">
+        <v>43.814</v>
+      </c>
+      <c r="GH8" s="0">
+        <v>83.394999999999996</v>
+      </c>
+      <c r="GI8" s="0">
+        <v>55.979999999999997</v>
+      </c>
+      <c r="GJ8" s="0">
+        <v>73.578999999999994</v>
+      </c>
+      <c r="GK8" s="0">
+        <v>20.401</v>
+      </c>
+      <c r="GL8" s="0">
+        <v>51.427999999999997</v>
+      </c>
+      <c r="GM8" s="0">
+        <v>79.715999999999994</v>
+      </c>
+      <c r="GN8" s="0">
+        <v>46.392000000000003</v>
+      </c>
+      <c r="GO8" s="0">
+        <v>100.23</v>
+      </c>
+      <c r="GP8" s="0">
+        <v>49.100000000000001</v>
+      </c>
+      <c r="GQ8" s="0">
+        <v>91.644000000000005</v>
+      </c>
+      <c r="GR8" s="0">
+        <v>48.267000000000003</v>
+      </c>
+      <c r="GS8" s="0">
+        <v>94.033000000000001</v>
+      </c>
+      <c r="GT8" s="0">
+        <v>41.810000000000002</v>
+      </c>
+      <c r="GU8" s="0">
+        <v>86.004999999999995</v>
+      </c>
+      <c r="GV8" s="0">
+        <v>50.902000000000001</v>
+      </c>
+      <c r="GW8" s="0">
+        <v>76.183000000000007</v>
+      </c>
+      <c r="GX8" s="0">
+        <v>62.838000000000001</v>
+      </c>
+      <c r="GY8" s="0">
+        <v>16.625</v>
+      </c>
+      <c r="GZ8" s="0">
+        <v>10.121</v>
+      </c>
+      <c r="HA8" s="0">
+        <v>14.401</v>
+      </c>
+      <c r="HB8" s="0">
+        <v>8.6159999999999997</v>
+      </c>
+      <c r="HC8" s="0">
+        <v>16.675999999999998</v>
+      </c>
+      <c r="HD8" s="0">
+        <v>7.6459999999999999</v>
+      </c>
+      <c r="HE8" s="0">
+        <v>17.59</v>
+      </c>
+      <c r="HF8" s="0">
+        <v>9.1069999999999993</v>
+      </c>
+      <c r="HG8" s="0">
+        <v>14.189</v>
+      </c>
+      <c r="HH8" s="0">
+        <v>9.6259999999999994</v>
+      </c>
+      <c r="HI8" s="0">
+        <v>14.539</v>
+      </c>
+      <c r="HJ8" s="0">
+        <v>11.102</v>
+      </c>
+      <c r="HK8" s="0">
+        <v>10.135999999999999</v>
+      </c>
+      <c r="HL8" s="0">
         <v>103.45399999999999</v>
       </c>
-      <c r="FM8" s="0">
+      <c r="HM8" s="0">
         <v>99.647000000000006</v>
       </c>
-      <c r="FN8" s="0">
+      <c r="HN8" s="0">
         <v>95.683000000000007</v>
       </c>
-      <c r="FO8" s="0">
+      <c r="HO8" s="0">
         <v>110.626</v>
       </c>
-      <c r="FP8" s="0">
+      <c r="HP8" s="0">
         <v>93.602999999999994</v>
       </c>
-      <c r="FQ8" s="0">
+      <c r="HQ8" s="0">
         <v>108.117</v>
       </c>
-      <c r="FR8" s="0">
+      <c r="HR8" s="0">
         <v>102.539</v>
       </c>
-      <c r="FS8" s="0">
+      <c r="HS8" s="0">
         <v>105.099</v>
       </c>
-      <c r="FT8" s="0">
+      <c r="HT8" s="0">
         <v>96.385000000000005</v>
       </c>
-      <c r="FU8" s="0">
+      <c r="HU8" s="0">
         <v>109.101</v>
       </c>
-      <c r="FV8" s="0">
+      <c r="HV8" s="0">
         <v>77.494</v>
       </c>
-      <c r="FW8" s="0">
+      <c r="HW8" s="0">
         <v>110.676</v>
       </c>
-      <c r="FX8" s="0">
+      <c r="HX8" s="0">
         <v>91.539000000000001</v>
-      </c>
-      <c r="FY8" s="0">
-        <v>27.963000000000001</v>
-      </c>
-      <c r="FZ8" s="0">
-        <v>19.809999999999999</v>
-      </c>
-      <c r="GA8" s="0">
-        <v>37.607999999999997</v>
-      </c>
-      <c r="GB8" s="0">
-        <v>24.821000000000002</v>
-      </c>
-      <c r="GC8" s="0">
-        <v>55.807000000000002</v>
-      </c>
-      <c r="GD8" s="0">
-        <v>14.382</v>
-      </c>
-      <c r="GE8" s="0">
-        <v>34.447000000000003</v>
-      </c>
-      <c r="GF8" s="0">
-        <v>17.748999999999999</v>
-      </c>
-      <c r="GG8" s="0">
-        <v>45.386000000000003</v>
-      </c>
-      <c r="GH8" s="0">
-        <v>15.535</v>
-      </c>
-      <c r="GI8" s="0">
-        <v>52.755000000000003</v>
-      </c>
-      <c r="GJ8" s="0">
-        <v>10.398999999999999</v>
-      </c>
-      <c r="GK8" s="0">
-        <v>13.430999999999999</v>
-      </c>
-      <c r="GL8" s="0">
-        <v>25.451000000000001</v>
-      </c>
-      <c r="GM8" s="0">
-        <v>63.639000000000003</v>
-      </c>
-      <c r="GN8" s="0">
-        <v>30.937999999999999</v>
-      </c>
-      <c r="GO8" s="0">
-        <v>96.144999999999996</v>
-      </c>
-      <c r="GP8" s="0">
-        <v>48.130000000000003</v>
-      </c>
-      <c r="GQ8" s="0">
-        <v>86.280000000000001</v>
-      </c>
-      <c r="GR8" s="0">
-        <v>35.020000000000003</v>
-      </c>
-      <c r="GS8" s="0">
-        <v>79.206000000000003</v>
-      </c>
-      <c r="GT8" s="0">
-        <v>43.814</v>
-      </c>
-      <c r="GU8" s="0">
-        <v>83.394999999999996</v>
-      </c>
-      <c r="GV8" s="0">
-        <v>55.979999999999997</v>
-      </c>
-      <c r="GW8" s="0">
-        <v>73.578999999999994</v>
-      </c>
-      <c r="GX8" s="0">
-        <v>20.401</v>
-      </c>
-      <c r="GY8" s="0">
-        <v>51.427999999999997</v>
-      </c>
-      <c r="GZ8" s="0">
-        <v>79.715999999999994</v>
-      </c>
-      <c r="HA8" s="0">
-        <v>46.392000000000003</v>
-      </c>
-      <c r="HB8" s="0">
-        <v>100.23</v>
-      </c>
-      <c r="HC8" s="0">
-        <v>49.100000000000001</v>
-      </c>
-      <c r="HD8" s="0">
-        <v>91.644000000000005</v>
-      </c>
-      <c r="HE8" s="0">
-        <v>48.267000000000003</v>
-      </c>
-      <c r="HF8" s="0">
-        <v>94.033000000000001</v>
-      </c>
-      <c r="HG8" s="0">
-        <v>41.810000000000002</v>
-      </c>
-      <c r="HH8" s="0">
-        <v>86.004999999999995</v>
-      </c>
-      <c r="HI8" s="0">
-        <v>50.902000000000001</v>
-      </c>
-      <c r="HJ8" s="0">
-        <v>76.183000000000007</v>
-      </c>
-      <c r="HK8" s="0">
-        <v>62.838000000000001</v>
-      </c>
-      <c r="HL8" s="0">
-        <v>16.625</v>
-      </c>
-      <c r="HM8" s="0">
-        <v>10.121</v>
-      </c>
-      <c r="HN8" s="0">
-        <v>14.401</v>
-      </c>
-      <c r="HO8" s="0">
-        <v>8.6159999999999997</v>
-      </c>
-      <c r="HP8" s="0">
-        <v>16.675999999999998</v>
-      </c>
-      <c r="HQ8" s="0">
-        <v>7.6459999999999999</v>
-      </c>
-      <c r="HR8" s="0">
-        <v>17.59</v>
-      </c>
-      <c r="HS8" s="0">
-        <v>9.1069999999999993</v>
-      </c>
-      <c r="HT8" s="0">
-        <v>14.189</v>
-      </c>
-      <c r="HU8" s="0">
-        <v>9.6259999999999994</v>
-      </c>
-      <c r="HV8" s="0">
-        <v>14.539</v>
-      </c>
-      <c r="HW8" s="0">
-        <v>11.102</v>
-      </c>
-      <c r="HX8" s="0">
-        <v>10.135999999999999</v>
       </c>
       <c r="HY8" s="0">
         <v>57.301000000000002</v>
@@ -10433,82 +10433,82 @@
         <v>48.023000000000003</v>
       </c>
       <c r="IY8" s="0">
+        <v>32.509</v>
+      </c>
+      <c r="IZ8" s="0">
+        <v>30.021000000000001</v>
+      </c>
+      <c r="JA8" s="0">
+        <v>30.012</v>
+      </c>
+      <c r="JB8" s="0">
+        <v>27.927</v>
+      </c>
+      <c r="JC8" s="0">
+        <v>29.158999999999999</v>
+      </c>
+      <c r="JD8" s="0">
+        <v>27.306000000000001</v>
+      </c>
+      <c r="JE8" s="0">
+        <v>33.159999999999997</v>
+      </c>
+      <c r="JF8" s="0">
+        <v>28.484999999999999</v>
+      </c>
+      <c r="JG8" s="0">
+        <v>32.750999999999998</v>
+      </c>
+      <c r="JH8" s="0">
+        <v>27.062999999999999</v>
+      </c>
+      <c r="JI8" s="0">
+        <v>29.338999999999999</v>
+      </c>
+      <c r="JJ8" s="0">
+        <v>26.727</v>
+      </c>
+      <c r="JK8" s="0">
+        <v>28.890999999999998</v>
+      </c>
+      <c r="JL8" s="0">
         <v>73.957999999999998</v>
       </c>
-      <c r="IZ8" s="0">
+      <c r="JM8" s="0">
         <v>77.040000000000006</v>
       </c>
-      <c r="JA8" s="0">
+      <c r="JN8" s="0">
         <v>69.915999999999997</v>
       </c>
-      <c r="JB8" s="0">
+      <c r="JO8" s="0">
         <v>87.811999999999998</v>
       </c>
-      <c r="JC8" s="0">
+      <c r="JP8" s="0">
         <v>73.917000000000002</v>
       </c>
-      <c r="JD8" s="0">
+      <c r="JQ8" s="0">
         <v>84.974000000000004</v>
       </c>
-      <c r="JE8" s="0">
+      <c r="JR8" s="0">
         <v>74.411000000000001</v>
       </c>
-      <c r="JF8" s="0">
+      <c r="JS8" s="0">
         <v>82.692999999999998</v>
       </c>
-      <c r="JG8" s="0">
+      <c r="JT8" s="0">
         <v>69.105000000000004</v>
       </c>
-      <c r="JH8" s="0">
+      <c r="JU8" s="0">
         <v>85.978999999999999</v>
       </c>
-      <c r="JI8" s="0">
+      <c r="JV8" s="0">
         <v>67.486999999999995</v>
       </c>
-      <c r="JJ8" s="0">
+      <c r="JW8" s="0">
         <v>85.265000000000001</v>
       </c>
-      <c r="JK8" s="0">
+      <c r="JX8" s="0">
         <v>67.834999999999994</v>
-      </c>
-      <c r="JL8" s="0">
-        <v>32.509</v>
-      </c>
-      <c r="JM8" s="0">
-        <v>30.021000000000001</v>
-      </c>
-      <c r="JN8" s="0">
-        <v>30.012</v>
-      </c>
-      <c r="JO8" s="0">
-        <v>27.927</v>
-      </c>
-      <c r="JP8" s="0">
-        <v>29.158999999999999</v>
-      </c>
-      <c r="JQ8" s="0">
-        <v>27.306000000000001</v>
-      </c>
-      <c r="JR8" s="0">
-        <v>33.159999999999997</v>
-      </c>
-      <c r="JS8" s="0">
-        <v>28.484999999999999</v>
-      </c>
-      <c r="JT8" s="0">
-        <v>32.750999999999998</v>
-      </c>
-      <c r="JU8" s="0">
-        <v>27.062999999999999</v>
-      </c>
-      <c r="JV8" s="0">
-        <v>29.338999999999999</v>
-      </c>
-      <c r="JW8" s="0">
-        <v>26.727</v>
-      </c>
-      <c r="JX8" s="0">
-        <v>28.890999999999998</v>
       </c>
       <c r="JY8" s="0">
         <v>29.495999999999999</v>
@@ -11326,199 +11326,199 @@
         <v>-7.3380000000000001</v>
       </c>
       <c r="FL9" s="0">
+        <v>74.119</v>
+      </c>
+      <c r="FM9" s="0">
+        <v>17.283999999999999</v>
+      </c>
+      <c r="FN9" s="0">
+        <v>47.679000000000002</v>
+      </c>
+      <c r="FO9" s="0">
+        <v>7.9290000000000003</v>
+      </c>
+      <c r="FP9" s="0">
+        <v>49.546999999999997</v>
+      </c>
+      <c r="FQ9" s="0">
+        <v>47.942999999999998</v>
+      </c>
+      <c r="FR9" s="0">
+        <v>50.475999999999999</v>
+      </c>
+      <c r="FS9" s="0">
+        <v>20.363</v>
+      </c>
+      <c r="FT9" s="0">
+        <v>52.076000000000001</v>
+      </c>
+      <c r="FU9" s="0">
+        <v>14.382</v>
+      </c>
+      <c r="FV9" s="0">
+        <v>27.178999999999998</v>
+      </c>
+      <c r="FW9" s="0">
+        <v>28.975000000000001</v>
+      </c>
+      <c r="FX9" s="0">
+        <v>21.59</v>
+      </c>
+      <c r="FY9" s="0">
+        <v>41.689999999999998</v>
+      </c>
+      <c r="FZ9" s="0">
+        <v>74.140000000000001</v>
+      </c>
+      <c r="GA9" s="0">
+        <v>65.850999999999999</v>
+      </c>
+      <c r="GB9" s="0">
+        <v>76.244</v>
+      </c>
+      <c r="GC9" s="0">
+        <v>57.780000000000001</v>
+      </c>
+      <c r="GD9" s="0">
+        <v>70.628</v>
+      </c>
+      <c r="GE9" s="0">
+        <v>50.832999999999998</v>
+      </c>
+      <c r="GF9" s="0">
+        <v>65.183999999999997</v>
+      </c>
+      <c r="GG9" s="0">
+        <v>74.489999999999995</v>
+      </c>
+      <c r="GH9" s="0">
+        <v>67.801000000000002</v>
+      </c>
+      <c r="GI9" s="0">
+        <v>63.472999999999999</v>
+      </c>
+      <c r="GJ9" s="0">
+        <v>72.076999999999998</v>
+      </c>
+      <c r="GK9" s="0">
+        <v>29.120999999999999</v>
+      </c>
+      <c r="GL9" s="0">
+        <v>74.853999999999999</v>
+      </c>
+      <c r="GM9" s="0">
+        <v>41.773000000000003</v>
+      </c>
+      <c r="GN9" s="0">
+        <v>42.880000000000003</v>
+      </c>
+      <c r="GO9" s="0">
+        <v>97.626999999999995</v>
+      </c>
+      <c r="GP9" s="0">
+        <v>60.405999999999999</v>
+      </c>
+      <c r="GQ9" s="0">
+        <v>64.278000000000006</v>
+      </c>
+      <c r="GR9" s="0">
+        <v>35.021000000000001</v>
+      </c>
+      <c r="GS9" s="0">
+        <v>84.221999999999994</v>
+      </c>
+      <c r="GT9" s="0">
+        <v>16.933</v>
+      </c>
+      <c r="GU9" s="0">
+        <v>130.65299999999999</v>
+      </c>
+      <c r="GV9" s="0">
+        <v>38.646000000000001</v>
+      </c>
+      <c r="GW9" s="0">
+        <v>114.292</v>
+      </c>
+      <c r="GX9" s="0">
+        <v>43.587000000000003</v>
+      </c>
+      <c r="GY9" s="0">
+        <v>7.5949999999999998</v>
+      </c>
+      <c r="GZ9" s="0">
+        <v>38.286999999999999</v>
+      </c>
+      <c r="HA9" s="0">
+        <v>8.3599999999999994</v>
+      </c>
+      <c r="HB9" s="0">
+        <v>14.672000000000001</v>
+      </c>
+      <c r="HC9" s="0">
+        <v>7.556</v>
+      </c>
+      <c r="HD9" s="0">
+        <v>19.199999999999999</v>
+      </c>
+      <c r="HE9" s="0">
+        <v>8.2300000000000004</v>
+      </c>
+      <c r="HF9" s="0">
+        <v>13.923999999999999</v>
+      </c>
+      <c r="HG9" s="0">
+        <v>12.819000000000001</v>
+      </c>
+      <c r="HH9" s="0">
+        <v>7.6550000000000002</v>
+      </c>
+      <c r="HI9" s="0">
+        <v>11.563000000000001</v>
+      </c>
+      <c r="HJ9" s="0">
+        <v>6.1100000000000003</v>
+      </c>
+      <c r="HK9" s="0">
+        <v>5.7400000000000002</v>
+      </c>
+      <c r="HL9" s="0">
         <v>97.927000000000007</v>
       </c>
-      <c r="FM9" s="0">
+      <c r="HM9" s="0">
         <v>106.947</v>
       </c>
-      <c r="FN9" s="0">
+      <c r="HN9" s="0">
         <v>75.566000000000003</v>
       </c>
-      <c r="FO9" s="0">
+      <c r="HO9" s="0">
         <v>134.54599999999999</v>
       </c>
-      <c r="FP9" s="0">
+      <c r="HP9" s="0">
         <v>77.903999999999996</v>
       </c>
-      <c r="FQ9" s="0">
+      <c r="HQ9" s="0">
         <v>123.95099999999999</v>
       </c>
-      <c r="FR9" s="0">
+      <c r="HR9" s="0">
         <v>82.677999999999997</v>
       </c>
-      <c r="FS9" s="0">
+      <c r="HS9" s="0">
         <v>123.93000000000001</v>
       </c>
-      <c r="FT9" s="0">
+      <c r="HT9" s="0">
         <v>85.866</v>
       </c>
-      <c r="FU9" s="0">
+      <c r="HU9" s="0">
         <v>134.67699999999999</v>
       </c>
-      <c r="FV9" s="0">
+      <c r="HV9" s="0">
         <v>92.688000000000002</v>
       </c>
-      <c r="FW9" s="0">
+      <c r="HW9" s="0">
         <v>128.714</v>
       </c>
-      <c r="FX9" s="0">
+      <c r="HX9" s="0">
         <v>78.497</v>
-      </c>
-      <c r="FY9" s="0">
-        <v>74.119</v>
-      </c>
-      <c r="FZ9" s="0">
-        <v>17.283999999999999</v>
-      </c>
-      <c r="GA9" s="0">
-        <v>47.679000000000002</v>
-      </c>
-      <c r="GB9" s="0">
-        <v>7.9290000000000003</v>
-      </c>
-      <c r="GC9" s="0">
-        <v>49.546999999999997</v>
-      </c>
-      <c r="GD9" s="0">
-        <v>47.942999999999998</v>
-      </c>
-      <c r="GE9" s="0">
-        <v>50.475999999999999</v>
-      </c>
-      <c r="GF9" s="0">
-        <v>20.363</v>
-      </c>
-      <c r="GG9" s="0">
-        <v>52.076000000000001</v>
-      </c>
-      <c r="GH9" s="0">
-        <v>14.382</v>
-      </c>
-      <c r="GI9" s="0">
-        <v>27.178999999999998</v>
-      </c>
-      <c r="GJ9" s="0">
-        <v>28.975000000000001</v>
-      </c>
-      <c r="GK9" s="0">
-        <v>21.59</v>
-      </c>
-      <c r="GL9" s="0">
-        <v>41.689999999999998</v>
-      </c>
-      <c r="GM9" s="0">
-        <v>74.140000000000001</v>
-      </c>
-      <c r="GN9" s="0">
-        <v>65.850999999999999</v>
-      </c>
-      <c r="GO9" s="0">
-        <v>76.244</v>
-      </c>
-      <c r="GP9" s="0">
-        <v>57.780000000000001</v>
-      </c>
-      <c r="GQ9" s="0">
-        <v>70.628</v>
-      </c>
-      <c r="GR9" s="0">
-        <v>50.832999999999998</v>
-      </c>
-      <c r="GS9" s="0">
-        <v>65.183999999999997</v>
-      </c>
-      <c r="GT9" s="0">
-        <v>74.489999999999995</v>
-      </c>
-      <c r="GU9" s="0">
-        <v>67.801000000000002</v>
-      </c>
-      <c r="GV9" s="0">
-        <v>63.472999999999999</v>
-      </c>
-      <c r="GW9" s="0">
-        <v>72.076999999999998</v>
-      </c>
-      <c r="GX9" s="0">
-        <v>29.120999999999999</v>
-      </c>
-      <c r="GY9" s="0">
-        <v>74.853999999999999</v>
-      </c>
-      <c r="GZ9" s="0">
-        <v>41.773000000000003</v>
-      </c>
-      <c r="HA9" s="0">
-        <v>42.880000000000003</v>
-      </c>
-      <c r="HB9" s="0">
-        <v>97.626999999999995</v>
-      </c>
-      <c r="HC9" s="0">
-        <v>60.405999999999999</v>
-      </c>
-      <c r="HD9" s="0">
-        <v>64.278000000000006</v>
-      </c>
-      <c r="HE9" s="0">
-        <v>35.021000000000001</v>
-      </c>
-      <c r="HF9" s="0">
-        <v>84.221999999999994</v>
-      </c>
-      <c r="HG9" s="0">
-        <v>16.933</v>
-      </c>
-      <c r="HH9" s="0">
-        <v>130.65299999999999</v>
-      </c>
-      <c r="HI9" s="0">
-        <v>38.646000000000001</v>
-      </c>
-      <c r="HJ9" s="0">
-        <v>114.292</v>
-      </c>
-      <c r="HK9" s="0">
-        <v>43.587000000000003</v>
-      </c>
-      <c r="HL9" s="0">
-        <v>7.5949999999999998</v>
-      </c>
-      <c r="HM9" s="0">
-        <v>38.286999999999999</v>
-      </c>
-      <c r="HN9" s="0">
-        <v>8.3599999999999994</v>
-      </c>
-      <c r="HO9" s="0">
-        <v>14.672000000000001</v>
-      </c>
-      <c r="HP9" s="0">
-        <v>7.556</v>
-      </c>
-      <c r="HQ9" s="0">
-        <v>19.199999999999999</v>
-      </c>
-      <c r="HR9" s="0">
-        <v>8.2300000000000004</v>
-      </c>
-      <c r="HS9" s="0">
-        <v>13.923999999999999</v>
-      </c>
-      <c r="HT9" s="0">
-        <v>12.819000000000001</v>
-      </c>
-      <c r="HU9" s="0">
-        <v>7.6550000000000002</v>
-      </c>
-      <c r="HV9" s="0">
-        <v>11.563000000000001</v>
-      </c>
-      <c r="HW9" s="0">
-        <v>6.1100000000000003</v>
-      </c>
-      <c r="HX9" s="0">
-        <v>5.7400000000000002</v>
       </c>
       <c r="HY9" s="0">
         <v>58.679000000000002</v>
@@ -11599,82 +11599,82 @@
         <v>44.396000000000001</v>
       </c>
       <c r="IY9" s="0">
+        <v>37.421999999999997</v>
+      </c>
+      <c r="IZ9" s="0">
+        <v>23.045000000000002</v>
+      </c>
+      <c r="JA9" s="0">
+        <v>32.186</v>
+      </c>
+      <c r="JB9" s="0">
+        <v>28.286000000000001</v>
+      </c>
+      <c r="JC9" s="0">
+        <v>32.963999999999999</v>
+      </c>
+      <c r="JD9" s="0">
+        <v>27.809999999999999</v>
+      </c>
+      <c r="JE9" s="0">
+        <v>30.288</v>
+      </c>
+      <c r="JF9" s="0">
+        <v>29.077999999999999</v>
+      </c>
+      <c r="JG9" s="0">
+        <v>38.057000000000002</v>
+      </c>
+      <c r="JH9" s="0">
+        <v>31.952000000000002</v>
+      </c>
+      <c r="JI9" s="0">
+        <v>42.57</v>
+      </c>
+      <c r="JJ9" s="0">
+        <v>26.562000000000001</v>
+      </c>
+      <c r="JK9" s="0">
+        <v>22.306000000000001</v>
+      </c>
+      <c r="JL9" s="0">
         <v>63.704000000000001</v>
       </c>
-      <c r="IZ9" s="0">
+      <c r="JM9" s="0">
         <v>88.067999999999998</v>
       </c>
-      <c r="JA9" s="0">
+      <c r="JN9" s="0">
         <v>53.893999999999998</v>
       </c>
-      <c r="JB9" s="0">
+      <c r="JO9" s="0">
         <v>110.29000000000001</v>
       </c>
-      <c r="JC9" s="0">
+      <c r="JP9" s="0">
         <v>59.442999999999998</v>
       </c>
-      <c r="JD9" s="0">
+      <c r="JQ9" s="0">
         <v>104.116</v>
       </c>
-      <c r="JE9" s="0">
+      <c r="JR9" s="0">
         <v>56.832000000000001</v>
       </c>
-      <c r="JF9" s="0">
+      <c r="JS9" s="0">
         <v>100.289</v>
       </c>
-      <c r="JG9" s="0">
+      <c r="JT9" s="0">
         <v>54.926000000000002</v>
       </c>
-      <c r="JH9" s="0">
+      <c r="JU9" s="0">
         <v>108.639</v>
       </c>
-      <c r="JI9" s="0">
+      <c r="JV9" s="0">
         <v>60.445999999999998</v>
       </c>
-      <c r="JJ9" s="0">
+      <c r="JW9" s="0">
         <v>108.422</v>
       </c>
-      <c r="JK9" s="0">
+      <c r="JX9" s="0">
         <v>61.777999999999999</v>
-      </c>
-      <c r="JL9" s="0">
-        <v>37.421999999999997</v>
-      </c>
-      <c r="JM9" s="0">
-        <v>23.045000000000002</v>
-      </c>
-      <c r="JN9" s="0">
-        <v>32.186</v>
-      </c>
-      <c r="JO9" s="0">
-        <v>28.286000000000001</v>
-      </c>
-      <c r="JP9" s="0">
-        <v>32.963999999999999</v>
-      </c>
-      <c r="JQ9" s="0">
-        <v>27.809999999999999</v>
-      </c>
-      <c r="JR9" s="0">
-        <v>30.288</v>
-      </c>
-      <c r="JS9" s="0">
-        <v>29.077999999999999</v>
-      </c>
-      <c r="JT9" s="0">
-        <v>38.057000000000002</v>
-      </c>
-      <c r="JU9" s="0">
-        <v>31.952000000000002</v>
-      </c>
-      <c r="JV9" s="0">
-        <v>42.57</v>
-      </c>
-      <c r="JW9" s="0">
-        <v>26.562000000000001</v>
-      </c>
-      <c r="JX9" s="0">
-        <v>22.306000000000001</v>
       </c>
       <c r="JY9" s="0">
         <v>34.222999999999999</v>
@@ -12436,167 +12436,167 @@
         <v>-39.613999999999997</v>
       </c>
       <c r="FL10" s="0">
-        <v>105.226</v>
+        <v>48.307000000000002</v>
       </c>
       <c r="FM10" s="0">
-        <v>117.872</v>
+        <v>52.783999999999999</v>
       </c>
       <c r="FN10" s="0">
-        <v>106.07899999999999</v>
+        <v>89.893000000000001</v>
       </c>
       <c r="FO10" s="0">
-        <v>126.59699999999999</v>
+        <v>35.911999999999999</v>
       </c>
       <c r="FP10" s="0">
-        <v>103.041</v>
+        <v>109.249</v>
       </c>
       <c r="FQ10" s="0">
-        <v>137.58600000000001</v>
-      </c>
-      <c r="FR10" s="0">
-        <v>109.121</v>
-      </c>
-      <c r="FS10" s="0">
-        <v>121.017</v>
-      </c>
+        <v>43.143999999999998</v>
+      </c>
+      <c r="FR10" s="0"/>
+      <c r="FS10" s="0"/>
       <c r="FT10" s="0">
-        <v>109.893</v>
+        <v>91.820999999999998</v>
       </c>
       <c r="FU10" s="0">
-        <v>136.768</v>
-      </c>
-      <c r="FV10" s="0">
-        <v>106.80800000000001</v>
-      </c>
-      <c r="FW10" s="0">
-        <v>139.86199999999999</v>
-      </c>
+        <v>42.048000000000002</v>
+      </c>
+      <c r="FV10" s="0"/>
+      <c r="FW10" s="0"/>
       <c r="FX10" s="0">
-        <v>95.778999999999996</v>
+        <v>18.175999999999998</v>
       </c>
       <c r="FY10" s="0">
-        <v>48.307000000000002</v>
+        <v>45.856999999999999</v>
       </c>
       <c r="FZ10" s="0">
-        <v>52.783999999999999</v>
+        <v>19.437000000000001</v>
       </c>
       <c r="GA10" s="0">
-        <v>89.893000000000001</v>
+        <v>58.088000000000001</v>
       </c>
       <c r="GB10" s="0">
-        <v>35.911999999999999</v>
+        <v>62.014000000000003</v>
       </c>
       <c r="GC10" s="0">
-        <v>109.249</v>
+        <v>67.991</v>
       </c>
       <c r="GD10" s="0">
-        <v>43.143999999999998</v>
+        <v>99.031000000000006</v>
       </c>
       <c r="GE10" s="0"/>
       <c r="GF10" s="0"/>
       <c r="GG10" s="0">
-        <v>91.820999999999998</v>
+        <v>56.25</v>
       </c>
       <c r="GH10" s="0">
-        <v>42.048000000000002</v>
+        <v>110.289</v>
       </c>
       <c r="GI10" s="0"/>
       <c r="GJ10" s="0"/>
       <c r="GK10" s="0">
-        <v>18.175999999999998</v>
+        <v>26.440000000000001</v>
       </c>
       <c r="GL10" s="0">
-        <v>45.856999999999999</v>
+        <v>40.063000000000002</v>
       </c>
       <c r="GM10" s="0">
-        <v>19.437000000000001</v>
+        <v>95.688000000000002</v>
       </c>
       <c r="GN10" s="0">
-        <v>58.088000000000001</v>
+        <v>54.356999999999999</v>
       </c>
       <c r="GO10" s="0">
-        <v>62.014000000000003</v>
+        <v>96.959999999999994</v>
       </c>
       <c r="GP10" s="0">
-        <v>67.991</v>
+        <v>54.887</v>
       </c>
       <c r="GQ10" s="0">
-        <v>99.031000000000006</v>
+        <v>143.21799999999999</v>
       </c>
       <c r="GR10" s="0"/>
       <c r="GS10" s="0"/>
       <c r="GT10" s="0">
-        <v>56.25</v>
+        <v>65.331000000000003</v>
       </c>
       <c r="GU10" s="0">
-        <v>110.289</v>
+        <v>133.11199999999999</v>
       </c>
       <c r="GV10" s="0"/>
       <c r="GW10" s="0"/>
       <c r="GX10" s="0">
-        <v>26.440000000000001</v>
+        <v>47.268999999999998</v>
       </c>
       <c r="GY10" s="0">
-        <v>40.063000000000002</v>
+        <v>57.130000000000003</v>
       </c>
       <c r="GZ10" s="0">
-        <v>95.688000000000002</v>
+        <v>36.421999999999997</v>
       </c>
       <c r="HA10" s="0">
-        <v>54.356999999999999</v>
+        <v>14.036</v>
       </c>
       <c r="HB10" s="0">
-        <v>96.959999999999994</v>
+        <v>16.489000000000001</v>
       </c>
       <c r="HC10" s="0">
-        <v>54.887</v>
+        <v>20.158000000000001</v>
       </c>
       <c r="HD10" s="0">
-        <v>143.21799999999999</v>
+        <v>27.550999999999998</v>
       </c>
       <c r="HE10" s="0"/>
       <c r="HF10" s="0"/>
       <c r="HG10" s="0">
-        <v>65.331000000000003</v>
+        <v>23.911000000000001</v>
       </c>
       <c r="HH10" s="0">
-        <v>133.11199999999999</v>
+        <v>29.908000000000001</v>
       </c>
       <c r="HI10" s="0"/>
       <c r="HJ10" s="0"/>
       <c r="HK10" s="0">
-        <v>47.268999999999998</v>
+        <v>11.474</v>
       </c>
       <c r="HL10" s="0">
-        <v>57.130000000000003</v>
+        <v>105.226</v>
       </c>
       <c r="HM10" s="0">
-        <v>36.421999999999997</v>
+        <v>117.872</v>
       </c>
       <c r="HN10" s="0">
-        <v>14.036</v>
+        <v>106.07899999999999</v>
       </c>
       <c r="HO10" s="0">
-        <v>16.489000000000001</v>
+        <v>126.59699999999999</v>
       </c>
       <c r="HP10" s="0">
-        <v>20.158000000000001</v>
+        <v>103.041</v>
       </c>
       <c r="HQ10" s="0">
-        <v>27.550999999999998</v>
-      </c>
-      <c r="HR10" s="0"/>
-      <c r="HS10" s="0"/>
+        <v>137.58600000000001</v>
+      </c>
+      <c r="HR10" s="0">
+        <v>109.121</v>
+      </c>
+      <c r="HS10" s="0">
+        <v>121.017</v>
+      </c>
       <c r="HT10" s="0">
-        <v>23.911000000000001</v>
+        <v>109.893</v>
       </c>
       <c r="HU10" s="0">
-        <v>29.908000000000001</v>
-      </c>
-      <c r="HV10" s="0"/>
-      <c r="HW10" s="0"/>
+        <v>136.768</v>
+      </c>
+      <c r="HV10" s="0">
+        <v>106.80800000000001</v>
+      </c>
+      <c r="HW10" s="0">
+        <v>139.86199999999999</v>
+      </c>
       <c r="HX10" s="0">
-        <v>11.474</v>
+        <v>95.778999999999996</v>
       </c>
       <c r="HY10" s="0">
         <v>54.886000000000003</v>
@@ -12677,82 +12677,82 @@
         <v>49.582000000000001</v>
       </c>
       <c r="IY10" s="0">
+        <v>29.719000000000001</v>
+      </c>
+      <c r="IZ10" s="0">
+        <v>27.433</v>
+      </c>
+      <c r="JA10" s="0">
+        <v>31.367000000000001</v>
+      </c>
+      <c r="JB10" s="0">
+        <v>25.699000000000002</v>
+      </c>
+      <c r="JC10" s="0">
+        <v>30.629000000000001</v>
+      </c>
+      <c r="JD10" s="0">
+        <v>24.613</v>
+      </c>
+      <c r="JE10" s="0">
+        <v>32.621000000000002</v>
+      </c>
+      <c r="JF10" s="0">
+        <v>26.774000000000001</v>
+      </c>
+      <c r="JG10" s="0">
+        <v>31.372</v>
+      </c>
+      <c r="JH10" s="0">
+        <v>25.216999999999999</v>
+      </c>
+      <c r="JI10" s="0">
+        <v>31.844999999999999</v>
+      </c>
+      <c r="JJ10" s="0">
+        <v>24.428000000000001</v>
+      </c>
+      <c r="JK10" s="0">
+        <v>28.937000000000001</v>
+      </c>
+      <c r="JL10" s="0">
         <v>71.040000000000006</v>
       </c>
-      <c r="IZ10" s="0">
+      <c r="JM10" s="0">
         <v>85.227999999999994</v>
       </c>
-      <c r="JA10" s="0">
+      <c r="JN10" s="0">
         <v>70.209000000000003</v>
       </c>
-      <c r="JB10" s="0">
+      <c r="JO10" s="0">
         <v>94.894999999999996</v>
       </c>
-      <c r="JC10" s="0">
+      <c r="JP10" s="0">
         <v>68.030000000000001</v>
       </c>
-      <c r="JD10" s="0">
+      <c r="JQ10" s="0">
         <v>104.479</v>
       </c>
-      <c r="JE10" s="0">
+      <c r="JR10" s="0">
         <v>72.853999999999999</v>
       </c>
-      <c r="JF10" s="0">
+      <c r="JS10" s="0">
         <v>87.971999999999994</v>
       </c>
-      <c r="JG10" s="0">
+      <c r="JT10" s="0">
         <v>74.722999999999999</v>
       </c>
-      <c r="JH10" s="0">
+      <c r="JU10" s="0">
         <v>103.04300000000001</v>
       </c>
-      <c r="JI10" s="0">
+      <c r="JV10" s="0">
         <v>70.325000000000003</v>
       </c>
-      <c r="JJ10" s="0">
+      <c r="JW10" s="0">
         <v>106.27</v>
       </c>
-      <c r="JK10" s="0">
+      <c r="JX10" s="0">
         <v>66.644999999999996</v>
-      </c>
-      <c r="JL10" s="0">
-        <v>29.719000000000001</v>
-      </c>
-      <c r="JM10" s="0">
-        <v>27.433</v>
-      </c>
-      <c r="JN10" s="0">
-        <v>31.367000000000001</v>
-      </c>
-      <c r="JO10" s="0">
-        <v>25.699000000000002</v>
-      </c>
-      <c r="JP10" s="0">
-        <v>30.629000000000001</v>
-      </c>
-      <c r="JQ10" s="0">
-        <v>24.613</v>
-      </c>
-      <c r="JR10" s="0">
-        <v>32.621000000000002</v>
-      </c>
-      <c r="JS10" s="0">
-        <v>26.774000000000001</v>
-      </c>
-      <c r="JT10" s="0">
-        <v>31.372</v>
-      </c>
-      <c r="JU10" s="0">
-        <v>25.216999999999999</v>
-      </c>
-      <c r="JV10" s="0">
-        <v>31.844999999999999</v>
-      </c>
-      <c r="JW10" s="0">
-        <v>24.428000000000001</v>
-      </c>
-      <c r="JX10" s="0">
-        <v>28.937000000000001</v>
       </c>
       <c r="JY10" s="0">
         <v>34.186</v>

--- a/Results/Group Analysis/GroupCrossing_YoungAdults_SPSS.xlsx
+++ b/Results/Group Analysis/GroupCrossing_YoungAdults_SPSS.xlsx
@@ -2786,112 +2786,112 @@
         <v>101</v>
       </c>
       <c r="B2" s="0">
-        <v>149.80000000000001</v>
+        <v>14.98</v>
       </c>
       <c r="C2" s="0">
-        <v>127.101</v>
+        <v>12.710000000000001</v>
       </c>
       <c r="D2" s="0">
-        <v>78.162000000000006</v>
+        <v>7.8159999999999998</v>
       </c>
       <c r="E2" s="0">
-        <v>133.76599999999999</v>
+        <v>13.377000000000001</v>
       </c>
       <c r="F2" s="0">
-        <v>123.491</v>
+        <v>12.349</v>
       </c>
       <c r="G2" s="0">
-        <v>145.542</v>
+        <v>14.554</v>
       </c>
       <c r="H2" s="0">
-        <v>135.322</v>
+        <v>13.532</v>
       </c>
       <c r="I2" s="0">
-        <v>116.411</v>
+        <v>11.641</v>
       </c>
       <c r="J2" s="0">
-        <v>147.54400000000001</v>
+        <v>14.754</v>
       </c>
       <c r="K2" s="0">
-        <v>129.97800000000001</v>
+        <v>12.997999999999999</v>
       </c>
       <c r="L2" s="0">
-        <v>84.867999999999995</v>
+        <v>8.4870000000000001</v>
       </c>
       <c r="M2" s="0">
-        <v>138.43700000000001</v>
+        <v>13.843999999999999</v>
       </c>
       <c r="N2" s="0">
-        <v>701.35599999999999</v>
+        <v>70.135999999999996</v>
       </c>
       <c r="O2" s="0">
-        <v>818.30499999999995</v>
+        <v>81.829999999999998</v>
       </c>
       <c r="P2" s="0">
-        <v>747.02999999999997</v>
+        <v>74.703000000000003</v>
       </c>
       <c r="Q2" s="0">
-        <v>831.25999999999999</v>
+        <v>83.126000000000005</v>
       </c>
       <c r="R2" s="0">
-        <v>855.83299999999997</v>
+        <v>85.582999999999998</v>
       </c>
       <c r="S2" s="0">
-        <v>740.93499999999995</v>
+        <v>74.093000000000004</v>
       </c>
       <c r="T2" s="0">
-        <v>124.35899999999999</v>
+        <v>12.436</v>
       </c>
       <c r="U2" s="0">
-        <v>451.98899999999998</v>
+        <v>45.198999999999998</v>
       </c>
       <c r="V2" s="0">
-        <v>153.95099999999999</v>
+        <v>15.395</v>
       </c>
       <c r="W2" s="0">
-        <v>131.55000000000001</v>
+        <v>13.154999999999999</v>
       </c>
       <c r="X2" s="0">
-        <v>156.43100000000001</v>
+        <v>15.643000000000001</v>
       </c>
       <c r="Y2" s="0">
-        <v>169.45699999999999</v>
+        <v>16.946000000000002</v>
       </c>
       <c r="Z2" s="0">
-        <v>296.55599999999998</v>
+        <v>29.655999999999999</v>
       </c>
       <c r="AA2" s="0">
-        <v>260.892</v>
+        <v>26.088999999999999</v>
       </c>
       <c r="AB2" s="0">
-        <v>263.435</v>
+        <v>26.343</v>
       </c>
       <c r="AC2" s="0">
-        <v>177.15100000000001</v>
+        <v>17.715</v>
       </c>
       <c r="AD2" s="0">
-        <v>213.06</v>
+        <v>21.306000000000001</v>
       </c>
       <c r="AE2" s="0">
-        <v>471.92599999999999</v>
+        <v>47.192999999999998</v>
       </c>
       <c r="AF2" s="0">
-        <v>1045.327</v>
+        <v>104.533</v>
       </c>
       <c r="AG2" s="0">
-        <v>1034.086</v>
+        <v>103.40900000000001</v>
       </c>
       <c r="AH2" s="0">
-        <v>1013.563</v>
+        <v>101.35599999999999</v>
       </c>
       <c r="AI2" s="0">
-        <v>949.67700000000002</v>
+        <v>94.968000000000004</v>
       </c>
       <c r="AJ2" s="0">
-        <v>741.34100000000001</v>
+        <v>74.134</v>
       </c>
       <c r="AK2" s="0">
-        <v>924.70399999999995</v>
+        <v>92.469999999999999</v>
       </c>
       <c r="AL2" s="0">
         <v>180.19900000000001</v>
@@ -3952,112 +3952,112 @@
         <v>102</v>
       </c>
       <c r="B3" s="0">
-        <v>257.31200000000001</v>
+        <v>25.731000000000002</v>
       </c>
       <c r="C3" s="0">
-        <v>259.14600000000002</v>
+        <v>25.914999999999999</v>
       </c>
       <c r="D3" s="0">
-        <v>282.78699999999998</v>
+        <v>28.279</v>
       </c>
       <c r="E3" s="0">
-        <v>241.85900000000001</v>
+        <v>24.186</v>
       </c>
       <c r="F3" s="0">
-        <v>277.49799999999999</v>
+        <v>27.75</v>
       </c>
       <c r="G3" s="0">
-        <v>249.697</v>
+        <v>24.969999999999999</v>
       </c>
       <c r="H3" s="0">
-        <v>165.29400000000001</v>
+        <v>16.529</v>
       </c>
       <c r="I3" s="0">
-        <v>154.762</v>
+        <v>15.476000000000001</v>
       </c>
       <c r="J3" s="0">
-        <v>105.063</v>
+        <v>10.506</v>
       </c>
       <c r="K3" s="0">
-        <v>201.857</v>
+        <v>20.186</v>
       </c>
       <c r="L3" s="0">
-        <v>113.852</v>
+        <v>11.385</v>
       </c>
       <c r="M3" s="0">
-        <v>93.292000000000002</v>
+        <v>9.3290000000000006</v>
       </c>
       <c r="N3" s="0">
-        <v>1045.6669999999999</v>
+        <v>104.56699999999999</v>
       </c>
       <c r="O3" s="0">
-        <v>1097.6859999999999</v>
+        <v>109.76900000000001</v>
       </c>
       <c r="P3" s="0">
-        <v>1085.075</v>
+        <v>108.50700000000001</v>
       </c>
       <c r="Q3" s="0">
-        <v>979.80999999999995</v>
+        <v>97.980999999999995</v>
       </c>
       <c r="R3" s="0">
-        <v>1067.8679999999999</v>
+        <v>106.78700000000001</v>
       </c>
       <c r="S3" s="0">
-        <v>1025.425</v>
+        <v>102.542</v>
       </c>
       <c r="T3" s="0">
-        <v>248.75299999999999</v>
+        <v>24.875</v>
       </c>
       <c r="U3" s="0">
-        <v>273.22399999999999</v>
+        <v>27.321999999999999</v>
       </c>
       <c r="V3" s="0">
-        <v>239.161</v>
+        <v>23.916</v>
       </c>
       <c r="W3" s="0">
-        <v>228.46799999999999</v>
+        <v>22.847000000000001</v>
       </c>
       <c r="X3" s="0">
-        <v>225.66499999999999</v>
+        <v>22.567</v>
       </c>
       <c r="Y3" s="0">
-        <v>209.15000000000001</v>
+        <v>20.914999999999999</v>
       </c>
       <c r="Z3" s="0">
-        <v>341.28699999999998</v>
+        <v>34.128999999999998</v>
       </c>
       <c r="AA3" s="0">
-        <v>298.50400000000002</v>
+        <v>29.850000000000001</v>
       </c>
       <c r="AB3" s="0">
-        <v>362.01900000000001</v>
+        <v>36.201999999999998</v>
       </c>
       <c r="AC3" s="0">
-        <v>249.28899999999999</v>
+        <v>24.928999999999998</v>
       </c>
       <c r="AD3" s="0">
-        <v>265.863</v>
+        <v>26.585999999999999</v>
       </c>
       <c r="AE3" s="0">
-        <v>282.983</v>
+        <v>28.297999999999998</v>
       </c>
       <c r="AF3" s="0">
-        <v>1093.002</v>
+        <v>109.3</v>
       </c>
       <c r="AG3" s="0">
-        <v>1116.2729999999999</v>
+        <v>111.627</v>
       </c>
       <c r="AH3" s="0">
-        <v>1155.825</v>
+        <v>115.583</v>
       </c>
       <c r="AI3" s="0">
-        <v>1021.275</v>
+        <v>102.128</v>
       </c>
       <c r="AJ3" s="0">
-        <v>1058.5740000000001</v>
+        <v>105.857</v>
       </c>
       <c r="AK3" s="0">
-        <v>1089.634</v>
+        <v>108.96299999999999</v>
       </c>
       <c r="AL3" s="0">
         <v>176.28999999999999</v>
@@ -5118,112 +5118,112 @@
         <v>103</v>
       </c>
       <c r="B4" s="0">
-        <v>219.31899999999999</v>
+        <v>21.931999999999999</v>
       </c>
       <c r="C4" s="0">
-        <v>180.86799999999999</v>
+        <v>18.087</v>
       </c>
       <c r="D4" s="0">
-        <v>211.34899999999999</v>
+        <v>21.135000000000002</v>
       </c>
       <c r="E4" s="0">
-        <v>228.85499999999999</v>
+        <v>22.885999999999999</v>
       </c>
       <c r="F4" s="0">
-        <v>189.44499999999999</v>
+        <v>18.943999999999999</v>
       </c>
       <c r="G4" s="0">
-        <v>163.33699999999999</v>
+        <v>16.334</v>
       </c>
       <c r="H4" s="0">
-        <v>215.33600000000001</v>
+        <v>21.533999999999999</v>
       </c>
       <c r="I4" s="0">
-        <v>202.94900000000001</v>
+        <v>20.295000000000002</v>
       </c>
       <c r="J4" s="0">
-        <v>206.233</v>
+        <v>20.623000000000001</v>
       </c>
       <c r="K4" s="0">
-        <v>219.32300000000001</v>
+        <v>21.931999999999999</v>
       </c>
       <c r="L4" s="0">
-        <v>239.923</v>
+        <v>23.992000000000001</v>
       </c>
       <c r="M4" s="0">
-        <v>202.351</v>
+        <v>20.234999999999999</v>
       </c>
       <c r="N4" s="0">
-        <v>1042.5340000000001</v>
+        <v>104.253</v>
       </c>
       <c r="O4" s="0">
-        <v>1090.9739999999999</v>
+        <v>109.09699999999999</v>
       </c>
       <c r="P4" s="0">
-        <v>1021.191</v>
+        <v>102.119</v>
       </c>
       <c r="Q4" s="0">
-        <v>1200.1389999999999</v>
+        <v>120.014</v>
       </c>
       <c r="R4" s="0">
-        <v>994.11000000000001</v>
+        <v>99.411000000000001</v>
       </c>
       <c r="S4" s="0">
-        <v>1145.5119999999999</v>
+        <v>114.551</v>
       </c>
       <c r="T4" s="0">
-        <v>261.67599999999999</v>
+        <v>26.167999999999999</v>
       </c>
       <c r="U4" s="0">
-        <v>304.64999999999998</v>
+        <v>30.465</v>
       </c>
       <c r="V4" s="0">
-        <v>230.53100000000001</v>
+        <v>23.053000000000001</v>
       </c>
       <c r="W4" s="0">
-        <v>306.26600000000002</v>
+        <v>30.626999999999999</v>
       </c>
       <c r="X4" s="0">
-        <v>210.84</v>
+        <v>21.084</v>
       </c>
       <c r="Y4" s="0">
-        <v>296.18599999999998</v>
+        <v>29.619</v>
       </c>
       <c r="Z4" s="0">
-        <v>241.678</v>
+        <v>24.167999999999999</v>
       </c>
       <c r="AA4" s="0">
-        <v>278.79199999999997</v>
+        <v>27.879000000000001</v>
       </c>
       <c r="AB4" s="0">
-        <v>289.072</v>
+        <v>28.907</v>
       </c>
       <c r="AC4" s="0">
-        <v>221.63800000000001</v>
+        <v>22.164000000000001</v>
       </c>
       <c r="AD4" s="0">
-        <v>263.94400000000002</v>
+        <v>26.393999999999998</v>
       </c>
       <c r="AE4" s="0">
-        <v>198.88399999999999</v>
+        <v>19.888000000000002</v>
       </c>
       <c r="AF4" s="0">
-        <v>1021.0119999999999</v>
+        <v>102.101</v>
       </c>
       <c r="AG4" s="0">
-        <v>1093.326</v>
+        <v>109.333</v>
       </c>
       <c r="AH4" s="0">
-        <v>1145.2380000000001</v>
+        <v>114.524</v>
       </c>
       <c r="AI4" s="0">
-        <v>1053.9590000000001</v>
+        <v>105.396</v>
       </c>
       <c r="AJ4" s="0">
-        <v>1095.03</v>
+        <v>109.503</v>
       </c>
       <c r="AK4" s="0">
-        <v>1037.2329999999999</v>
+        <v>103.723</v>
       </c>
       <c r="AL4" s="0">
         <v>164.751</v>
@@ -6284,112 +6284,112 @@
         <v>104</v>
       </c>
       <c r="B5" s="0">
-        <v>191.58500000000001</v>
+        <v>19.158999999999999</v>
       </c>
       <c r="C5" s="0">
-        <v>202.702</v>
+        <v>20.27</v>
       </c>
       <c r="D5" s="0">
-        <v>193.55799999999999</v>
+        <v>19.356000000000002</v>
       </c>
       <c r="E5" s="0">
-        <v>146.75200000000001</v>
+        <v>14.675000000000001</v>
       </c>
       <c r="F5" s="0">
-        <v>199.709</v>
+        <v>19.971</v>
       </c>
       <c r="G5" s="0">
-        <v>182.85300000000001</v>
+        <v>18.285</v>
       </c>
       <c r="H5" s="0">
-        <v>308.78500000000003</v>
+        <v>30.879000000000001</v>
       </c>
       <c r="I5" s="0">
-        <v>333.892</v>
+        <v>33.389000000000003</v>
       </c>
       <c r="J5" s="0">
-        <v>263.29000000000002</v>
+        <v>26.329000000000001</v>
       </c>
       <c r="K5" s="0">
-        <v>261.57900000000001</v>
+        <v>26.158000000000001</v>
       </c>
       <c r="L5" s="0">
-        <v>297.85700000000003</v>
+        <v>29.786000000000001</v>
       </c>
       <c r="M5" s="0">
-        <v>307.69299999999998</v>
+        <v>30.768999999999998</v>
       </c>
       <c r="N5" s="0">
-        <v>681.59299999999996</v>
+        <v>68.159000000000006</v>
       </c>
       <c r="O5" s="0">
-        <v>718.81100000000004</v>
+        <v>71.881</v>
       </c>
       <c r="P5" s="0">
-        <v>514.07600000000002</v>
+        <v>51.408000000000001</v>
       </c>
       <c r="Q5" s="0">
-        <v>707.40800000000002</v>
+        <v>70.741</v>
       </c>
       <c r="R5" s="0">
-        <v>589.03899999999999</v>
+        <v>58.904000000000003</v>
       </c>
       <c r="S5" s="0">
-        <v>655.34400000000005</v>
+        <v>65.534000000000006</v>
       </c>
       <c r="T5" s="0">
-        <v>183.87799999999999</v>
+        <v>18.388000000000002</v>
       </c>
       <c r="U5" s="0">
-        <v>150.98099999999999</v>
+        <v>15.098000000000001</v>
       </c>
       <c r="V5" s="0">
-        <v>145.06100000000001</v>
+        <v>14.506</v>
       </c>
       <c r="W5" s="0">
-        <v>155.14099999999999</v>
+        <v>15.513999999999999</v>
       </c>
       <c r="X5" s="0">
-        <v>135.19499999999999</v>
+        <v>13.519</v>
       </c>
       <c r="Y5" s="0">
-        <v>111.051</v>
+        <v>11.105</v>
       </c>
       <c r="Z5" s="0">
-        <v>519.00400000000002</v>
+        <v>51.899999999999999</v>
       </c>
       <c r="AA5" s="0">
-        <v>209.666</v>
+        <v>20.966999999999999</v>
       </c>
       <c r="AB5" s="0">
-        <v>170.41499999999999</v>
+        <v>17.042000000000002</v>
       </c>
       <c r="AC5" s="0">
-        <v>464.36599999999999</v>
+        <v>46.436999999999998</v>
       </c>
       <c r="AD5" s="0">
-        <v>140.62299999999999</v>
+        <v>14.061999999999999</v>
       </c>
       <c r="AE5" s="0">
-        <v>47.326000000000001</v>
+        <v>4.7329999999999997</v>
       </c>
       <c r="AF5" s="0">
-        <v>945.69399999999996</v>
+        <v>94.569000000000003</v>
       </c>
       <c r="AG5" s="0">
-        <v>736.26599999999996</v>
+        <v>73.626999999999995</v>
       </c>
       <c r="AH5" s="0">
-        <v>481.43299999999999</v>
+        <v>48.143000000000001</v>
       </c>
       <c r="AI5" s="0">
-        <v>924.92899999999997</v>
+        <v>92.492999999999995</v>
       </c>
       <c r="AJ5" s="0">
-        <v>448.88400000000001</v>
+        <v>44.887999999999998</v>
       </c>
       <c r="AK5" s="0">
-        <v>777.40700000000004</v>
+        <v>77.741</v>
       </c>
       <c r="AL5" s="0">
         <v>156.81999999999999</v>
@@ -7450,112 +7450,112 @@
         <v>105</v>
       </c>
       <c r="B6" s="0">
-        <v>144.20699999999999</v>
+        <v>14.420999999999999</v>
       </c>
       <c r="C6" s="0">
-        <v>156.529</v>
+        <v>15.653</v>
       </c>
       <c r="D6" s="0">
-        <v>108.252</v>
+        <v>10.824999999999999</v>
       </c>
       <c r="E6" s="0">
-        <v>152.416</v>
+        <v>15.242000000000001</v>
       </c>
       <c r="F6" s="0">
-        <v>130.334</v>
+        <v>13.032999999999999</v>
       </c>
       <c r="G6" s="0">
-        <v>116.70399999999999</v>
+        <v>11.67</v>
       </c>
       <c r="H6" s="0">
-        <v>83.417000000000002</v>
+        <v>8.3420000000000005</v>
       </c>
       <c r="I6" s="0">
-        <v>115.16800000000001</v>
+        <v>11.516999999999999</v>
       </c>
       <c r="J6" s="0">
-        <v>135.47200000000001</v>
+        <v>13.547000000000001</v>
       </c>
       <c r="K6" s="0">
-        <v>119.733</v>
+        <v>11.973000000000001</v>
       </c>
       <c r="L6" s="0">
-        <v>60.098999999999997</v>
+        <v>6.0099999999999998</v>
       </c>
       <c r="M6" s="0">
-        <v>119.20999999999999</v>
+        <v>11.920999999999999</v>
       </c>
       <c r="N6" s="0">
-        <v>723.77499999999998</v>
+        <v>72.376999999999995</v>
       </c>
       <c r="O6" s="0">
-        <v>746.27099999999996</v>
+        <v>74.626999999999995</v>
       </c>
       <c r="P6" s="0">
-        <v>682.30600000000004</v>
+        <v>68.230999999999995</v>
       </c>
       <c r="Q6" s="0">
-        <v>627.69600000000003</v>
+        <v>62.770000000000003</v>
       </c>
       <c r="R6" s="0">
-        <v>654.50699999999995</v>
+        <v>65.450999999999993</v>
       </c>
       <c r="S6" s="0">
-        <v>635.95799999999997</v>
+        <v>63.595999999999997</v>
       </c>
       <c r="T6" s="0">
-        <v>161.43799999999999</v>
+        <v>16.143999999999998</v>
       </c>
       <c r="U6" s="0">
-        <v>160.85400000000001</v>
+        <v>16.085000000000001</v>
       </c>
       <c r="V6" s="0">
-        <v>107.05</v>
+        <v>10.705</v>
       </c>
       <c r="W6" s="0">
-        <v>116.66800000000001</v>
+        <v>11.667</v>
       </c>
       <c r="X6" s="0">
-        <v>96.986000000000004</v>
+        <v>9.6989999999999998</v>
       </c>
       <c r="Y6" s="0">
-        <v>102.649</v>
+        <v>10.265000000000001</v>
       </c>
       <c r="Z6" s="0">
-        <v>346.971</v>
+        <v>34.697000000000003</v>
       </c>
       <c r="AA6" s="0">
-        <v>124.643</v>
+        <v>12.464</v>
       </c>
       <c r="AB6" s="0">
-        <v>178.52799999999999</v>
+        <v>17.853000000000002</v>
       </c>
       <c r="AC6" s="0">
-        <v>81.293999999999997</v>
+        <v>8.1289999999999996</v>
       </c>
       <c r="AD6" s="0">
-        <v>110.863</v>
+        <v>11.086</v>
       </c>
       <c r="AE6" s="0">
-        <v>110.557</v>
+        <v>11.055999999999999</v>
       </c>
       <c r="AF6" s="0">
-        <v>674.17600000000004</v>
+        <v>67.418000000000006</v>
       </c>
       <c r="AG6" s="0">
-        <v>634.17399999999998</v>
+        <v>63.417000000000002</v>
       </c>
       <c r="AH6" s="0">
-        <v>711.36400000000003</v>
+        <v>71.135999999999996</v>
       </c>
       <c r="AI6" s="0">
-        <v>568.74000000000001</v>
+        <v>56.874000000000002</v>
       </c>
       <c r="AJ6" s="0">
-        <v>623.55399999999997</v>
+        <v>62.354999999999997</v>
       </c>
       <c r="AK6" s="0">
-        <v>603.54100000000005</v>
+        <v>60.353999999999999</v>
       </c>
       <c r="AL6" s="0">
         <v>142.52799999999999</v>
@@ -8616,112 +8616,112 @@
         <v>106</v>
       </c>
       <c r="B7" s="0">
-        <v>155.27500000000001</v>
+        <v>15.528</v>
       </c>
       <c r="C7" s="0">
-        <v>192.18199999999999</v>
+        <v>19.218</v>
       </c>
       <c r="D7" s="0">
-        <v>118.169</v>
+        <v>11.817</v>
       </c>
       <c r="E7" s="0">
-        <v>99.162000000000006</v>
+        <v>9.9160000000000004</v>
       </c>
       <c r="F7" s="0">
-        <v>167.60900000000001</v>
+        <v>16.760999999999999</v>
       </c>
       <c r="G7" s="0">
-        <v>133.73099999999999</v>
+        <v>13.372999999999999</v>
       </c>
       <c r="H7" s="0">
-        <v>92.402000000000001</v>
+        <v>9.2400000000000002</v>
       </c>
       <c r="I7" s="0">
-        <v>136.90600000000001</v>
+        <v>13.691000000000001</v>
       </c>
       <c r="J7" s="0">
-        <v>58.338000000000001</v>
+        <v>5.8339999999999996</v>
       </c>
       <c r="K7" s="0">
-        <v>124.274</v>
+        <v>12.427</v>
       </c>
       <c r="L7" s="0">
-        <v>148.851</v>
+        <v>14.885</v>
       </c>
       <c r="M7" s="0">
-        <v>203.16900000000001</v>
+        <v>20.317</v>
       </c>
       <c r="N7" s="0">
-        <v>799.28999999999996</v>
+        <v>79.929000000000002</v>
       </c>
       <c r="O7" s="0">
-        <v>940.18100000000004</v>
+        <v>94.018000000000001</v>
       </c>
       <c r="P7" s="0">
-        <v>987.95600000000002</v>
+        <v>98.796000000000006</v>
       </c>
       <c r="Q7" s="0">
-        <v>1065.4960000000001</v>
+        <v>106.55</v>
       </c>
       <c r="R7" s="0">
-        <v>941.19500000000005</v>
+        <v>94.119</v>
       </c>
       <c r="S7" s="0">
-        <v>948.31500000000005</v>
+        <v>94.831000000000003</v>
       </c>
       <c r="T7" s="0">
-        <v>164.52500000000001</v>
+        <v>16.452999999999999</v>
       </c>
       <c r="U7" s="0">
-        <v>269.44900000000001</v>
+        <v>26.945</v>
       </c>
       <c r="V7" s="0">
-        <v>267.875</v>
+        <v>26.788</v>
       </c>
       <c r="W7" s="0">
-        <v>309.05900000000003</v>
+        <v>30.905999999999999</v>
       </c>
       <c r="X7" s="0">
-        <v>243.65199999999999</v>
+        <v>24.364999999999998</v>
       </c>
       <c r="Y7" s="0">
-        <v>206.71100000000001</v>
+        <v>20.670999999999999</v>
       </c>
       <c r="Z7" s="0">
-        <v>270.36799999999999</v>
+        <v>27.036999999999999</v>
       </c>
       <c r="AA7" s="0">
-        <v>206.078</v>
+        <v>20.608000000000001</v>
       </c>
       <c r="AB7" s="0">
-        <v>202.96600000000001</v>
+        <v>20.297000000000001</v>
       </c>
       <c r="AC7" s="0">
-        <v>147.96199999999999</v>
+        <v>14.795999999999999</v>
       </c>
       <c r="AD7" s="0">
-        <v>154.386</v>
+        <v>15.439</v>
       </c>
       <c r="AE7" s="0">
-        <v>192.215</v>
+        <v>19.222000000000001</v>
       </c>
       <c r="AF7" s="0">
-        <v>974.87199999999996</v>
+        <v>97.486999999999995</v>
       </c>
       <c r="AG7" s="0">
-        <v>893.62800000000004</v>
+        <v>89.363</v>
       </c>
       <c r="AH7" s="0">
-        <v>930.05399999999997</v>
+        <v>93.004999999999995</v>
       </c>
       <c r="AI7" s="0">
-        <v>881.76499999999999</v>
+        <v>88.177000000000007</v>
       </c>
       <c r="AJ7" s="0">
-        <v>850.86900000000003</v>
+        <v>85.087000000000003</v>
       </c>
       <c r="AK7" s="0">
-        <v>867.27099999999996</v>
+        <v>86.727000000000004</v>
       </c>
       <c r="AL7" s="0">
         <v>141.18199999999999</v>
@@ -8879,57 +8879,81 @@
       <c r="CK7" s="0">
         <v>46.844000000000001</v>
       </c>
-      <c r="CL7" s="0"/>
+      <c r="CL7" s="0">
+        <v>29.968</v>
+      </c>
       <c r="CM7" s="0">
         <v>75.823999999999998</v>
       </c>
-      <c r="CN7" s="0"/>
+      <c r="CN7" s="0">
+        <v>36.895000000000003</v>
+      </c>
       <c r="CO7" s="0">
         <v>37.932000000000002</v>
       </c>
       <c r="CP7" s="0">
         <v>42.509</v>
       </c>
-      <c r="CQ7" s="0"/>
-      <c r="CR7" s="0"/>
+      <c r="CQ7" s="0">
+        <v>60.479999999999997</v>
+      </c>
+      <c r="CR7" s="0">
+        <v>23.052</v>
+      </c>
       <c r="CS7" s="0">
         <v>36.811999999999998</v>
       </c>
-      <c r="CT7" s="0"/>
+      <c r="CT7" s="0">
+        <v>42.279000000000003</v>
+      </c>
       <c r="CU7" s="0">
         <v>32.301000000000002</v>
       </c>
       <c r="CV7" s="0">
         <v>20.425999999999998</v>
       </c>
-      <c r="CW7" s="0"/>
+      <c r="CW7" s="0">
+        <v>28.919</v>
+      </c>
       <c r="CX7" s="0">
         <v>16.748000000000001</v>
       </c>
-      <c r="CY7" s="0"/>
+      <c r="CY7" s="0">
+        <v>57.133000000000003</v>
+      </c>
       <c r="CZ7" s="0">
         <v>87.706000000000003</v>
       </c>
-      <c r="DA7" s="0"/>
+      <c r="DA7" s="0">
+        <v>93.936000000000007</v>
+      </c>
       <c r="DB7" s="0">
         <v>43.975999999999999</v>
       </c>
       <c r="DC7" s="0">
         <v>86.609999999999999</v>
       </c>
-      <c r="DD7" s="0"/>
-      <c r="DE7" s="0"/>
+      <c r="DD7" s="0">
+        <v>66.489999999999995</v>
+      </c>
+      <c r="DE7" s="0">
+        <v>17.943000000000001</v>
+      </c>
       <c r="DF7" s="0">
         <v>27.395</v>
       </c>
-      <c r="DG7" s="0"/>
+      <c r="DG7" s="0">
+        <v>33.232999999999997</v>
+      </c>
       <c r="DH7" s="0">
         <v>93.325000000000003</v>
       </c>
       <c r="DI7" s="0">
         <v>30.792999999999999</v>
       </c>
-      <c r="DJ7" s="0"/>
+      <c r="DJ7" s="0">
+        <v>106.02</v>
+      </c>
       <c r="DK7" s="0">
         <v>57.911999999999999</v>
       </c>
@@ -8972,57 +8996,81 @@
       <c r="DX7" s="0">
         <v>8.2319999999999993</v>
       </c>
-      <c r="DY7" s="0"/>
+      <c r="DY7" s="0">
+        <v>-13.789999999999999</v>
+      </c>
       <c r="DZ7" s="0">
         <v>-15.231999999999999</v>
       </c>
-      <c r="EA7" s="0"/>
+      <c r="EA7" s="0">
+        <v>-15.377000000000001</v>
+      </c>
       <c r="EB7" s="0">
         <v>-11.234999999999999</v>
       </c>
       <c r="EC7" s="0">
         <v>-21.981000000000002</v>
       </c>
-      <c r="ED7" s="0"/>
-      <c r="EE7" s="0"/>
+      <c r="ED7" s="0">
+        <v>-7.6210000000000004</v>
+      </c>
+      <c r="EE7" s="0">
+        <v>-2.6549999999999998</v>
+      </c>
       <c r="EF7" s="0">
         <v>-8.8520000000000003</v>
       </c>
-      <c r="EG7" s="0"/>
+      <c r="EG7" s="0">
+        <v>-8.4700000000000006</v>
+      </c>
       <c r="EH7" s="0">
         <v>-22.593</v>
       </c>
       <c r="EI7" s="0">
         <v>-14.754</v>
       </c>
-      <c r="EJ7" s="0"/>
+      <c r="EJ7" s="0">
+        <v>-17.393000000000001</v>
+      </c>
       <c r="EK7" s="0">
         <v>-3.431</v>
       </c>
-      <c r="EL7" s="0"/>
+      <c r="EL7" s="0">
+        <v>-3.1419999999999999</v>
+      </c>
       <c r="EM7" s="0">
         <v>-3.79</v>
       </c>
-      <c r="EN7" s="0"/>
+      <c r="EN7" s="0">
+        <v>-3.3580000000000001</v>
+      </c>
       <c r="EO7" s="0">
         <v>1.883</v>
       </c>
       <c r="EP7" s="0">
         <v>-4.9370000000000003</v>
       </c>
-      <c r="EQ7" s="0"/>
-      <c r="ER7" s="0"/>
+      <c r="EQ7" s="0">
+        <v>1.635</v>
+      </c>
+      <c r="ER7" s="0">
+        <v>1.5600000000000001</v>
+      </c>
       <c r="ES7" s="0">
         <v>0.38500000000000001</v>
       </c>
-      <c r="ET7" s="0"/>
+      <c r="ET7" s="0">
+        <v>-0.81399999999999995</v>
+      </c>
       <c r="EU7" s="0">
         <v>-1.99</v>
       </c>
       <c r="EV7" s="0">
         <v>-1.3700000000000001</v>
       </c>
-      <c r="EW7" s="0"/>
+      <c r="EW7" s="0">
+        <v>-1.794</v>
+      </c>
       <c r="EX7" s="0">
         <v>-2.5739999999999998</v>
       </c>
@@ -9065,57 +9113,81 @@
       <c r="FK7" s="0">
         <v>-38.613</v>
       </c>
-      <c r="FL7" s="0"/>
+      <c r="FL7" s="0">
+        <v>30.131</v>
+      </c>
       <c r="FM7" s="0">
         <v>76.933999999999997</v>
       </c>
-      <c r="FN7" s="0"/>
+      <c r="FN7" s="0">
+        <v>37.009999999999998</v>
+      </c>
       <c r="FO7" s="0">
         <v>38.414999999999999</v>
       </c>
       <c r="FP7" s="0">
         <v>40.965000000000003</v>
       </c>
-      <c r="FQ7" s="0"/>
-      <c r="FR7" s="0"/>
+      <c r="FQ7" s="0">
+        <v>63.828000000000003</v>
+      </c>
+      <c r="FR7" s="0">
+        <v>20.693999999999999</v>
+      </c>
       <c r="FS7" s="0">
         <v>42.774000000000001</v>
       </c>
-      <c r="FT7" s="0"/>
+      <c r="FT7" s="0">
+        <v>45.981000000000002</v>
+      </c>
       <c r="FU7" s="0">
         <v>30.053999999999998</v>
       </c>
       <c r="FV7" s="0">
         <v>29.837</v>
       </c>
-      <c r="FW7" s="0"/>
+      <c r="FW7" s="0">
+        <v>33.026000000000003</v>
+      </c>
       <c r="FX7" s="0">
         <v>13.313000000000001</v>
       </c>
-      <c r="FY7" s="0"/>
+      <c r="FY7" s="0">
+        <v>61.247</v>
+      </c>
       <c r="FZ7" s="0">
         <v>84.745000000000005</v>
       </c>
-      <c r="GA7" s="0"/>
+      <c r="GA7" s="0">
+        <v>91.774000000000001</v>
+      </c>
       <c r="GB7" s="0">
         <v>40.372999999999998</v>
       </c>
       <c r="GC7" s="0">
         <v>81.939999999999998</v>
       </c>
-      <c r="GD7" s="0"/>
-      <c r="GE7" s="0"/>
+      <c r="GD7" s="0">
+        <v>61.106999999999999</v>
+      </c>
+      <c r="GE7" s="0">
+        <v>14.045999999999999</v>
+      </c>
       <c r="GF7" s="0">
         <v>24.518000000000001</v>
       </c>
-      <c r="GG7" s="0"/>
+      <c r="GG7" s="0">
+        <v>29.995999999999999</v>
+      </c>
       <c r="GH7" s="0">
         <v>92.975999999999999</v>
       </c>
       <c r="GI7" s="0">
         <v>26.93</v>
       </c>
-      <c r="GJ7" s="0"/>
+      <c r="GJ7" s="0">
+        <v>105.048</v>
+      </c>
       <c r="GK7" s="0">
         <v>57.353000000000002</v>
       </c>
@@ -9236,30 +9308,42 @@
       <c r="HX7" s="0">
         <v>80.947999999999993</v>
       </c>
-      <c r="HY7" s="0"/>
+      <c r="HY7" s="0">
+        <v>43.009</v>
+      </c>
       <c r="HZ7" s="0">
         <v>87.033000000000001</v>
       </c>
-      <c r="IA7" s="0"/>
+      <c r="IA7" s="0">
+        <v>91.959000000000003</v>
+      </c>
       <c r="IB7" s="0">
         <v>58.820999999999998</v>
       </c>
       <c r="IC7" s="0">
         <v>83.519999999999996</v>
       </c>
-      <c r="ID7" s="0"/>
-      <c r="IE7" s="0"/>
+      <c r="ID7" s="0">
+        <v>80.769000000000005</v>
+      </c>
+      <c r="IE7" s="0">
+        <v>26.925000000000001</v>
+      </c>
       <c r="IF7" s="0">
         <v>45.262</v>
       </c>
-      <c r="IG7" s="0"/>
+      <c r="IG7" s="0">
+        <v>49.752000000000002</v>
+      </c>
       <c r="IH7" s="0">
         <v>41.037999999999997</v>
       </c>
       <c r="II7" s="0">
         <v>47.109000000000002</v>
       </c>
-      <c r="IJ7" s="0"/>
+      <c r="IJ7" s="0">
+        <v>31.440000000000001</v>
+      </c>
       <c r="IK7" s="0">
         <v>23.312000000000001</v>
       </c>
@@ -9419,57 +9503,81 @@
       <c r="KK7" s="0">
         <v>18.579000000000001</v>
       </c>
-      <c r="KL7" s="0"/>
+      <c r="KL7" s="0">
+        <v>7.0350000000000001</v>
+      </c>
       <c r="KM7" s="0">
         <v>8.5429999999999993</v>
       </c>
-      <c r="KN7" s="0"/>
+      <c r="KN7" s="0">
+        <v>-6.7839999999999998</v>
+      </c>
       <c r="KO7" s="0">
         <v>-0.503</v>
       </c>
       <c r="KP7" s="0">
         <v>8.0399999999999991</v>
       </c>
-      <c r="KQ7" s="0"/>
-      <c r="KR7" s="0"/>
+      <c r="KQ7" s="0">
+        <v>-1.0049999999999999</v>
+      </c>
+      <c r="KR7" s="0">
+        <v>24.120999999999999</v>
+      </c>
       <c r="KS7" s="0">
         <v>7.2859999999999996</v>
       </c>
-      <c r="KT7" s="0"/>
+      <c r="KT7" s="0">
+        <v>4.5229999999999997</v>
+      </c>
       <c r="KU7" s="0">
         <v>12.06</v>
       </c>
       <c r="KV7" s="0">
         <v>7.0350000000000001</v>
       </c>
-      <c r="KW7" s="0"/>
+      <c r="KW7" s="0">
+        <v>12.563000000000001</v>
+      </c>
       <c r="KX7" s="0">
         <v>13.568</v>
       </c>
-      <c r="KY7" s="0"/>
+      <c r="KY7" s="0">
+        <v>34.170999999999999</v>
+      </c>
       <c r="KZ7" s="0">
         <v>51.759</v>
       </c>
-      <c r="LA7" s="0"/>
+      <c r="LA7" s="0">
+        <v>51.005000000000003</v>
+      </c>
       <c r="LB7" s="0">
         <v>18.593</v>
       </c>
       <c r="LC7" s="0">
         <v>50.250999999999998</v>
       </c>
-      <c r="LD7" s="0"/>
-      <c r="LE7" s="0"/>
+      <c r="LD7" s="0">
+        <v>-43.216000000000001</v>
+      </c>
+      <c r="LE7" s="0">
+        <v>-4.0199999999999996</v>
+      </c>
       <c r="LF7" s="0">
         <v>-4.0199999999999996</v>
       </c>
-      <c r="LG7" s="0"/>
+      <c r="LG7" s="0">
+        <v>-5.5279999999999996</v>
+      </c>
       <c r="LH7" s="0">
         <v>24.120999999999999</v>
       </c>
       <c r="LI7" s="0">
         <v>-5.5279999999999996</v>
       </c>
-      <c r="LJ7" s="0"/>
+      <c r="LJ7" s="0">
+        <v>25.628</v>
+      </c>
       <c r="LK7" s="0">
         <v>24.873999999999999</v>
       </c>
@@ -9629,30 +9737,42 @@
       <c r="NK7" s="0">
         <v>-7.9880000000000004</v>
       </c>
-      <c r="NL7" s="0"/>
+      <c r="NL7" s="0">
+        <v>6.5330000000000004</v>
+      </c>
       <c r="NM7" s="0">
         <v>0.503</v>
       </c>
-      <c r="NN7" s="0"/>
+      <c r="NN7" s="0">
+        <v>2.2610000000000001</v>
+      </c>
       <c r="NO7" s="0">
         <v>-6.5330000000000004</v>
       </c>
       <c r="NP7" s="0">
         <v>0.503</v>
       </c>
-      <c r="NQ7" s="0"/>
-      <c r="NR7" s="0"/>
+      <c r="NQ7" s="0">
+        <v>1.0049999999999999</v>
+      </c>
+      <c r="NR7" s="0">
+        <v>22.864000000000001</v>
+      </c>
       <c r="NS7" s="0">
         <v>7.0350000000000001</v>
       </c>
-      <c r="NT7" s="0"/>
+      <c r="NT7" s="0">
+        <v>7.5380000000000003</v>
+      </c>
       <c r="NU7" s="0">
         <v>8.0399999999999991</v>
       </c>
       <c r="NV7" s="0">
         <v>7.5380000000000003</v>
       </c>
-      <c r="NW7" s="0"/>
+      <c r="NW7" s="0">
+        <v>10.050000000000001</v>
+      </c>
       <c r="NX7" s="0">
         <v>28.140999999999998</v>
       </c>
@@ -9662,112 +9782,112 @@
         <v>107</v>
       </c>
       <c r="B8" s="0">
-        <v>118.895</v>
+        <v>11.890000000000001</v>
       </c>
       <c r="C8" s="0">
-        <v>132.30500000000001</v>
+        <v>13.23</v>
       </c>
       <c r="D8" s="0">
-        <v>82.813999999999993</v>
+        <v>8.2810000000000006</v>
       </c>
       <c r="E8" s="0">
-        <v>187.636</v>
+        <v>18.763999999999999</v>
       </c>
       <c r="F8" s="0">
-        <v>151.286</v>
+        <v>15.129</v>
       </c>
       <c r="G8" s="0">
-        <v>185.70599999999999</v>
+        <v>18.571000000000002</v>
       </c>
       <c r="H8" s="0">
-        <v>226.83600000000001</v>
+        <v>22.684000000000001</v>
       </c>
       <c r="I8" s="0">
-        <v>119.70699999999999</v>
+        <v>11.971</v>
       </c>
       <c r="J8" s="0">
-        <v>94.471999999999994</v>
+        <v>9.4469999999999992</v>
       </c>
       <c r="K8" s="0">
-        <v>190.03200000000001</v>
+        <v>19.003</v>
       </c>
       <c r="L8" s="0">
-        <v>299.71899999999999</v>
+        <v>29.972000000000001</v>
       </c>
       <c r="M8" s="0">
-        <v>276.995</v>
+        <v>27.699999999999999</v>
       </c>
       <c r="N8" s="0">
-        <v>1181.1289999999999</v>
+        <v>118.113</v>
       </c>
       <c r="O8" s="0">
-        <v>1013.602</v>
+        <v>101.36</v>
       </c>
       <c r="P8" s="0">
-        <v>1143.71</v>
+        <v>114.371</v>
       </c>
       <c r="Q8" s="0">
-        <v>916.63199999999995</v>
+        <v>91.662999999999997</v>
       </c>
       <c r="R8" s="0">
-        <v>1040.2</v>
+        <v>104.02</v>
       </c>
       <c r="S8" s="0">
-        <v>972.85299999999995</v>
+        <v>97.284999999999997</v>
       </c>
       <c r="T8" s="0">
-        <v>315.96899999999999</v>
+        <v>31.597000000000001</v>
       </c>
       <c r="U8" s="0">
-        <v>229.696</v>
+        <v>22.969999999999999</v>
       </c>
       <c r="V8" s="0">
-        <v>257.45100000000002</v>
+        <v>25.745000000000001</v>
       </c>
       <c r="W8" s="0">
-        <v>151.035</v>
+        <v>15.103999999999999</v>
       </c>
       <c r="X8" s="0">
-        <v>234.72800000000001</v>
+        <v>23.472999999999999</v>
       </c>
       <c r="Y8" s="0">
-        <v>197.28899999999999</v>
+        <v>19.728999999999999</v>
       </c>
       <c r="Z8" s="0">
-        <v>257.61900000000003</v>
+        <v>25.762</v>
       </c>
       <c r="AA8" s="0">
-        <v>297.74900000000002</v>
+        <v>29.774999999999999</v>
       </c>
       <c r="AB8" s="0">
-        <v>223.08000000000001</v>
+        <v>22.308</v>
       </c>
       <c r="AC8" s="0">
-        <v>498.50900000000001</v>
+        <v>49.850999999999999</v>
       </c>
       <c r="AD8" s="0">
-        <v>208.81999999999999</v>
+        <v>20.882000000000001</v>
       </c>
       <c r="AE8" s="0">
-        <v>148.87899999999999</v>
+        <v>14.888</v>
       </c>
       <c r="AF8" s="0">
-        <v>1056.104</v>
+        <v>105.61</v>
       </c>
       <c r="AG8" s="0">
-        <v>1091.9300000000001</v>
+        <v>109.193</v>
       </c>
       <c r="AH8" s="0">
-        <v>1033.425</v>
+        <v>103.342</v>
       </c>
       <c r="AI8" s="0">
-        <v>1056.2429999999999</v>
+        <v>105.624</v>
       </c>
       <c r="AJ8" s="0">
-        <v>1016.511</v>
+        <v>101.651</v>
       </c>
       <c r="AK8" s="0">
-        <v>937.88300000000004</v>
+        <v>93.787999999999997</v>
       </c>
       <c r="AL8" s="0">
         <v>182.453</v>
@@ -10828,112 +10948,112 @@
         <v>108</v>
       </c>
       <c r="B9" s="0">
-        <v>184.65199999999999</v>
+        <v>18.465</v>
       </c>
       <c r="C9" s="0">
-        <v>198.12700000000001</v>
+        <v>19.812999999999999</v>
       </c>
       <c r="D9" s="0">
-        <v>194.292</v>
+        <v>19.428999999999998</v>
       </c>
       <c r="E9" s="0">
-        <v>182.77799999999999</v>
+        <v>18.277999999999999</v>
       </c>
       <c r="F9" s="0">
-        <v>265.447</v>
+        <v>26.545000000000002</v>
       </c>
       <c r="G9" s="0">
-        <v>224.57499999999999</v>
+        <v>22.457999999999998</v>
       </c>
       <c r="H9" s="0">
-        <v>300.03199999999998</v>
+        <v>30.003</v>
       </c>
       <c r="I9" s="0">
-        <v>340.375</v>
+        <v>34.037999999999997</v>
       </c>
       <c r="J9" s="0">
-        <v>153.32900000000001</v>
+        <v>15.333</v>
       </c>
       <c r="K9" s="0">
-        <v>227.54900000000001</v>
+        <v>22.754999999999999</v>
       </c>
       <c r="L9" s="0">
-        <v>105.095</v>
+        <v>10.509</v>
       </c>
       <c r="M9" s="0">
-        <v>100.042</v>
+        <v>10.004</v>
       </c>
       <c r="N9" s="0">
-        <v>945.952</v>
+        <v>94.594999999999999</v>
       </c>
       <c r="O9" s="0">
-        <v>592.61599999999999</v>
+        <v>59.262</v>
       </c>
       <c r="P9" s="0">
-        <v>690.73099999999999</v>
+        <v>69.072999999999993</v>
       </c>
       <c r="Q9" s="0">
-        <v>678.58900000000006</v>
+        <v>67.858999999999995</v>
       </c>
       <c r="R9" s="0">
-        <v>586.053</v>
+        <v>58.604999999999997</v>
       </c>
       <c r="S9" s="0">
-        <v>719.13300000000004</v>
+        <v>71.912999999999997</v>
       </c>
       <c r="T9" s="0">
-        <v>246.63800000000001</v>
+        <v>24.664000000000001</v>
       </c>
       <c r="U9" s="0">
-        <v>136.03999999999999</v>
+        <v>13.603999999999999</v>
       </c>
       <c r="V9" s="0">
-        <v>137.643</v>
+        <v>13.763999999999999</v>
       </c>
       <c r="W9" s="0">
-        <v>153.86799999999999</v>
+        <v>15.387</v>
       </c>
       <c r="X9" s="0">
-        <v>113.886</v>
+        <v>11.388999999999999</v>
       </c>
       <c r="Y9" s="0">
-        <v>139.761</v>
+        <v>13.976000000000001</v>
       </c>
       <c r="Z9" s="0">
-        <v>217.74000000000001</v>
+        <v>21.774000000000001</v>
       </c>
       <c r="AA9" s="0">
-        <v>254.876</v>
+        <v>25.488</v>
       </c>
       <c r="AB9" s="0">
-        <v>253.17099999999999</v>
+        <v>25.317</v>
       </c>
       <c r="AC9" s="0">
-        <v>162.58500000000001</v>
+        <v>16.257999999999999</v>
       </c>
       <c r="AD9" s="0">
-        <v>218.58099999999999</v>
+        <v>21.858000000000001</v>
       </c>
       <c r="AE9" s="0">
-        <v>252.96000000000001</v>
+        <v>25.295999999999999</v>
       </c>
       <c r="AF9" s="0">
-        <v>905.34100000000001</v>
+        <v>90.534000000000006</v>
       </c>
       <c r="AG9" s="0">
-        <v>944.96100000000001</v>
+        <v>94.495999999999995</v>
       </c>
       <c r="AH9" s="0">
-        <v>898.03300000000002</v>
+        <v>89.802999999999997</v>
       </c>
       <c r="AI9" s="0">
-        <v>796.84000000000003</v>
+        <v>79.683999999999997</v>
       </c>
       <c r="AJ9" s="0">
-        <v>857.11599999999999</v>
+        <v>85.712000000000003</v>
       </c>
       <c r="AK9" s="0">
-        <v>920.44000000000005</v>
+        <v>92.043999999999997</v>
       </c>
       <c r="AL9" s="0">
         <v>148.67500000000001</v>
@@ -11994,112 +12114,112 @@
         <v>109</v>
       </c>
       <c r="B10" s="0">
-        <v>153.58199999999999</v>
+        <v>15.358000000000001</v>
       </c>
       <c r="C10" s="0">
-        <v>95.462000000000003</v>
+        <v>9.5459999999999994</v>
       </c>
       <c r="D10" s="0">
-        <v>106.86</v>
+        <v>10.686</v>
       </c>
       <c r="E10" s="0">
-        <v>150.08199999999999</v>
+        <v>15.007999999999999</v>
       </c>
       <c r="F10" s="0">
-        <v>163.26499999999999</v>
+        <v>16.326000000000001</v>
       </c>
       <c r="G10" s="0">
-        <v>155.762</v>
+        <v>15.576000000000001</v>
       </c>
       <c r="H10" s="0">
-        <v>84.262</v>
+        <v>8.4260000000000002</v>
       </c>
       <c r="I10" s="0">
-        <v>50.454000000000001</v>
+        <v>5.0449999999999999</v>
       </c>
       <c r="J10" s="0">
-        <v>57.049999999999997</v>
+        <v>5.7050000000000001</v>
       </c>
       <c r="K10" s="0">
-        <v>83.703000000000003</v>
+        <v>8.3699999999999992</v>
       </c>
       <c r="L10" s="0">
-        <v>81.197000000000003</v>
+        <v>8.1199999999999992</v>
       </c>
       <c r="M10" s="0">
-        <v>11.699999999999999</v>
+        <v>1.1699999999999999</v>
       </c>
       <c r="N10" s="0">
-        <v>1022.218</v>
+        <v>102.22199999999999</v>
       </c>
       <c r="O10" s="0">
-        <v>1018.111</v>
+        <v>101.81100000000001</v>
       </c>
       <c r="P10" s="0">
-        <v>927.93200000000002</v>
+        <v>92.793000000000006</v>
       </c>
       <c r="Q10" s="0">
-        <v>1008.562</v>
+        <v>100.85599999999999</v>
       </c>
       <c r="R10" s="0">
-        <v>1047.702</v>
+        <v>104.77</v>
       </c>
       <c r="S10" s="0">
-        <v>964.68299999999999</v>
+        <v>96.468000000000004</v>
       </c>
       <c r="T10" s="0">
-        <v>233.61500000000001</v>
+        <v>23.361000000000001</v>
       </c>
       <c r="U10" s="0">
-        <v>229.274</v>
+        <v>22.927</v>
       </c>
       <c r="V10" s="0">
-        <v>175.631</v>
+        <v>17.562999999999999</v>
       </c>
       <c r="W10" s="0">
-        <v>210.90299999999999</v>
+        <v>21.09</v>
       </c>
       <c r="X10" s="0">
-        <v>219.43700000000001</v>
+        <v>21.943999999999999</v>
       </c>
       <c r="Y10" s="0">
-        <v>180.99600000000001</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="Z10" s="0">
-        <v>344.21300000000002</v>
+        <v>34.420999999999999</v>
       </c>
       <c r="AA10" s="0">
-        <v>368.59699999999998</v>
+        <v>36.859999999999999</v>
       </c>
       <c r="AB10" s="0">
-        <v>432.41000000000003</v>
+        <v>43.241</v>
       </c>
       <c r="AC10" s="0">
-        <v>299.12299999999999</v>
+        <v>29.911999999999999</v>
       </c>
       <c r="AD10" s="0">
-        <v>323.22000000000003</v>
+        <v>32.322000000000003</v>
       </c>
       <c r="AE10" s="0">
-        <v>342.48700000000002</v>
+        <v>34.249000000000002</v>
       </c>
       <c r="AF10" s="0">
-        <v>1102.6600000000001</v>
+        <v>110.26600000000001</v>
       </c>
       <c r="AG10" s="0">
-        <v>1147.335</v>
+        <v>114.733</v>
       </c>
       <c r="AH10" s="0">
-        <v>1231.9390000000001</v>
+        <v>123.194</v>
       </c>
       <c r="AI10" s="0">
-        <v>1107.903</v>
+        <v>110.79000000000001</v>
       </c>
       <c r="AJ10" s="0">
-        <v>1147.451</v>
+        <v>114.745</v>
       </c>
       <c r="AK10" s="0">
-        <v>1191.7670000000001</v>
+        <v>119.17700000000001</v>
       </c>
       <c r="AL10" s="0">
         <v>168.53</v>
